--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O340"/>
+  <dimension ref="A1:O343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17104,6 +17104,153 @@
         <v>13</v>
       </c>
     </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>0</v>
+      </c>
+      <c r="C341" t="n">
+        <v>1</v>
+      </c>
+      <c r="D341" t="n">
+        <v>0</v>
+      </c>
+      <c r="E341" t="n">
+        <v>0</v>
+      </c>
+      <c r="F341" t="n">
+        <v>1</v>
+      </c>
+      <c r="G341" t="n">
+        <v>1</v>
+      </c>
+      <c r="H341" t="n">
+        <v>0</v>
+      </c>
+      <c r="I341" t="n">
+        <v>0</v>
+      </c>
+      <c r="J341" t="n">
+        <v>0</v>
+      </c>
+      <c r="K341" t="n">
+        <v>1</v>
+      </c>
+      <c r="L341" t="n">
+        <v>8</v>
+      </c>
+      <c r="M341" t="n">
+        <v>12</v>
+      </c>
+      <c r="N341" t="n">
+        <v>14</v>
+      </c>
+      <c r="O341" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>0</v>
+      </c>
+      <c r="C342" t="n">
+        <v>0</v>
+      </c>
+      <c r="D342" t="n">
+        <v>0</v>
+      </c>
+      <c r="E342" t="n">
+        <v>1</v>
+      </c>
+      <c r="F342" t="n">
+        <v>0</v>
+      </c>
+      <c r="G342" t="n">
+        <v>0</v>
+      </c>
+      <c r="H342" t="n">
+        <v>1</v>
+      </c>
+      <c r="I342" t="n">
+        <v>1</v>
+      </c>
+      <c r="J342" t="n">
+        <v>0</v>
+      </c>
+      <c r="K342" t="n">
+        <v>0</v>
+      </c>
+      <c r="L342" t="n">
+        <v>5</v>
+      </c>
+      <c r="M342" t="n">
+        <v>8</v>
+      </c>
+      <c r="N342" t="n">
+        <v>10</v>
+      </c>
+      <c r="O342" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>0</v>
+      </c>
+      <c r="C343" t="n">
+        <v>0</v>
+      </c>
+      <c r="D343" t="n">
+        <v>0</v>
+      </c>
+      <c r="E343" t="n">
+        <v>0</v>
+      </c>
+      <c r="F343" t="n">
+        <v>0</v>
+      </c>
+      <c r="G343" t="n">
+        <v>0</v>
+      </c>
+      <c r="H343" t="n">
+        <v>0</v>
+      </c>
+      <c r="I343" t="n">
+        <v>0</v>
+      </c>
+      <c r="J343" t="n">
+        <v>0</v>
+      </c>
+      <c r="K343" t="n">
+        <v>1</v>
+      </c>
+      <c r="L343" t="n">
+        <v>5</v>
+      </c>
+      <c r="M343" t="n">
+        <v>6</v>
+      </c>
+      <c r="N343" t="n">
+        <v>6</v>
+      </c>
+      <c r="O343" t="n">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O343"/>
+  <dimension ref="A1:O345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1642,10 +1642,10 @@
         <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>2</v>
@@ -1746,10 +1746,10 @@
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -5565,10 +5565,10 @@
         <v>3</v>
       </c>
       <c r="H105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -6349,10 +6349,10 @@
         <v>3</v>
       </c>
       <c r="H121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -8361,10 +8361,10 @@
         <v>1</v>
       </c>
       <c r="I162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K162" t="n">
         <v>0</v>
@@ -8756,10 +8756,10 @@
         <v>2</v>
       </c>
       <c r="J170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K170" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L170" t="n">
         <v>0</v>
@@ -8845,10 +8845,10 @@
         <v>12</v>
       </c>
       <c r="G172" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I172" t="n">
         <v>2</v>
@@ -9231,10 +9231,10 @@
         <v>15</v>
       </c>
       <c r="E180" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F180" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G180" t="n">
         <v>24</v>
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C185" t="n">
         <v>12</v>
@@ -9476,7 +9476,7 @@
         <v>15</v>
       </c>
       <c r="E185" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F185" t="n">
         <v>13</v>
@@ -9724,10 +9724,10 @@
         <v>22</v>
       </c>
       <c r="F190" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G190" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H190" t="n">
         <v>4</v>
@@ -9923,10 +9923,10 @@
         <v>7</v>
       </c>
       <c r="G194" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I194" t="n">
         <v>3</v>
@@ -10407,10 +10407,10 @@
         <v>10</v>
       </c>
       <c r="E204" t="n">
+        <v>19</v>
+      </c>
+      <c r="F204" t="n">
         <v>18</v>
-      </c>
-      <c r="F204" t="n">
-        <v>19</v>
       </c>
       <c r="G204" t="n">
         <v>20</v>
@@ -10462,10 +10462,10 @@
         <v>12</v>
       </c>
       <c r="G205" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H205" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I205" t="n">
         <v>4</v>
@@ -10998,10 +10998,10 @@
         <v>3</v>
       </c>
       <c r="F216" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G216" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H216" t="n">
         <v>3</v>
@@ -11439,10 +11439,10 @@
         <v>4</v>
       </c>
       <c r="F225" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G225" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H225" t="n">
         <v>6</v>
@@ -11638,13 +11638,13 @@
         <v>3</v>
       </c>
       <c r="G229" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H229" t="n">
         <v>8</v>
       </c>
       <c r="I229" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J229" t="n">
         <v>2</v>
@@ -11834,10 +11834,10 @@
         <v>17</v>
       </c>
       <c r="G233" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H233" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I233" t="n">
         <v>3</v>
@@ -11932,10 +11932,10 @@
         <v>14</v>
       </c>
       <c r="G235" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H235" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I235" t="n">
         <v>2</v>
@@ -11975,16 +11975,16 @@
         <v>9</v>
       </c>
       <c r="E236" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F236" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G236" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H236" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I236" t="n">
         <v>8</v>
@@ -12027,10 +12027,10 @@
         <v>16</v>
       </c>
       <c r="F237" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G237" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H237" t="n">
         <v>7</v>
@@ -12171,16 +12171,16 @@
         <v>13</v>
       </c>
       <c r="E240" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F240" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G240" t="n">
         <v>65</v>
       </c>
       <c r="H240" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I240" t="n">
         <v>6</v>
@@ -12223,10 +12223,10 @@
         <v>21</v>
       </c>
       <c r="F241" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G241" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -12324,10 +12324,10 @@
         <v>9</v>
       </c>
       <c r="G243" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H243" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I243" t="n">
         <v>0</v>
@@ -12618,10 +12618,10 @@
         <v>13</v>
       </c>
       <c r="G249" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H249" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I249" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>1</v>
       </c>
       <c r="G254" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H254" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I254" t="n">
         <v>9</v>
@@ -12915,10 +12915,10 @@
         <v>43</v>
       </c>
       <c r="H255" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I255" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J255" t="n">
         <v>1</v>
@@ -12952,10 +12952,10 @@
         <v>20</v>
       </c>
       <c r="D256" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E256" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F256" t="n">
         <v>17</v>
@@ -12970,10 +12970,10 @@
         <v>5</v>
       </c>
       <c r="J256" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K256" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L256" t="n">
         <v>5</v>
@@ -13010,10 +13010,10 @@
         <v>6</v>
       </c>
       <c r="G257" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H257" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I257" t="n">
         <v>4</v>
@@ -13206,10 +13206,10 @@
         <v>60</v>
       </c>
       <c r="G261" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H261" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I261" t="n">
         <v>3</v>
@@ -13301,10 +13301,10 @@
         <v>19</v>
       </c>
       <c r="F263" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G263" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H263" t="n">
         <v>2</v>
@@ -13347,10 +13347,10 @@
         <v>13</v>
       </c>
       <c r="E264" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F264" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G264" t="n">
         <v>13</v>
@@ -13494,10 +13494,10 @@
         <v>7</v>
       </c>
       <c r="E267" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F267" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G267" t="n">
         <v>47</v>
@@ -13549,10 +13549,10 @@
         <v>11</v>
       </c>
       <c r="G268" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H268" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I268" t="n">
         <v>2</v>
@@ -13598,10 +13598,10 @@
         <v>0</v>
       </c>
       <c r="G269" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H269" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I269" t="n">
         <v>2</v>
@@ -13892,10 +13892,10 @@
         <v>26</v>
       </c>
       <c r="G275" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H275" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I275" t="n">
         <v>2</v>
@@ -13993,13 +13993,13 @@
         <v>16</v>
       </c>
       <c r="H277" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I277" t="n">
         <v>1</v>
       </c>
       <c r="J277" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K277" t="n">
         <v>0</v>
@@ -14042,10 +14042,10 @@
         <v>14</v>
       </c>
       <c r="H278" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I278" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J278" t="n">
         <v>0</v>
@@ -14183,10 +14183,10 @@
         <v>24</v>
       </c>
       <c r="F281" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G281" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H281" t="n">
         <v>1</v>
@@ -14342,10 +14342,10 @@
         <v>3</v>
       </c>
       <c r="J284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K284" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L284" t="n">
         <v>16</v>
@@ -14581,10 +14581,10 @@
         <v>35</v>
       </c>
       <c r="H289" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I289" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J289" t="n">
         <v>0</v>
@@ -14872,10 +14872,10 @@
         <v>21</v>
       </c>
       <c r="G295" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H295" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I295" t="n">
         <v>5</v>
@@ -14912,13 +14912,13 @@
         <v>0</v>
       </c>
       <c r="D296" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E296" t="n">
         <v>30</v>
       </c>
       <c r="F296" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G296" t="n">
         <v>22</v>
@@ -14976,10 +14976,10 @@
         <v>4</v>
       </c>
       <c r="I297" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J297" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K297" t="n">
         <v>1</v>
@@ -15261,16 +15261,16 @@
         <v>2</v>
       </c>
       <c r="F303" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G303" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H303" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I303" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J303" t="n">
         <v>3</v>
@@ -15319,10 +15319,10 @@
         <v>3</v>
       </c>
       <c r="I304" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J304" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K304" t="n">
         <v>0</v>
@@ -15362,13 +15362,13 @@
         <v>5</v>
       </c>
       <c r="G305" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H305" t="n">
         <v>7</v>
       </c>
       <c r="I305" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J305" t="n">
         <v>3</v>
@@ -15509,10 +15509,10 @@
         <v>0</v>
       </c>
       <c r="G308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H308" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I308" t="n">
         <v>1</v>
@@ -15555,22 +15555,22 @@
         <v>2</v>
       </c>
       <c r="F309" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G309" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H309" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I309" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J309" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K309" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L309" t="n">
         <v>4</v>
@@ -15754,10 +15754,10 @@
         <v>31</v>
       </c>
       <c r="G313" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H313" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I313" t="n">
         <v>12</v>
@@ -15800,10 +15800,10 @@
         <v>27</v>
       </c>
       <c r="F314" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G314" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H314" t="n">
         <v>9</v>
@@ -15895,13 +15895,13 @@
         <v>3</v>
       </c>
       <c r="E316" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F316" t="n">
         <v>13</v>
       </c>
       <c r="G316" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H316" t="n">
         <v>5</v>
@@ -15950,10 +15950,10 @@
         <v>8</v>
       </c>
       <c r="G317" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H317" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I317" t="n">
         <v>7</v>
@@ -16106,10 +16106,10 @@
         <v>1</v>
       </c>
       <c r="J320" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K320" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L320" t="n">
         <v>7</v>
@@ -16498,10 +16498,10 @@
         <v>0</v>
       </c>
       <c r="J328" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K328" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L328" t="n">
         <v>4</v>
@@ -16587,10 +16587,10 @@
         <v>1</v>
       </c>
       <c r="G330" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H330" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I330" t="n">
         <v>4</v>
@@ -16682,10 +16682,10 @@
         <v>3</v>
       </c>
       <c r="F332" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G332" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H332" t="n">
         <v>3</v>
@@ -16734,10 +16734,10 @@
         <v>2</v>
       </c>
       <c r="G333" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H333" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I333" t="n">
         <v>0</v>
@@ -16786,7 +16786,7 @@
         <v>13</v>
       </c>
       <c r="H334" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I334" t="n">
         <v>2</v>
@@ -16798,7 +16798,7 @@
         <v>0</v>
       </c>
       <c r="L334" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M334" t="n">
         <v>32</v>
@@ -16979,10 +16979,10 @@
         <v>5</v>
       </c>
       <c r="G338" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H338" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I338" t="n">
         <v>6</v>
@@ -17025,10 +17025,10 @@
         <v>0</v>
       </c>
       <c r="F339" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G339" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -17111,7 +17111,7 @@
         </is>
       </c>
       <c r="B341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C341" t="n">
         <v>1</v>
@@ -17120,10 +17120,10 @@
         <v>0</v>
       </c>
       <c r="E341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G341" t="n">
         <v>1</v>
@@ -17141,7 +17141,7 @@
         <v>1</v>
       </c>
       <c r="L341" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M341" t="n">
         <v>12</v>
@@ -17160,25 +17160,25 @@
         </is>
       </c>
       <c r="B342" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C342" t="n">
         <v>0</v>
       </c>
       <c r="D342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F342" t="n">
         <v>0</v>
       </c>
       <c r="G342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I342" t="n">
         <v>1</v>
@@ -17190,7 +17190,7 @@
         <v>0</v>
       </c>
       <c r="L342" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M342" t="n">
         <v>8</v>
@@ -17233,10 +17233,10 @@
         <v>0</v>
       </c>
       <c r="J343" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K343" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L343" t="n">
         <v>5</v>
@@ -17249,6 +17249,104 @@
       </c>
       <c r="O343" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>1</v>
+      </c>
+      <c r="C344" t="n">
+        <v>0</v>
+      </c>
+      <c r="D344" t="n">
+        <v>0</v>
+      </c>
+      <c r="E344" t="n">
+        <v>3</v>
+      </c>
+      <c r="F344" t="n">
+        <v>6</v>
+      </c>
+      <c r="G344" t="n">
+        <v>17</v>
+      </c>
+      <c r="H344" t="n">
+        <v>10</v>
+      </c>
+      <c r="I344" t="n">
+        <v>6</v>
+      </c>
+      <c r="J344" t="n">
+        <v>2</v>
+      </c>
+      <c r="K344" t="n">
+        <v>1</v>
+      </c>
+      <c r="L344" t="n">
+        <v>10</v>
+      </c>
+      <c r="M344" t="n">
+        <v>56</v>
+      </c>
+      <c r="N344" t="n">
+        <v>58</v>
+      </c>
+      <c r="O344" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>0</v>
+      </c>
+      <c r="C345" t="n">
+        <v>0</v>
+      </c>
+      <c r="D345" t="n">
+        <v>0</v>
+      </c>
+      <c r="E345" t="n">
+        <v>1</v>
+      </c>
+      <c r="F345" t="n">
+        <v>3</v>
+      </c>
+      <c r="G345" t="n">
+        <v>21</v>
+      </c>
+      <c r="H345" t="n">
+        <v>4</v>
+      </c>
+      <c r="I345" t="n">
+        <v>3</v>
+      </c>
+      <c r="J345" t="n">
+        <v>0</v>
+      </c>
+      <c r="K345" t="n">
+        <v>0</v>
+      </c>
+      <c r="L345" t="n">
+        <v>33</v>
+      </c>
+      <c r="M345" t="n">
+        <v>65</v>
+      </c>
+      <c r="N345" t="n">
+        <v>69</v>
+      </c>
+      <c r="O345" t="n">
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O345"/>
+  <dimension ref="A1:O350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17349,6 +17349,251 @@
         <v>73</v>
       </c>
     </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>0</v>
+      </c>
+      <c r="C346" t="n">
+        <v>0</v>
+      </c>
+      <c r="D346" t="n">
+        <v>0</v>
+      </c>
+      <c r="E346" t="n">
+        <v>2</v>
+      </c>
+      <c r="F346" t="n">
+        <v>4</v>
+      </c>
+      <c r="G346" t="n">
+        <v>10</v>
+      </c>
+      <c r="H346" t="n">
+        <v>5</v>
+      </c>
+      <c r="I346" t="n">
+        <v>4</v>
+      </c>
+      <c r="J346" t="n">
+        <v>2</v>
+      </c>
+      <c r="K346" t="n">
+        <v>0</v>
+      </c>
+      <c r="L346" t="n">
+        <v>24</v>
+      </c>
+      <c r="M346" t="n">
+        <v>51</v>
+      </c>
+      <c r="N346" t="n">
+        <v>54</v>
+      </c>
+      <c r="O346" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>1</v>
+      </c>
+      <c r="C347" t="n">
+        <v>0</v>
+      </c>
+      <c r="D347" t="n">
+        <v>0</v>
+      </c>
+      <c r="E347" t="n">
+        <v>2</v>
+      </c>
+      <c r="F347" t="n">
+        <v>4</v>
+      </c>
+      <c r="G347" t="n">
+        <v>2</v>
+      </c>
+      <c r="H347" t="n">
+        <v>1</v>
+      </c>
+      <c r="I347" t="n">
+        <v>3</v>
+      </c>
+      <c r="J347" t="n">
+        <v>1</v>
+      </c>
+      <c r="K347" t="n">
+        <v>0</v>
+      </c>
+      <c r="L347" t="n">
+        <v>10</v>
+      </c>
+      <c r="M347" t="n">
+        <v>24</v>
+      </c>
+      <c r="N347" t="n">
+        <v>24</v>
+      </c>
+      <c r="O347" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>0</v>
+      </c>
+      <c r="C348" t="n">
+        <v>1</v>
+      </c>
+      <c r="D348" t="n">
+        <v>1</v>
+      </c>
+      <c r="E348" t="n">
+        <v>1</v>
+      </c>
+      <c r="F348" t="n">
+        <v>4</v>
+      </c>
+      <c r="G348" t="n">
+        <v>22</v>
+      </c>
+      <c r="H348" t="n">
+        <v>3</v>
+      </c>
+      <c r="I348" t="n">
+        <v>0</v>
+      </c>
+      <c r="J348" t="n">
+        <v>3</v>
+      </c>
+      <c r="K348" t="n">
+        <v>0</v>
+      </c>
+      <c r="L348" t="n">
+        <v>12</v>
+      </c>
+      <c r="M348" t="n">
+        <v>47</v>
+      </c>
+      <c r="N348" t="n">
+        <v>50</v>
+      </c>
+      <c r="O348" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>0</v>
+      </c>
+      <c r="C349" t="n">
+        <v>0</v>
+      </c>
+      <c r="D349" t="n">
+        <v>0</v>
+      </c>
+      <c r="E349" t="n">
+        <v>0</v>
+      </c>
+      <c r="F349" t="n">
+        <v>1</v>
+      </c>
+      <c r="G349" t="n">
+        <v>9</v>
+      </c>
+      <c r="H349" t="n">
+        <v>2</v>
+      </c>
+      <c r="I349" t="n">
+        <v>3</v>
+      </c>
+      <c r="J349" t="n">
+        <v>1</v>
+      </c>
+      <c r="K349" t="n">
+        <v>0</v>
+      </c>
+      <c r="L349" t="n">
+        <v>14</v>
+      </c>
+      <c r="M349" t="n">
+        <v>30</v>
+      </c>
+      <c r="N349" t="n">
+        <v>31</v>
+      </c>
+      <c r="O349" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>0</v>
+      </c>
+      <c r="C350" t="n">
+        <v>0</v>
+      </c>
+      <c r="D350" t="n">
+        <v>0</v>
+      </c>
+      <c r="E350" t="n">
+        <v>0</v>
+      </c>
+      <c r="F350" t="n">
+        <v>0</v>
+      </c>
+      <c r="G350" t="n">
+        <v>1</v>
+      </c>
+      <c r="H350" t="n">
+        <v>2</v>
+      </c>
+      <c r="I350" t="n">
+        <v>1</v>
+      </c>
+      <c r="J350" t="n">
+        <v>0</v>
+      </c>
+      <c r="K350" t="n">
+        <v>0</v>
+      </c>
+      <c r="L350" t="n">
+        <v>7</v>
+      </c>
+      <c r="M350" t="n">
+        <v>11</v>
+      </c>
+      <c r="N350" t="n">
+        <v>13</v>
+      </c>
+      <c r="O350" t="n">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O350"/>
+  <dimension ref="A1:O351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17594,6 +17594,55 @@
         <v>18</v>
       </c>
     </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>0</v>
+      </c>
+      <c r="C351" t="n">
+        <v>0</v>
+      </c>
+      <c r="D351" t="n">
+        <v>0</v>
+      </c>
+      <c r="E351" t="n">
+        <v>2</v>
+      </c>
+      <c r="F351" t="n">
+        <v>2</v>
+      </c>
+      <c r="G351" t="n">
+        <v>15</v>
+      </c>
+      <c r="H351" t="n">
+        <v>3</v>
+      </c>
+      <c r="I351" t="n">
+        <v>4</v>
+      </c>
+      <c r="J351" t="n">
+        <v>0</v>
+      </c>
+      <c r="K351" t="n">
+        <v>1</v>
+      </c>
+      <c r="L351" t="n">
+        <v>19</v>
+      </c>
+      <c r="M351" t="n">
+        <v>46</v>
+      </c>
+      <c r="N351" t="n">
+        <v>56</v>
+      </c>
+      <c r="O351" t="n">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O351"/>
+  <dimension ref="A1:O352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17643,6 +17643,55 @@
         <v>61</v>
       </c>
     </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>2</v>
+      </c>
+      <c r="C352" t="n">
+        <v>0</v>
+      </c>
+      <c r="D352" t="n">
+        <v>0</v>
+      </c>
+      <c r="E352" t="n">
+        <v>1</v>
+      </c>
+      <c r="F352" t="n">
+        <v>5</v>
+      </c>
+      <c r="G352" t="n">
+        <v>13</v>
+      </c>
+      <c r="H352" t="n">
+        <v>2</v>
+      </c>
+      <c r="I352" t="n">
+        <v>4</v>
+      </c>
+      <c r="J352" t="n">
+        <v>2</v>
+      </c>
+      <c r="K352" t="n">
+        <v>0</v>
+      </c>
+      <c r="L352" t="n">
+        <v>17</v>
+      </c>
+      <c r="M352" t="n">
+        <v>46</v>
+      </c>
+      <c r="N352" t="n">
+        <v>54</v>
+      </c>
+      <c r="O352" t="n">
+        <v>57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O352"/>
+  <dimension ref="A1:O353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17692,6 +17692,55 @@
         <v>57</v>
       </c>
     </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>0</v>
+      </c>
+      <c r="C353" t="n">
+        <v>0</v>
+      </c>
+      <c r="D353" t="n">
+        <v>0</v>
+      </c>
+      <c r="E353" t="n">
+        <v>1</v>
+      </c>
+      <c r="F353" t="n">
+        <v>1</v>
+      </c>
+      <c r="G353" t="n">
+        <v>9</v>
+      </c>
+      <c r="H353" t="n">
+        <v>2</v>
+      </c>
+      <c r="I353" t="n">
+        <v>3</v>
+      </c>
+      <c r="J353" t="n">
+        <v>1</v>
+      </c>
+      <c r="K353" t="n">
+        <v>1</v>
+      </c>
+      <c r="L353" t="n">
+        <v>26</v>
+      </c>
+      <c r="M353" t="n">
+        <v>44</v>
+      </c>
+      <c r="N353" t="n">
+        <v>47</v>
+      </c>
+      <c r="O353" t="n">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -518,16 +518,16 @@
         <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -907,10 +907,10 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -1838,10 +1838,10 @@
         <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>4</v>
@@ -4294,10 +4294,10 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -5127,10 +5127,10 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -7972,10 +7972,10 @@
         <v>5</v>
       </c>
       <c r="J154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L154" t="n">
         <v>0</v>
@@ -8211,7 +8211,7 @@
         <v>8</v>
       </c>
       <c r="H159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I159" t="n">
         <v>3</v>
@@ -8220,7 +8220,7 @@
         <v>0</v>
       </c>
       <c r="K159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L159" t="n">
         <v>0</v>
@@ -8263,10 +8263,10 @@
         <v>1</v>
       </c>
       <c r="I160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K160" t="n">
         <v>0</v>
@@ -9776,10 +9776,10 @@
         <v>13</v>
       </c>
       <c r="G191" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H191" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I191" t="n">
         <v>2</v>
@@ -10315,10 +10315,10 @@
         <v>25</v>
       </c>
       <c r="G202" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H202" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I202" t="n">
         <v>17</v>
@@ -11589,10 +11589,10 @@
         <v>3</v>
       </c>
       <c r="G228" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H228" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I228" t="n">
         <v>5</v>
@@ -11843,10 +11843,10 @@
         <v>3</v>
       </c>
       <c r="J233" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L233" t="n">
         <v>0</v>
@@ -13007,16 +13007,16 @@
         <v>2</v>
       </c>
       <c r="F257" t="n">
+        <v>7</v>
+      </c>
+      <c r="G257" t="n">
+        <v>28</v>
+      </c>
+      <c r="H257" t="n">
         <v>6</v>
       </c>
-      <c r="G257" t="n">
-        <v>29</v>
-      </c>
-      <c r="H257" t="n">
-        <v>5</v>
-      </c>
       <c r="I257" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -13356,10 +13356,10 @@
         <v>13</v>
       </c>
       <c r="H264" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I264" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -13509,10 +13509,10 @@
         <v>3</v>
       </c>
       <c r="J267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K267" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L267" t="n">
         <v>3</v>
@@ -14140,10 +14140,10 @@
         <v>8</v>
       </c>
       <c r="H280" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I280" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J280" t="n">
         <v>4</v>
@@ -15267,10 +15267,10 @@
         <v>90</v>
       </c>
       <c r="H303" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I303" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J303" t="n">
         <v>3</v>
@@ -15561,10 +15561,10 @@
         <v>24</v>
       </c>
       <c r="H309" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I309" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J309" t="n">
         <v>3</v>
@@ -15754,10 +15754,10 @@
         <v>31</v>
       </c>
       <c r="G313" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H313" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I313" t="n">
         <v>12</v>
@@ -15950,10 +15950,10 @@
         <v>8</v>
       </c>
       <c r="G317" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H317" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I317" t="n">
         <v>7</v>
@@ -16394,10 +16394,10 @@
         <v>6</v>
       </c>
       <c r="H326" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I326" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J326" t="n">
         <v>0</v>
@@ -16685,10 +16685,10 @@
         <v>4</v>
       </c>
       <c r="G332" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H332" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I332" t="n">
         <v>3</v>
@@ -16734,10 +16734,10 @@
         <v>2</v>
       </c>
       <c r="G333" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H333" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I333" t="n">
         <v>0</v>
@@ -17570,10 +17570,10 @@
         <v>1</v>
       </c>
       <c r="H350" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I350" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J350" t="n">
         <v>0</v>
@@ -17601,7 +17601,7 @@
         </is>
       </c>
       <c r="B351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C351" t="n">
         <v>0</v>
@@ -17619,10 +17619,10 @@
         <v>15</v>
       </c>
       <c r="H351" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I351" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J351" t="n">
         <v>0</v>
@@ -17631,7 +17631,7 @@
         <v>1</v>
       </c>
       <c r="L351" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M351" t="n">
         <v>46</v>
@@ -17708,7 +17708,7 @@
         <v>0</v>
       </c>
       <c r="E353" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F353" t="n">
         <v>1</v>
@@ -17729,7 +17729,7 @@
         <v>1</v>
       </c>
       <c r="L353" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M353" t="n">
         <v>44</v>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O353"/>
+  <dimension ref="A1:O354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16621,7 +16621,7 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C331" t="n">
         <v>4</v>
@@ -16636,7 +16636,7 @@
         <v>17</v>
       </c>
       <c r="G331" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H331" t="n">
         <v>3</v>
@@ -16651,16 +16651,16 @@
         <v>0</v>
       </c>
       <c r="L331" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M331" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="N331" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="O331" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="332">
@@ -16786,7 +16786,7 @@
         <v>13</v>
       </c>
       <c r="H334" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I334" t="n">
         <v>2</v>
@@ -16801,13 +16801,13 @@
         <v>10</v>
       </c>
       <c r="M334" t="n">
+        <v>31</v>
+      </c>
+      <c r="N334" t="n">
         <v>32</v>
       </c>
-      <c r="N334" t="n">
+      <c r="O334" t="n">
         <v>33</v>
-      </c>
-      <c r="O334" t="n">
-        <v>34</v>
       </c>
     </row>
     <row r="335">
@@ -16976,10 +16976,10 @@
         <v>3</v>
       </c>
       <c r="F338" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G338" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H338" t="n">
         <v>8</v>
@@ -16994,16 +16994,16 @@
         <v>1</v>
       </c>
       <c r="L338" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M338" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N338" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O338" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="339">
@@ -17043,16 +17043,16 @@
         <v>2</v>
       </c>
       <c r="L339" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M339" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N339" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O339" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="340">
@@ -17092,16 +17092,16 @@
         <v>0</v>
       </c>
       <c r="L340" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M340" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N340" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O340" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="341">
@@ -17738,6 +17738,55 @@
         <v>47</v>
       </c>
       <c r="O353" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>1</v>
+      </c>
+      <c r="C354" t="n">
+        <v>0</v>
+      </c>
+      <c r="D354" t="n">
+        <v>2</v>
+      </c>
+      <c r="E354" t="n">
+        <v>2</v>
+      </c>
+      <c r="F354" t="n">
+        <v>2</v>
+      </c>
+      <c r="G354" t="n">
+        <v>13</v>
+      </c>
+      <c r="H354" t="n">
+        <v>4</v>
+      </c>
+      <c r="I354" t="n">
+        <v>3</v>
+      </c>
+      <c r="J354" t="n">
+        <v>1</v>
+      </c>
+      <c r="K354" t="n">
+        <v>0</v>
+      </c>
+      <c r="L354" t="n">
+        <v>13</v>
+      </c>
+      <c r="M354" t="n">
+        <v>41</v>
+      </c>
+      <c r="N354" t="n">
+        <v>46</v>
+      </c>
+      <c r="O354" t="n">
         <v>53</v>
       </c>
     </row>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O354"/>
+  <dimension ref="A1:O358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13938,7 +13938,7 @@
         <v>18</v>
       </c>
       <c r="F276" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G276" t="n">
         <v>7</v>
@@ -13956,7 +13956,7 @@
         <v>0</v>
       </c>
       <c r="L276" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M276" t="n">
         <v>85</v>
@@ -16621,7 +16621,7 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C331" t="n">
         <v>4</v>
@@ -16636,7 +16636,7 @@
         <v>17</v>
       </c>
       <c r="G331" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H331" t="n">
         <v>3</v>
@@ -16651,7 +16651,7 @@
         <v>0</v>
       </c>
       <c r="L331" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M331" t="n">
         <v>118</v>
@@ -16979,10 +16979,10 @@
         <v>3</v>
       </c>
       <c r="G338" t="n">
+        <v>10</v>
+      </c>
+      <c r="H338" t="n">
         <v>9</v>
-      </c>
-      <c r="H338" t="n">
-        <v>8</v>
       </c>
       <c r="I338" t="n">
         <v>6</v>
@@ -16994,7 +16994,7 @@
         <v>1</v>
       </c>
       <c r="L338" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M338" t="n">
         <v>49</v>
@@ -17319,13 +17319,13 @@
         <v>1</v>
       </c>
       <c r="F345" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G345" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H345" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I345" t="n">
         <v>3</v>
@@ -17337,7 +17337,7 @@
         <v>0</v>
       </c>
       <c r="L345" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="M345" t="n">
         <v>65</v>
@@ -17365,20 +17365,20 @@
         <v>0</v>
       </c>
       <c r="E346" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F346" t="n">
         <v>4</v>
       </c>
       <c r="G346" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H346" t="n">
+        <v>7</v>
+      </c>
+      <c r="I346" t="n">
         <v>5</v>
       </c>
-      <c r="I346" t="n">
-        <v>4</v>
-      </c>
       <c r="J346" t="n">
         <v>2</v>
       </c>
@@ -17386,7 +17386,7 @@
         <v>0</v>
       </c>
       <c r="L346" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="M346" t="n">
         <v>51</v>
@@ -17417,17 +17417,17 @@
         <v>2</v>
       </c>
       <c r="F347" t="n">
+        <v>5</v>
+      </c>
+      <c r="G347" t="n">
+        <v>3</v>
+      </c>
+      <c r="H347" t="n">
+        <v>1</v>
+      </c>
+      <c r="I347" t="n">
         <v>4</v>
       </c>
-      <c r="G347" t="n">
-        <v>2</v>
-      </c>
-      <c r="H347" t="n">
-        <v>1</v>
-      </c>
-      <c r="I347" t="n">
-        <v>3</v>
-      </c>
       <c r="J347" t="n">
         <v>1</v>
       </c>
@@ -17435,7 +17435,7 @@
         <v>0</v>
       </c>
       <c r="L347" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M347" t="n">
         <v>24</v>
@@ -17454,7 +17454,7 @@
         </is>
       </c>
       <c r="B348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C348" t="n">
         <v>1</v>
@@ -17466,16 +17466,16 @@
         <v>1</v>
       </c>
       <c r="F348" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G348" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H348" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J348" t="n">
         <v>3</v>
@@ -17484,7 +17484,7 @@
         <v>0</v>
       </c>
       <c r="L348" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M348" t="n">
         <v>47</v>
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="B349" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C349" t="n">
         <v>0</v>
@@ -17515,10 +17515,10 @@
         <v>0</v>
       </c>
       <c r="F349" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G349" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H349" t="n">
         <v>2</v>
@@ -17533,7 +17533,7 @@
         <v>0</v>
       </c>
       <c r="L349" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M349" t="n">
         <v>30</v>
@@ -17601,7 +17601,7 @@
         </is>
       </c>
       <c r="B351" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C351" t="n">
         <v>0</v>
@@ -17616,13 +17616,13 @@
         <v>2</v>
       </c>
       <c r="G351" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H351" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I351" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J351" t="n">
         <v>0</v>
@@ -17631,7 +17631,7 @@
         <v>1</v>
       </c>
       <c r="L351" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="M351" t="n">
         <v>46</v>
@@ -17650,7 +17650,7 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C352" t="n">
         <v>0</v>
@@ -17668,7 +17668,7 @@
         <v>13</v>
       </c>
       <c r="H352" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I352" t="n">
         <v>4</v>
@@ -17680,7 +17680,7 @@
         <v>0</v>
       </c>
       <c r="L352" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M352" t="n">
         <v>46</v>
@@ -17714,7 +17714,7 @@
         <v>1</v>
       </c>
       <c r="G353" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H353" t="n">
         <v>2</v>
@@ -17729,7 +17729,7 @@
         <v>1</v>
       </c>
       <c r="L353" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M353" t="n">
         <v>44</v>
@@ -17763,13 +17763,13 @@
         <v>2</v>
       </c>
       <c r="G354" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H354" t="n">
         <v>4</v>
       </c>
       <c r="I354" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J354" t="n">
         <v>1</v>
@@ -17778,7 +17778,7 @@
         <v>0</v>
       </c>
       <c r="L354" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M354" t="n">
         <v>41</v>
@@ -17788,6 +17788,202 @@
       </c>
       <c r="O354" t="n">
         <v>53</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>0</v>
+      </c>
+      <c r="C355" t="n">
+        <v>0</v>
+      </c>
+      <c r="D355" t="n">
+        <v>0</v>
+      </c>
+      <c r="E355" t="n">
+        <v>0</v>
+      </c>
+      <c r="F355" t="n">
+        <v>0</v>
+      </c>
+      <c r="G355" t="n">
+        <v>1</v>
+      </c>
+      <c r="H355" t="n">
+        <v>0</v>
+      </c>
+      <c r="I355" t="n">
+        <v>4</v>
+      </c>
+      <c r="J355" t="n">
+        <v>0</v>
+      </c>
+      <c r="K355" t="n">
+        <v>1</v>
+      </c>
+      <c r="L355" t="n">
+        <v>17</v>
+      </c>
+      <c r="M355" t="n">
+        <v>23</v>
+      </c>
+      <c r="N355" t="n">
+        <v>24</v>
+      </c>
+      <c r="O355" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>0</v>
+      </c>
+      <c r="C356" t="n">
+        <v>0</v>
+      </c>
+      <c r="D356" t="n">
+        <v>0</v>
+      </c>
+      <c r="E356" t="n">
+        <v>0</v>
+      </c>
+      <c r="F356" t="n">
+        <v>0</v>
+      </c>
+      <c r="G356" t="n">
+        <v>10</v>
+      </c>
+      <c r="H356" t="n">
+        <v>4</v>
+      </c>
+      <c r="I356" t="n">
+        <v>2</v>
+      </c>
+      <c r="J356" t="n">
+        <v>2</v>
+      </c>
+      <c r="K356" t="n">
+        <v>0</v>
+      </c>
+      <c r="L356" t="n">
+        <v>26</v>
+      </c>
+      <c r="M356" t="n">
+        <v>44</v>
+      </c>
+      <c r="N356" t="n">
+        <v>47</v>
+      </c>
+      <c r="O356" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>1</v>
+      </c>
+      <c r="C357" t="n">
+        <v>0</v>
+      </c>
+      <c r="D357" t="n">
+        <v>0</v>
+      </c>
+      <c r="E357" t="n">
+        <v>0</v>
+      </c>
+      <c r="F357" t="n">
+        <v>0</v>
+      </c>
+      <c r="G357" t="n">
+        <v>1</v>
+      </c>
+      <c r="H357" t="n">
+        <v>0</v>
+      </c>
+      <c r="I357" t="n">
+        <v>1</v>
+      </c>
+      <c r="J357" t="n">
+        <v>0</v>
+      </c>
+      <c r="K357" t="n">
+        <v>0</v>
+      </c>
+      <c r="L357" t="n">
+        <v>5</v>
+      </c>
+      <c r="M357" t="n">
+        <v>8</v>
+      </c>
+      <c r="N357" t="n">
+        <v>9</v>
+      </c>
+      <c r="O357" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>1</v>
+      </c>
+      <c r="C358" t="n">
+        <v>0</v>
+      </c>
+      <c r="D358" t="n">
+        <v>2</v>
+      </c>
+      <c r="E358" t="n">
+        <v>13</v>
+      </c>
+      <c r="F358" t="n">
+        <v>19</v>
+      </c>
+      <c r="G358" t="n">
+        <v>45</v>
+      </c>
+      <c r="H358" t="n">
+        <v>5</v>
+      </c>
+      <c r="I358" t="n">
+        <v>7</v>
+      </c>
+      <c r="J358" t="n">
+        <v>2</v>
+      </c>
+      <c r="K358" t="n">
+        <v>0</v>
+      </c>
+      <c r="L358" t="n">
+        <v>31</v>
+      </c>
+      <c r="M358" t="n">
+        <v>125</v>
+      </c>
+      <c r="N358" t="n">
+        <v>141</v>
+      </c>
+      <c r="O358" t="n">
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O358"/>
+  <dimension ref="A1:O359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17986,6 +17986,55 @@
         <v>150</v>
       </c>
     </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>4</v>
+      </c>
+      <c r="C359" t="n">
+        <v>1</v>
+      </c>
+      <c r="D359" t="n">
+        <v>5</v>
+      </c>
+      <c r="E359" t="n">
+        <v>5</v>
+      </c>
+      <c r="F359" t="n">
+        <v>8</v>
+      </c>
+      <c r="G359" t="n">
+        <v>33</v>
+      </c>
+      <c r="H359" t="n">
+        <v>4</v>
+      </c>
+      <c r="I359" t="n">
+        <v>7</v>
+      </c>
+      <c r="J359" t="n">
+        <v>1</v>
+      </c>
+      <c r="K359" t="n">
+        <v>0</v>
+      </c>
+      <c r="L359" t="n">
+        <v>24</v>
+      </c>
+      <c r="M359" t="n">
+        <v>92</v>
+      </c>
+      <c r="N359" t="n">
+        <v>100</v>
+      </c>
+      <c r="O359" t="n">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O359"/>
+  <dimension ref="A1:O360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C359" t="n">
         <v>1</v>
@@ -18023,7 +18023,7 @@
         <v>0</v>
       </c>
       <c r="L359" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M359" t="n">
         <v>92</v>
@@ -18033,6 +18033,55 @@
       </c>
       <c r="O359" t="n">
         <v>104</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>0</v>
+      </c>
+      <c r="C360" t="n">
+        <v>0</v>
+      </c>
+      <c r="D360" t="n">
+        <v>0</v>
+      </c>
+      <c r="E360" t="n">
+        <v>1</v>
+      </c>
+      <c r="F360" t="n">
+        <v>3</v>
+      </c>
+      <c r="G360" t="n">
+        <v>10</v>
+      </c>
+      <c r="H360" t="n">
+        <v>1</v>
+      </c>
+      <c r="I360" t="n">
+        <v>5</v>
+      </c>
+      <c r="J360" t="n">
+        <v>0</v>
+      </c>
+      <c r="K360" t="n">
+        <v>0</v>
+      </c>
+      <c r="L360" t="n">
+        <v>27</v>
+      </c>
+      <c r="M360" t="n">
+        <v>47</v>
+      </c>
+      <c r="N360" t="n">
+        <v>61</v>
+      </c>
+      <c r="O360" t="n">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -3109,10 +3109,10 @@
         <v>2</v>
       </c>
       <c r="F55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H55" t="n">
         <v>2</v>
@@ -7911,10 +7911,10 @@
         <v>4</v>
       </c>
       <c r="F153" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G153" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H153" t="n">
         <v>4</v>
@@ -7960,10 +7960,10 @@
         <v>10</v>
       </c>
       <c r="F154" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G154" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H154" t="n">
         <v>7</v>
@@ -8845,10 +8845,10 @@
         <v>12</v>
       </c>
       <c r="G172" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I172" t="n">
         <v>2</v>
@@ -11298,10 +11298,10 @@
         <v>18</v>
       </c>
       <c r="H222" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I222" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -12076,10 +12076,10 @@
         <v>25</v>
       </c>
       <c r="F238" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G238" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H238" t="n">
         <v>5</v>
@@ -12125,10 +12125,10 @@
         <v>0</v>
       </c>
       <c r="F239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -13497,10 +13497,10 @@
         <v>25</v>
       </c>
       <c r="F267" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G267" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H267" t="n">
         <v>6</v>
@@ -13549,10 +13549,10 @@
         <v>11</v>
       </c>
       <c r="G268" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H268" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I268" t="n">
         <v>2</v>
@@ -13690,13 +13690,13 @@
         <v>3</v>
       </c>
       <c r="E271" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F271" t="n">
         <v>11</v>
       </c>
       <c r="G271" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H271" t="n">
         <v>1</v>
@@ -13889,13 +13889,13 @@
         <v>26</v>
       </c>
       <c r="F275" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G275" t="n">
         <v>16</v>
       </c>
       <c r="H275" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I275" t="n">
         <v>2</v>
@@ -14526,10 +14526,10 @@
         <v>1</v>
       </c>
       <c r="F288" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G288" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H288" t="n">
         <v>8</v>
@@ -14918,10 +14918,10 @@
         <v>30</v>
       </c>
       <c r="F296" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G296" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H296" t="n">
         <v>3</v>
@@ -15754,10 +15754,10 @@
         <v>31</v>
       </c>
       <c r="G313" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H313" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I313" t="n">
         <v>12</v>
@@ -15800,10 +15800,10 @@
         <v>27</v>
       </c>
       <c r="F314" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G314" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H314" t="n">
         <v>9</v>
@@ -16593,10 +16593,10 @@
         <v>9</v>
       </c>
       <c r="I330" t="n">
+        <v>3</v>
+      </c>
+      <c r="J330" t="n">
         <v>4</v>
-      </c>
-      <c r="J330" t="n">
-        <v>3</v>
       </c>
       <c r="K330" t="n">
         <v>1</v>
@@ -16734,10 +16734,10 @@
         <v>2</v>
       </c>
       <c r="G333" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H333" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I333" t="n">
         <v>0</v>
@@ -16979,7 +16979,7 @@
         <v>3</v>
       </c>
       <c r="G338" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H338" t="n">
         <v>9</v>
@@ -16994,7 +16994,7 @@
         <v>1</v>
       </c>
       <c r="L338" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M338" t="n">
         <v>49</v>
@@ -17086,13 +17086,13 @@
         <v>0</v>
       </c>
       <c r="J340" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K340" t="n">
         <v>0</v>
       </c>
       <c r="L340" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M340" t="n">
         <v>12</v>
@@ -17273,10 +17273,10 @@
         <v>6</v>
       </c>
       <c r="G344" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H344" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I344" t="n">
         <v>6</v>
@@ -17714,22 +17714,22 @@
         <v>1</v>
       </c>
       <c r="G353" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H353" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I353" t="n">
         <v>3</v>
       </c>
       <c r="J353" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K353" t="n">
         <v>1</v>
       </c>
       <c r="L353" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M353" t="n">
         <v>44</v>
@@ -18008,13 +18008,13 @@
         <v>8</v>
       </c>
       <c r="G359" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H359" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I359" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J359" t="n">
         <v>1</v>
@@ -18023,7 +18023,7 @@
         <v>0</v>
       </c>
       <c r="L359" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M359" t="n">
         <v>92</v>
@@ -18054,25 +18054,25 @@
         <v>1</v>
       </c>
       <c r="F360" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G360" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H360" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I360" t="n">
         <v>5</v>
       </c>
       <c r="J360" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K360" t="n">
         <v>0</v>
       </c>
       <c r="L360" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="M360" t="n">
         <v>47</v>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O365"/>
+  <dimension ref="A1:O366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18106,7 +18106,7 @@
         <v>5</v>
       </c>
       <c r="G361" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H361" t="n">
         <v>2</v>
@@ -18121,16 +18121,16 @@
         <v>1</v>
       </c>
       <c r="L361" t="n">
+        <v>44</v>
+      </c>
+      <c r="M361" t="n">
+        <v>71</v>
+      </c>
+      <c r="N361" t="n">
         <v>81</v>
       </c>
-      <c r="M361" t="n">
-        <v>109</v>
-      </c>
-      <c r="N361" t="n">
-        <v>162</v>
-      </c>
       <c r="O361" t="n">
-        <v>184</v>
+        <v>92</v>
       </c>
     </row>
     <row r="362">
@@ -18170,16 +18170,16 @@
         <v>0</v>
       </c>
       <c r="L362" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M362" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N362" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="O362" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="363">
@@ -18219,16 +18219,16 @@
         <v>0</v>
       </c>
       <c r="L363" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M363" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N363" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="O363" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="364">
@@ -18253,7 +18253,7 @@
         <v>3</v>
       </c>
       <c r="G364" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H364" t="n">
         <v>4</v>
@@ -18268,16 +18268,16 @@
         <v>0</v>
       </c>
       <c r="L364" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="M364" t="n">
+        <v>51</v>
+      </c>
+      <c r="N364" t="n">
+        <v>52</v>
+      </c>
+      <c r="O364" t="n">
         <v>59</v>
-      </c>
-      <c r="N364" t="n">
-        <v>104</v>
-      </c>
-      <c r="O364" t="n">
-        <v>118</v>
       </c>
     </row>
     <row r="365">
@@ -18287,7 +18287,7 @@
         </is>
       </c>
       <c r="B365" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C365" t="n">
         <v>0</v>
@@ -18296,37 +18296,86 @@
         <v>0</v>
       </c>
       <c r="E365" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F365" t="n">
         <v>0</v>
       </c>
       <c r="G365" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H365" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I365" t="n">
         <v>0</v>
       </c>
       <c r="J365" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K365" t="n">
         <v>0</v>
       </c>
       <c r="L365" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M365" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="N365" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="O365" t="n">
-        <v>3</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>1</v>
+      </c>
+      <c r="C366" t="n">
+        <v>0</v>
+      </c>
+      <c r="D366" t="n">
+        <v>0</v>
+      </c>
+      <c r="E366" t="n">
+        <v>0</v>
+      </c>
+      <c r="F366" t="n">
+        <v>0</v>
+      </c>
+      <c r="G366" t="n">
+        <v>0</v>
+      </c>
+      <c r="H366" t="n">
+        <v>0</v>
+      </c>
+      <c r="I366" t="n">
+        <v>0</v>
+      </c>
+      <c r="J366" t="n">
+        <v>0</v>
+      </c>
+      <c r="K366" t="n">
+        <v>0</v>
+      </c>
+      <c r="L366" t="n">
+        <v>0</v>
+      </c>
+      <c r="M366" t="n">
+        <v>1</v>
+      </c>
+      <c r="N366" t="n">
+        <v>1</v>
+      </c>
+      <c r="O366" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -16621,10 +16621,10 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C331" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D331" t="n">
         <v>8</v>
@@ -16633,7 +16633,7 @@
         <v>12</v>
       </c>
       <c r="F331" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G331" t="n">
         <v>7</v>
@@ -16651,16 +16651,16 @@
         <v>0</v>
       </c>
       <c r="L331" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M331" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="N331" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="O331" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="332">
@@ -16682,10 +16682,10 @@
         <v>3</v>
       </c>
       <c r="F332" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G332" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H332" t="n">
         <v>4</v>
@@ -18023,16 +18023,16 @@
         <v>0</v>
       </c>
       <c r="L359" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M359" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N359" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O359" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="360">
@@ -18342,40 +18342,40 @@
         <v>0</v>
       </c>
       <c r="D366" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E366" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F366" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G366" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H366" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I366" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J366" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K366" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L366" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M366" t="n">
-        <v>1</v>
+        <v>82</v>
       </c>
       <c r="N366" t="n">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="O366" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O366"/>
+  <dimension ref="A1:O367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3795,7 +3795,7 @@
         <v>3</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G69" t="n">
         <v>1</v>
@@ -3813,7 +3813,7 @@
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M69" t="n">
         <v>37</v>
@@ -4533,7 +4533,7 @@
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -4548,7 +4548,7 @@
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
         <v>25</v>
@@ -9075,7 +9075,7 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C177" t="n">
         <v>6</v>
@@ -9105,7 +9105,7 @@
         <v>0</v>
       </c>
       <c r="L177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M177" t="n">
         <v>71</v>
@@ -9770,7 +9770,7 @@
         <v>13</v>
       </c>
       <c r="E191" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F191" t="n">
         <v>12</v>
@@ -9791,7 +9791,7 @@
         <v>0</v>
       </c>
       <c r="L191" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M191" t="n">
         <v>118</v>
@@ -9874,7 +9874,7 @@
         <v>11</v>
       </c>
       <c r="G193" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H193" t="n">
         <v>2</v>
@@ -9889,7 +9889,7 @@
         <v>2</v>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M193" t="n">
         <v>82</v>
@@ -10006,25 +10006,25 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C196" t="n">
         <v>8</v>
       </c>
       <c r="D196" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E196" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F196" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G196" t="n">
         <v>17</v>
       </c>
       <c r="H196" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I196" t="n">
         <v>4</v>
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="L196" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M196" t="n">
         <v>103</v>
@@ -10055,7 +10055,7 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C197" t="n">
         <v>5</v>
@@ -10085,7 +10085,7 @@
         <v>1</v>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M197" t="n">
         <v>63</v>
@@ -10104,7 +10104,7 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C198" t="n">
         <v>9</v>
@@ -10119,7 +10119,7 @@
         <v>8</v>
       </c>
       <c r="G198" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H198" t="n">
         <v>1</v>
@@ -10134,7 +10134,7 @@
         <v>0</v>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M198" t="n">
         <v>62</v>
@@ -10162,13 +10162,13 @@
         <v>9</v>
       </c>
       <c r="E199" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F199" t="n">
         <v>3</v>
       </c>
       <c r="G199" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H199" t="n">
         <v>1</v>
@@ -10183,7 +10183,7 @@
         <v>0</v>
       </c>
       <c r="L199" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M199" t="n">
         <v>58</v>
@@ -10214,7 +10214,7 @@
         <v>11</v>
       </c>
       <c r="F200" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G200" t="n">
         <v>3</v>
@@ -10232,7 +10232,7 @@
         <v>0</v>
       </c>
       <c r="L200" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M200" t="n">
         <v>44</v>
@@ -10300,16 +10300,16 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C202" t="n">
         <v>8</v>
       </c>
       <c r="D202" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E202" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F202" t="n">
         <v>25</v>
@@ -10318,10 +10318,10 @@
         <v>36</v>
       </c>
       <c r="H202" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I202" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J202" t="n">
         <v>6</v>
@@ -10330,10 +10330,10 @@
         <v>3</v>
       </c>
       <c r="L202" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M202" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="N202" t="n">
         <v>182</v>
@@ -10398,7 +10398,7 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C204" t="n">
         <v>10</v>
@@ -10422,16 +10422,16 @@
         <v>4</v>
       </c>
       <c r="J204" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K204" t="n">
         <v>0</v>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M204" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N204" t="n">
         <v>105</v>
@@ -10508,7 +10508,7 @@
         <v>1</v>
       </c>
       <c r="F206" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G206" t="n">
         <v>8</v>
@@ -10526,7 +10526,7 @@
         <v>2</v>
       </c>
       <c r="L206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M206" t="n">
         <v>25</v>
@@ -10664,7 +10664,7 @@
         <v>2</v>
       </c>
       <c r="I209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -10673,7 +10673,7 @@
         <v>0</v>
       </c>
       <c r="L209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M209" t="n">
         <v>15</v>
@@ -10805,7 +10805,7 @@
         <v>4</v>
       </c>
       <c r="G212" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -10820,7 +10820,7 @@
         <v>0</v>
       </c>
       <c r="L212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M212" t="n">
         <v>20</v>
@@ -10848,7 +10848,7 @@
         <v>2</v>
       </c>
       <c r="E213" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F213" t="n">
         <v>3</v>
@@ -10869,7 +10869,7 @@
         <v>0</v>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M213" t="n">
         <v>17</v>
@@ -11007,7 +11007,7 @@
         <v>3</v>
       </c>
       <c r="I216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J216" t="n">
         <v>2</v>
@@ -11016,7 +11016,7 @@
         <v>1</v>
       </c>
       <c r="L216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M216" t="n">
         <v>27</v>
@@ -11093,10 +11093,10 @@
         <v>2</v>
       </c>
       <c r="E218" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F218" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G218" t="n">
         <v>13</v>
@@ -11114,7 +11114,7 @@
         <v>0</v>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M218" t="n">
         <v>53</v>
@@ -11142,7 +11142,7 @@
         <v>2</v>
       </c>
       <c r="E219" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F219" t="n">
         <v>7</v>
@@ -11163,7 +11163,7 @@
         <v>1</v>
       </c>
       <c r="L219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M219" t="n">
         <v>33</v>
@@ -11295,7 +11295,7 @@
         <v>5</v>
       </c>
       <c r="G222" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H222" t="n">
         <v>7</v>
@@ -11310,7 +11310,7 @@
         <v>1</v>
       </c>
       <c r="L222" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M222" t="n">
         <v>59</v>
@@ -11338,10 +11338,10 @@
         <v>1</v>
       </c>
       <c r="E223" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F223" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G223" t="n">
         <v>8</v>
@@ -11359,7 +11359,7 @@
         <v>0</v>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M223" t="n">
         <v>29</v>
@@ -11402,13 +11402,13 @@
         <v>2</v>
       </c>
       <c r="J224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K224" t="n">
         <v>1</v>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M224" t="n">
         <v>25</v>
@@ -11482,7 +11482,7 @@
         <v>3</v>
       </c>
       <c r="D226" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E226" t="n">
         <v>7</v>
@@ -11506,7 +11506,7 @@
         <v>0</v>
       </c>
       <c r="L226" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M226" t="n">
         <v>23</v>
@@ -11595,7 +11595,7 @@
         <v>6</v>
       </c>
       <c r="I228" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -11607,7 +11607,7 @@
         <v>0</v>
       </c>
       <c r="M228" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N228" t="n">
         <v>47</v>
@@ -11681,7 +11681,7 @@
         <v>0</v>
       </c>
       <c r="E230" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F230" t="n">
         <v>4</v>
@@ -11702,7 +11702,7 @@
         <v>0</v>
       </c>
       <c r="L230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M230" t="n">
         <v>38</v>
@@ -11733,7 +11733,7 @@
         <v>6</v>
       </c>
       <c r="F231" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G231" t="n">
         <v>30</v>
@@ -11751,7 +11751,7 @@
         <v>1</v>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M231" t="n">
         <v>65</v>
@@ -11825,13 +11825,13 @@
         <v>1</v>
       </c>
       <c r="D233" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E233" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F233" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G233" t="n">
         <v>38</v>
@@ -11849,7 +11849,7 @@
         <v>0</v>
       </c>
       <c r="L233" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M233" t="n">
         <v>86</v>
@@ -11880,7 +11880,7 @@
         <v>8</v>
       </c>
       <c r="F234" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G234" t="n">
         <v>7</v>
@@ -11898,7 +11898,7 @@
         <v>1</v>
       </c>
       <c r="L234" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M234" t="n">
         <v>50</v>
@@ -11972,16 +11972,16 @@
         <v>4</v>
       </c>
       <c r="D236" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E236" t="n">
         <v>37</v>
       </c>
       <c r="F236" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G236" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H236" t="n">
         <v>14</v>
@@ -11996,7 +11996,7 @@
         <v>0</v>
       </c>
       <c r="L236" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M236" t="n">
         <v>187</v>
@@ -12015,10 +12015,10 @@
         </is>
       </c>
       <c r="B237" t="n">
+        <v>5</v>
+      </c>
+      <c r="C237" t="n">
         <v>6</v>
-      </c>
-      <c r="C237" t="n">
-        <v>7</v>
       </c>
       <c r="D237" t="n">
         <v>6</v>
@@ -12027,7 +12027,7 @@
         <v>16</v>
       </c>
       <c r="F237" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G237" t="n">
         <v>30</v>
@@ -12045,10 +12045,10 @@
         <v>0</v>
       </c>
       <c r="L237" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M237" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N237" t="n">
         <v>94</v>
@@ -12067,10 +12067,10 @@
         <v>8</v>
       </c>
       <c r="C238" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D238" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E238" t="n">
         <v>25</v>
@@ -12094,7 +12094,7 @@
         <v>0</v>
       </c>
       <c r="L238" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M238" t="n">
         <v>120</v>
@@ -12171,10 +12171,10 @@
         <v>13</v>
       </c>
       <c r="E240" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F240" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G240" t="n">
         <v>65</v>
@@ -12183,16 +12183,16 @@
         <v>8</v>
       </c>
       <c r="I240" t="n">
+        <v>5</v>
+      </c>
+      <c r="J240" t="n">
+        <v>0</v>
+      </c>
+      <c r="K240" t="n">
+        <v>2</v>
+      </c>
+      <c r="L240" t="n">
         <v>6</v>
-      </c>
-      <c r="J240" t="n">
-        <v>0</v>
-      </c>
-      <c r="K240" t="n">
-        <v>2</v>
-      </c>
-      <c r="L240" t="n">
-        <v>1</v>
       </c>
       <c r="M240" t="n">
         <v>149</v>
@@ -12220,13 +12220,13 @@
         <v>9</v>
       </c>
       <c r="E241" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F241" t="n">
         <v>14</v>
       </c>
       <c r="G241" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -12241,7 +12241,7 @@
         <v>0</v>
       </c>
       <c r="L241" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M241" t="n">
         <v>65</v>
@@ -12263,16 +12263,16 @@
         <v>1</v>
       </c>
       <c r="C242" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D242" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E242" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F242" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G242" t="n">
         <v>20</v>
@@ -12290,7 +12290,7 @@
         <v>1</v>
       </c>
       <c r="L242" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M242" t="n">
         <v>71</v>
@@ -12456,16 +12456,16 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C246" t="n">
         <v>4</v>
       </c>
       <c r="D246" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E246" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F246" t="n">
         <v>22</v>
@@ -12477,7 +12477,7 @@
         <v>11</v>
       </c>
       <c r="I246" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J246" t="n">
         <v>3</v>
@@ -12486,7 +12486,7 @@
         <v>1</v>
       </c>
       <c r="L246" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M246" t="n">
         <v>175</v>
@@ -12505,13 +12505,13 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C247" t="n">
         <v>1</v>
       </c>
       <c r="D247" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E247" t="n">
         <v>4</v>
@@ -12615,7 +12615,7 @@
         <v>10</v>
       </c>
       <c r="F249" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G249" t="n">
         <v>26</v>
@@ -12633,7 +12633,7 @@
         <v>1</v>
       </c>
       <c r="L249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M249" t="n">
         <v>59</v>
@@ -12652,7 +12652,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C250" t="n">
         <v>0</v>
@@ -12661,7 +12661,7 @@
         <v>0</v>
       </c>
       <c r="E250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F250" t="n">
         <v>3</v>
@@ -12682,7 +12682,7 @@
         <v>1</v>
       </c>
       <c r="L250" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M250" t="n">
         <v>38</v>
@@ -12869,16 +12869,16 @@
         <v>12</v>
       </c>
       <c r="I254" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J254" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K254" t="n">
         <v>1</v>
       </c>
       <c r="L254" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M254" t="n">
         <v>50</v>
@@ -12897,16 +12897,16 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D255" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E255" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F255" t="n">
         <v>20</v>
@@ -12927,7 +12927,7 @@
         <v>1</v>
       </c>
       <c r="L255" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M255" t="n">
         <v>144</v>
@@ -12946,16 +12946,16 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C256" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D256" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E256" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F256" t="n">
         <v>17</v>
@@ -12976,7 +12976,7 @@
         <v>1</v>
       </c>
       <c r="L256" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M256" t="n">
         <v>222</v>
@@ -13142,22 +13142,22 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C260" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D260" t="n">
         <v>27</v>
       </c>
       <c r="E260" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F260" t="n">
         <v>29</v>
       </c>
       <c r="G260" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H260" t="n">
         <v>18</v>
@@ -13172,10 +13172,10 @@
         <v>3</v>
       </c>
       <c r="L260" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="M260" t="n">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="N260" t="n">
         <v>295</v>
@@ -13191,25 +13191,25 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>800</v>
+        <v>766</v>
       </c>
       <c r="C261" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D261" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E261" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F261" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G261" t="n">
         <v>45</v>
       </c>
       <c r="H261" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I261" t="n">
         <v>3</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="L261" t="n">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="M261" t="n">
-        <v>1164</v>
+        <v>1160</v>
       </c>
       <c r="N261" t="n">
         <v>1170</v>
@@ -13240,19 +13240,19 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C262" t="n">
         <v>18</v>
       </c>
       <c r="D262" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E262" t="n">
         <v>13</v>
       </c>
       <c r="F262" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G262" t="n">
         <v>15</v>
@@ -13261,7 +13261,7 @@
         <v>1</v>
       </c>
       <c r="I262" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -13270,7 +13270,7 @@
         <v>1</v>
       </c>
       <c r="L262" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M262" t="n">
         <v>157</v>
@@ -13289,7 +13289,7 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C263" t="n">
         <v>12</v>
@@ -13298,7 +13298,7 @@
         <v>19</v>
       </c>
       <c r="E263" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F263" t="n">
         <v>11</v>
@@ -13319,10 +13319,10 @@
         <v>0</v>
       </c>
       <c r="L263" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M263" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="N263" t="n">
         <v>173</v>
@@ -13338,7 +13338,7 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C264" t="n">
         <v>13</v>
@@ -13347,7 +13347,7 @@
         <v>13</v>
       </c>
       <c r="E264" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F264" t="n">
         <v>8</v>
@@ -13368,10 +13368,10 @@
         <v>1</v>
       </c>
       <c r="L264" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M264" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N264" t="n">
         <v>191</v>
@@ -13387,16 +13387,16 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C265" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D265" t="n">
         <v>25</v>
       </c>
       <c r="E265" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F265" t="n">
         <v>18</v>
@@ -13417,7 +13417,7 @@
         <v>0</v>
       </c>
       <c r="L265" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M265" t="n">
         <v>268</v>
@@ -13494,13 +13494,13 @@
         <v>7</v>
       </c>
       <c r="E267" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F267" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G267" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H267" t="n">
         <v>6</v>
@@ -13515,7 +13515,7 @@
         <v>0</v>
       </c>
       <c r="L267" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M267" t="n">
         <v>131</v>
@@ -13534,7 +13534,7 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C268" t="n">
         <v>1</v>
@@ -13564,7 +13564,7 @@
         <v>1</v>
       </c>
       <c r="L268" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M268" t="n">
         <v>66</v>
@@ -13696,7 +13696,7 @@
         <v>11</v>
       </c>
       <c r="G271" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H271" t="n">
         <v>1</v>
@@ -13711,7 +13711,7 @@
         <v>0</v>
       </c>
       <c r="L271" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M271" t="n">
         <v>49</v>
@@ -13779,7 +13779,7 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C273" t="n">
         <v>0</v>
@@ -13809,7 +13809,7 @@
         <v>0</v>
       </c>
       <c r="L273" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M273" t="n">
         <v>29</v>
@@ -13828,7 +13828,7 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C274" t="n">
         <v>6</v>
@@ -13840,13 +13840,13 @@
         <v>14</v>
       </c>
       <c r="F274" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G274" t="n">
         <v>29</v>
       </c>
       <c r="H274" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I274" t="n">
         <v>4</v>
@@ -13877,19 +13877,19 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C275" t="n">
         <v>12</v>
       </c>
       <c r="D275" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E275" t="n">
         <v>26</v>
       </c>
       <c r="F275" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G275" t="n">
         <v>16</v>
@@ -13907,10 +13907,10 @@
         <v>1</v>
       </c>
       <c r="L275" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M275" t="n">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="N275" t="n">
         <v>271</v>
@@ -13926,7 +13926,7 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C276" t="n">
         <v>5</v>
@@ -13935,19 +13935,19 @@
         <v>10</v>
       </c>
       <c r="E276" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F276" t="n">
         <v>10</v>
       </c>
       <c r="G276" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H276" t="n">
         <v>4</v>
       </c>
       <c r="I276" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J276" t="n">
         <v>1</v>
@@ -13956,7 +13956,7 @@
         <v>0</v>
       </c>
       <c r="L276" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M276" t="n">
         <v>85</v>
@@ -13990,7 +13990,7 @@
         <v>8</v>
       </c>
       <c r="G277" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H277" t="n">
         <v>2</v>
@@ -14005,7 +14005,7 @@
         <v>0</v>
       </c>
       <c r="L277" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M277" t="n">
         <v>100</v>
@@ -14054,10 +14054,10 @@
         <v>0</v>
       </c>
       <c r="L278" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M278" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N278" t="n">
         <v>93</v>
@@ -14122,7 +14122,7 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C280" t="n">
         <v>2</v>
@@ -14131,7 +14131,7 @@
         <v>8</v>
       </c>
       <c r="E280" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F280" t="n">
         <v>3</v>
@@ -14143,7 +14143,7 @@
         <v>3</v>
       </c>
       <c r="I280" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J280" t="n">
         <v>4</v>
@@ -14152,10 +14152,10 @@
         <v>0</v>
       </c>
       <c r="L280" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M280" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N280" t="n">
         <v>143</v>
@@ -14171,7 +14171,7 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C281" t="n">
         <v>12</v>
@@ -14180,7 +14180,7 @@
         <v>19</v>
       </c>
       <c r="E281" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F281" t="n">
         <v>16</v>
@@ -14192,7 +14192,7 @@
         <v>1</v>
       </c>
       <c r="I281" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J281" t="n">
         <v>1</v>
@@ -14201,7 +14201,7 @@
         <v>2</v>
       </c>
       <c r="L281" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M281" t="n">
         <v>155</v>
@@ -14223,22 +14223,22 @@
         <v>8</v>
       </c>
       <c r="C282" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D282" t="n">
         <v>10</v>
       </c>
       <c r="E282" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F282" t="n">
         <v>7</v>
       </c>
       <c r="G282" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H282" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I282" t="n">
         <v>0</v>
@@ -14250,10 +14250,10 @@
         <v>0</v>
       </c>
       <c r="L282" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M282" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N282" t="n">
         <v>101</v>
@@ -14278,7 +14278,7 @@
         <v>7</v>
       </c>
       <c r="E283" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F283" t="n">
         <v>6</v>
@@ -14299,7 +14299,7 @@
         <v>0</v>
       </c>
       <c r="L283" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M283" t="n">
         <v>102</v>
@@ -14324,7 +14324,7 @@
         <v>0</v>
       </c>
       <c r="D284" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E284" t="n">
         <v>22</v>
@@ -14348,7 +14348,7 @@
         <v>1</v>
       </c>
       <c r="L284" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M284" t="n">
         <v>94</v>
@@ -14416,37 +14416,37 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C286" t="n">
         <v>13</v>
       </c>
       <c r="D286" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E286" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F286" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G286" t="n">
         <v>12</v>
       </c>
       <c r="H286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I286" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J286" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K286" t="n">
         <v>1</v>
       </c>
       <c r="L286" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="M286" t="n">
         <v>291</v>
@@ -14465,7 +14465,7 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C287" t="n">
         <v>0</v>
@@ -14495,7 +14495,7 @@
         <v>1</v>
       </c>
       <c r="L287" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M287" t="n">
         <v>25</v>
@@ -14563,7 +14563,7 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C289" t="n">
         <v>1</v>
@@ -14575,13 +14575,13 @@
         <v>11</v>
       </c>
       <c r="F289" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G289" t="n">
         <v>35</v>
       </c>
       <c r="H289" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I289" t="n">
         <v>3</v>
@@ -14593,7 +14593,7 @@
         <v>1</v>
       </c>
       <c r="L289" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M289" t="n">
         <v>100</v>
@@ -14612,16 +14612,16 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="C290" t="n">
         <v>11</v>
       </c>
       <c r="D290" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E290" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F290" t="n">
         <v>8</v>
@@ -14642,7 +14642,7 @@
         <v>1</v>
       </c>
       <c r="L290" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="M290" t="n">
         <v>302</v>
@@ -14661,22 +14661,22 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C291" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D291" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E291" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F291" t="n">
         <v>11</v>
       </c>
       <c r="G291" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H291" t="n">
         <v>2</v>
@@ -14691,7 +14691,7 @@
         <v>1</v>
       </c>
       <c r="L291" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M291" t="n">
         <v>122</v>
@@ -14863,22 +14863,22 @@
         <v>1</v>
       </c>
       <c r="D295" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E295" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F295" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G295" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H295" t="n">
+        <v>7</v>
+      </c>
+      <c r="I295" t="n">
         <v>6</v>
-      </c>
-      <c r="I295" t="n">
-        <v>5</v>
       </c>
       <c r="J295" t="n">
         <v>1</v>
@@ -14906,22 +14906,22 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D296" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E296" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F296" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G296" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H296" t="n">
         <v>3</v>
@@ -14936,7 +14936,7 @@
         <v>0</v>
       </c>
       <c r="L296" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="M296" t="n">
         <v>122</v>
@@ -14964,16 +14964,16 @@
         <v>0</v>
       </c>
       <c r="E297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F297" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G297" t="n">
         <v>9</v>
       </c>
       <c r="H297" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I297" t="n">
         <v>3</v>
@@ -14985,7 +14985,7 @@
         <v>1</v>
       </c>
       <c r="L297" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M297" t="n">
         <v>46</v>
@@ -15200,7 +15200,7 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C302" t="n">
         <v>0</v>
@@ -15218,7 +15218,7 @@
         <v>0</v>
       </c>
       <c r="H302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I302" t="n">
         <v>0</v>
@@ -15230,7 +15230,7 @@
         <v>0</v>
       </c>
       <c r="L302" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M302" t="n">
         <v>25</v>
@@ -15258,10 +15258,10 @@
         <v>0</v>
       </c>
       <c r="E303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F303" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G303" t="n">
         <v>87</v>
@@ -15279,7 +15279,7 @@
         <v>5</v>
       </c>
       <c r="L303" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M303" t="n">
         <v>158</v>
@@ -15362,13 +15362,13 @@
         <v>5</v>
       </c>
       <c r="G305" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H305" t="n">
         <v>7</v>
       </c>
       <c r="I305" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J305" t="n">
         <v>3</v>
@@ -15396,7 +15396,7 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C306" t="n">
         <v>3</v>
@@ -15405,13 +15405,13 @@
         <v>4</v>
       </c>
       <c r="E306" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F306" t="n">
         <v>12</v>
       </c>
       <c r="G306" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H306" t="n">
         <v>5</v>
@@ -15426,7 +15426,7 @@
         <v>2</v>
       </c>
       <c r="L306" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M306" t="n">
         <v>78</v>
@@ -15445,7 +15445,7 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C307" t="n">
         <v>0</v>
@@ -15475,7 +15475,7 @@
         <v>0</v>
       </c>
       <c r="L307" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M307" t="n">
         <v>13</v>
@@ -15543,7 +15543,7 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C309" t="n">
         <v>0</v>
@@ -15573,7 +15573,7 @@
         <v>1</v>
       </c>
       <c r="L309" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M309" t="n">
         <v>78</v>
@@ -15647,7 +15647,7 @@
         <v>1</v>
       </c>
       <c r="D311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E311" t="n">
         <v>1</v>
@@ -15671,7 +15671,7 @@
         <v>1</v>
       </c>
       <c r="L311" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M311" t="n">
         <v>36</v>
@@ -15739,7 +15739,7 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C313" t="n">
         <v>3</v>
@@ -15751,13 +15751,13 @@
         <v>34</v>
       </c>
       <c r="F313" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G313" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H313" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I313" t="n">
         <v>12</v>
@@ -15769,7 +15769,7 @@
         <v>1</v>
       </c>
       <c r="L313" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M313" t="n">
         <v>232</v>
@@ -15791,19 +15791,19 @@
         <v>12</v>
       </c>
       <c r="C314" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D314" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E314" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F314" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G314" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H314" t="n">
         <v>9</v>
@@ -15818,7 +15818,7 @@
         <v>0</v>
       </c>
       <c r="L314" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M314" t="n">
         <v>210</v>
@@ -15886,22 +15886,22 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C316" t="n">
         <v>2</v>
       </c>
       <c r="D316" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E316" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F316" t="n">
         <v>13</v>
       </c>
       <c r="G316" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H316" t="n">
         <v>5</v>
@@ -15916,7 +15916,7 @@
         <v>0</v>
       </c>
       <c r="L316" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M316" t="n">
         <v>59</v>
@@ -15947,10 +15947,10 @@
         <v>12</v>
       </c>
       <c r="F317" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G317" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H317" t="n">
         <v>9</v>
@@ -15965,7 +15965,7 @@
         <v>0</v>
       </c>
       <c r="L317" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M317" t="n">
         <v>82</v>
@@ -15990,16 +15990,16 @@
         <v>4</v>
       </c>
       <c r="D318" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E318" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F318" t="n">
         <v>9</v>
       </c>
       <c r="G318" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H318" t="n">
         <v>6</v>
@@ -16014,7 +16014,7 @@
         <v>0</v>
       </c>
       <c r="L318" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M318" t="n">
         <v>91</v>
@@ -16082,10 +16082,10 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C320" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D320" t="n">
         <v>2</v>
@@ -16161,10 +16161,10 @@
         <v>2</v>
       </c>
       <c r="L321" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M321" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N321" t="n">
         <v>39</v>
@@ -16189,7 +16189,7 @@
         <v>0</v>
       </c>
       <c r="E322" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F322" t="n">
         <v>1</v>
@@ -16210,7 +16210,7 @@
         <v>0</v>
       </c>
       <c r="L322" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M322" t="n">
         <v>16</v>
@@ -16327,7 +16327,7 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C325" t="n">
         <v>0</v>
@@ -16348,7 +16348,7 @@
         <v>1</v>
       </c>
       <c r="I325" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J325" t="n">
         <v>0</v>
@@ -16357,7 +16357,7 @@
         <v>1</v>
       </c>
       <c r="L325" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M325" t="n">
         <v>20</v>
@@ -16455,16 +16455,16 @@
         <v>0</v>
       </c>
       <c r="L327" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M327" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N327" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O327" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="328">
@@ -16474,7 +16474,7 @@
         </is>
       </c>
       <c r="B328" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C328" t="n">
         <v>0</v>
@@ -16504,7 +16504,7 @@
         <v>4</v>
       </c>
       <c r="L328" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M328" t="n">
         <v>18</v>
@@ -16587,10 +16587,10 @@
         <v>1</v>
       </c>
       <c r="G330" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H330" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I330" t="n">
         <v>3</v>
@@ -16602,16 +16602,16 @@
         <v>1</v>
       </c>
       <c r="L330" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M330" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N330" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O330" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="331">
@@ -16633,7 +16633,7 @@
         <v>12</v>
       </c>
       <c r="F331" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G331" t="n">
         <v>7</v>
@@ -16651,7 +16651,7 @@
         <v>0</v>
       </c>
       <c r="L331" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M331" t="n">
         <v>118</v>
@@ -16670,7 +16670,7 @@
         </is>
       </c>
       <c r="B332" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C332" t="n">
         <v>0</v>
@@ -16700,7 +16700,7 @@
         <v>0</v>
       </c>
       <c r="L332" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M332" t="n">
         <v>45</v>
@@ -16725,7 +16725,7 @@
         <v>0</v>
       </c>
       <c r="D333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E333" t="n">
         <v>0</v>
@@ -16734,7 +16734,7 @@
         <v>2</v>
       </c>
       <c r="G333" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H333" t="n">
         <v>1</v>
@@ -16749,7 +16749,7 @@
         <v>0</v>
       </c>
       <c r="L333" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M333" t="n">
         <v>23</v>
@@ -17518,10 +17518,10 @@
         <v>2</v>
       </c>
       <c r="G349" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H349" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I349" t="n">
         <v>3</v>
@@ -17533,7 +17533,7 @@
         <v>0</v>
       </c>
       <c r="L349" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M349" t="n">
         <v>30</v>
@@ -17959,7 +17959,7 @@
         <v>21</v>
       </c>
       <c r="G358" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H358" t="n">
         <v>6</v>
@@ -17974,7 +17974,7 @@
         <v>0</v>
       </c>
       <c r="L358" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M358" t="n">
         <v>125</v>
@@ -18097,16 +18097,16 @@
         <v>1</v>
       </c>
       <c r="D361" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E361" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F361" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G361" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H361" t="n">
         <v>2</v>
@@ -18121,7 +18121,7 @@
         <v>1</v>
       </c>
       <c r="L361" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="M361" t="n">
         <v>71</v>
@@ -18140,7 +18140,7 @@
         </is>
       </c>
       <c r="B362" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C362" t="n">
         <v>0</v>
@@ -18170,7 +18170,7 @@
         <v>0</v>
       </c>
       <c r="L362" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M362" t="n">
         <v>12</v>
@@ -18250,13 +18250,13 @@
         <v>2</v>
       </c>
       <c r="F364" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G364" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H364" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I364" t="n">
         <v>6</v>
@@ -18268,7 +18268,7 @@
         <v>0</v>
       </c>
       <c r="L364" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="M364" t="n">
         <v>51</v>
@@ -18345,16 +18345,16 @@
         <v>2</v>
       </c>
       <c r="E366" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F366" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G366" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="H366" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I366" t="n">
         <v>3</v>
@@ -18366,7 +18366,7 @@
         <v>1</v>
       </c>
       <c r="L366" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="M366" t="n">
         <v>82</v>
@@ -18376,6 +18376,55 @@
       </c>
       <c r="O366" t="n">
         <v>102</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>0</v>
+      </c>
+      <c r="C367" t="n">
+        <v>0</v>
+      </c>
+      <c r="D367" t="n">
+        <v>0</v>
+      </c>
+      <c r="E367" t="n">
+        <v>0</v>
+      </c>
+      <c r="F367" t="n">
+        <v>0</v>
+      </c>
+      <c r="G367" t="n">
+        <v>0</v>
+      </c>
+      <c r="H367" t="n">
+        <v>0</v>
+      </c>
+      <c r="I367" t="n">
+        <v>0</v>
+      </c>
+      <c r="J367" t="n">
+        <v>0</v>
+      </c>
+      <c r="K367" t="n">
+        <v>1</v>
+      </c>
+      <c r="L367" t="n">
+        <v>0</v>
+      </c>
+      <c r="M367" t="n">
+        <v>1</v>
+      </c>
+      <c r="N367" t="n">
+        <v>1</v>
+      </c>
+      <c r="O367" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -9874,7 +9874,7 @@
         <v>11</v>
       </c>
       <c r="G193" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H193" t="n">
         <v>2</v>
@@ -9889,7 +9889,7 @@
         <v>2</v>
       </c>
       <c r="L193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M193" t="n">
         <v>82</v>
@@ -10006,25 +10006,25 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C196" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D196" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E196" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F196" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G196" t="n">
         <v>17</v>
       </c>
       <c r="H196" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I196" t="n">
         <v>4</v>
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="L196" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
         <v>103</v>
@@ -10055,7 +10055,7 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C197" t="n">
         <v>5</v>
@@ -10085,7 +10085,7 @@
         <v>1</v>
       </c>
       <c r="L197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M197" t="n">
         <v>63</v>
@@ -10104,7 +10104,7 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C198" t="n">
         <v>9</v>
@@ -10119,7 +10119,7 @@
         <v>8</v>
       </c>
       <c r="G198" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H198" t="n">
         <v>1</v>
@@ -10134,7 +10134,7 @@
         <v>0</v>
       </c>
       <c r="L198" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M198" t="n">
         <v>62</v>
@@ -10162,14 +10162,14 @@
         <v>9</v>
       </c>
       <c r="E199" t="n">
+        <v>13</v>
+      </c>
+      <c r="F199" t="n">
+        <v>3</v>
+      </c>
+      <c r="G199" t="n">
         <v>11</v>
       </c>
-      <c r="F199" t="n">
-        <v>3</v>
-      </c>
-      <c r="G199" t="n">
-        <v>10</v>
-      </c>
       <c r="H199" t="n">
         <v>1</v>
       </c>
@@ -10183,7 +10183,7 @@
         <v>0</v>
       </c>
       <c r="L199" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M199" t="n">
         <v>58</v>
@@ -10214,7 +10214,7 @@
         <v>11</v>
       </c>
       <c r="F200" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G200" t="n">
         <v>3</v>
@@ -10232,7 +10232,7 @@
         <v>0</v>
       </c>
       <c r="L200" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M200" t="n">
         <v>44</v>
@@ -10300,16 +10300,16 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C202" t="n">
         <v>8</v>
       </c>
       <c r="D202" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E202" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F202" t="n">
         <v>25</v>
@@ -10318,10 +10318,10 @@
         <v>36</v>
       </c>
       <c r="H202" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I202" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J202" t="n">
         <v>6</v>
@@ -10330,7 +10330,7 @@
         <v>3</v>
       </c>
       <c r="L202" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M202" t="n">
         <v>181</v>
@@ -10422,13 +10422,13 @@
         <v>4</v>
       </c>
       <c r="J204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K204" t="n">
         <v>0</v>
       </c>
       <c r="L204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M204" t="n">
         <v>103</v>
@@ -10508,7 +10508,7 @@
         <v>1</v>
       </c>
       <c r="F206" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G206" t="n">
         <v>8</v>
@@ -10526,7 +10526,7 @@
         <v>2</v>
       </c>
       <c r="L206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M206" t="n">
         <v>25</v>
@@ -10664,7 +10664,7 @@
         <v>2</v>
       </c>
       <c r="I209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -10673,7 +10673,7 @@
         <v>0</v>
       </c>
       <c r="L209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M209" t="n">
         <v>15</v>
@@ -10805,7 +10805,7 @@
         <v>4</v>
       </c>
       <c r="G212" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -10820,7 +10820,7 @@
         <v>0</v>
       </c>
       <c r="L212" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M212" t="n">
         <v>20</v>
@@ -10848,7 +10848,7 @@
         <v>2</v>
       </c>
       <c r="E213" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F213" t="n">
         <v>3</v>
@@ -10869,7 +10869,7 @@
         <v>0</v>
       </c>
       <c r="L213" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M213" t="n">
         <v>17</v>
@@ -11007,7 +11007,7 @@
         <v>3</v>
       </c>
       <c r="I216" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J216" t="n">
         <v>2</v>
@@ -11016,7 +11016,7 @@
         <v>1</v>
       </c>
       <c r="L216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M216" t="n">
         <v>27</v>
@@ -11093,10 +11093,10 @@
         <v>2</v>
       </c>
       <c r="E218" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F218" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G218" t="n">
         <v>13</v>
@@ -11114,7 +11114,7 @@
         <v>0</v>
       </c>
       <c r="L218" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M218" t="n">
         <v>53</v>
@@ -11142,7 +11142,7 @@
         <v>2</v>
       </c>
       <c r="E219" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F219" t="n">
         <v>7</v>
@@ -11163,7 +11163,7 @@
         <v>1</v>
       </c>
       <c r="L219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M219" t="n">
         <v>33</v>
@@ -11295,7 +11295,7 @@
         <v>5</v>
       </c>
       <c r="G222" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H222" t="n">
         <v>7</v>
@@ -11310,7 +11310,7 @@
         <v>1</v>
       </c>
       <c r="L222" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M222" t="n">
         <v>59</v>
@@ -11338,10 +11338,10 @@
         <v>1</v>
       </c>
       <c r="E223" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F223" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G223" t="n">
         <v>8</v>
@@ -11359,7 +11359,7 @@
         <v>0</v>
       </c>
       <c r="L223" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M223" t="n">
         <v>29</v>
@@ -11402,13 +11402,13 @@
         <v>2</v>
       </c>
       <c r="J224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K224" t="n">
         <v>1</v>
       </c>
       <c r="L224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M224" t="n">
         <v>25</v>
@@ -11482,7 +11482,7 @@
         <v>3</v>
       </c>
       <c r="D226" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E226" t="n">
         <v>7</v>
@@ -11506,7 +11506,7 @@
         <v>0</v>
       </c>
       <c r="L226" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M226" t="n">
         <v>23</v>
@@ -11681,7 +11681,7 @@
         <v>0</v>
       </c>
       <c r="E230" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F230" t="n">
         <v>4</v>
@@ -11702,7 +11702,7 @@
         <v>0</v>
       </c>
       <c r="L230" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M230" t="n">
         <v>38</v>
@@ -11733,7 +11733,7 @@
         <v>6</v>
       </c>
       <c r="F231" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G231" t="n">
         <v>30</v>
@@ -11751,7 +11751,7 @@
         <v>1</v>
       </c>
       <c r="L231" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M231" t="n">
         <v>65</v>
@@ -11825,13 +11825,13 @@
         <v>1</v>
       </c>
       <c r="D233" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E233" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F233" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G233" t="n">
         <v>38</v>
@@ -11849,7 +11849,7 @@
         <v>0</v>
       </c>
       <c r="L233" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M233" t="n">
         <v>86</v>
@@ -11880,7 +11880,7 @@
         <v>8</v>
       </c>
       <c r="F234" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G234" t="n">
         <v>7</v>
@@ -11898,7 +11898,7 @@
         <v>1</v>
       </c>
       <c r="L234" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M234" t="n">
         <v>50</v>
@@ -11972,16 +11972,16 @@
         <v>4</v>
       </c>
       <c r="D236" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E236" t="n">
         <v>37</v>
       </c>
       <c r="F236" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G236" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H236" t="n">
         <v>14</v>
@@ -11996,7 +11996,7 @@
         <v>0</v>
       </c>
       <c r="L236" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M236" t="n">
         <v>187</v>
@@ -12018,7 +12018,7 @@
         <v>5</v>
       </c>
       <c r="C237" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D237" t="n">
         <v>6</v>
@@ -12027,7 +12027,7 @@
         <v>16</v>
       </c>
       <c r="F237" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G237" t="n">
         <v>30</v>
@@ -12045,7 +12045,7 @@
         <v>0</v>
       </c>
       <c r="L237" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M237" t="n">
         <v>86</v>
@@ -12067,10 +12067,10 @@
         <v>8</v>
       </c>
       <c r="C238" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D238" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E238" t="n">
         <v>25</v>
@@ -12094,7 +12094,7 @@
         <v>0</v>
       </c>
       <c r="L238" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M238" t="n">
         <v>120</v>
@@ -12168,13 +12168,13 @@
         <v>5</v>
       </c>
       <c r="D240" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E240" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F240" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G240" t="n">
         <v>65</v>
@@ -12183,7 +12183,7 @@
         <v>8</v>
       </c>
       <c r="I240" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -12192,7 +12192,7 @@
         <v>2</v>
       </c>
       <c r="L240" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M240" t="n">
         <v>149</v>
@@ -12220,13 +12220,13 @@
         <v>9</v>
       </c>
       <c r="E241" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F241" t="n">
         <v>14</v>
       </c>
       <c r="G241" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -12241,7 +12241,7 @@
         <v>0</v>
       </c>
       <c r="L241" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M241" t="n">
         <v>65</v>
@@ -12263,16 +12263,16 @@
         <v>1</v>
       </c>
       <c r="C242" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D242" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E242" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F242" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G242" t="n">
         <v>20</v>
@@ -12290,7 +12290,7 @@
         <v>1</v>
       </c>
       <c r="L242" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M242" t="n">
         <v>71</v>
@@ -12456,16 +12456,16 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C246" t="n">
         <v>4</v>
       </c>
       <c r="D246" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E246" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F246" t="n">
         <v>22</v>
@@ -12477,7 +12477,7 @@
         <v>11</v>
       </c>
       <c r="I246" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J246" t="n">
         <v>3</v>
@@ -12486,7 +12486,7 @@
         <v>1</v>
       </c>
       <c r="L246" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M246" t="n">
         <v>175</v>
@@ -12511,7 +12511,7 @@
         <v>1</v>
       </c>
       <c r="D247" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E247" t="n">
         <v>4</v>
@@ -12535,7 +12535,7 @@
         <v>0</v>
       </c>
       <c r="L247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M247" t="n">
         <v>43</v>
@@ -12615,7 +12615,7 @@
         <v>10</v>
       </c>
       <c r="F249" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G249" t="n">
         <v>26</v>
@@ -12633,7 +12633,7 @@
         <v>1</v>
       </c>
       <c r="L249" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M249" t="n">
         <v>59</v>
@@ -12652,7 +12652,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C250" t="n">
         <v>0</v>
@@ -12661,7 +12661,7 @@
         <v>0</v>
       </c>
       <c r="E250" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F250" t="n">
         <v>3</v>
@@ -12682,7 +12682,7 @@
         <v>1</v>
       </c>
       <c r="L250" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M250" t="n">
         <v>38</v>
@@ -12869,16 +12869,16 @@
         <v>12</v>
       </c>
       <c r="I254" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J254" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K254" t="n">
         <v>1</v>
       </c>
       <c r="L254" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M254" t="n">
         <v>50</v>
@@ -12897,13 +12897,13 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D255" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E255" t="n">
         <v>29</v>
@@ -12927,7 +12927,7 @@
         <v>1</v>
       </c>
       <c r="L255" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M255" t="n">
         <v>144</v>
@@ -12946,7 +12946,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C256" t="n">
         <v>19</v>
@@ -12976,7 +12976,7 @@
         <v>1</v>
       </c>
       <c r="L256" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M256" t="n">
         <v>222</v>
@@ -13142,10 +13142,10 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C260" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D260" t="n">
         <v>27</v>
@@ -13157,7 +13157,7 @@
         <v>29</v>
       </c>
       <c r="G260" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H260" t="n">
         <v>18</v>
@@ -13172,7 +13172,7 @@
         <v>3</v>
       </c>
       <c r="L260" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="M260" t="n">
         <v>289</v>
@@ -13191,19 +13191,19 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>766</v>
+        <v>797</v>
       </c>
       <c r="C261" t="n">
+        <v>82</v>
+      </c>
+      <c r="D261" t="n">
         <v>80</v>
       </c>
-      <c r="D261" t="n">
-        <v>75</v>
-      </c>
       <c r="E261" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F261" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G261" t="n">
         <v>45</v>
@@ -13221,7 +13221,7 @@
         <v>0</v>
       </c>
       <c r="L261" t="n">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="M261" t="n">
         <v>1160</v>
@@ -13240,19 +13240,19 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C262" t="n">
         <v>18</v>
       </c>
       <c r="D262" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E262" t="n">
         <v>13</v>
       </c>
       <c r="F262" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G262" t="n">
         <v>15</v>
@@ -13261,7 +13261,7 @@
         <v>1</v>
       </c>
       <c r="I262" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -13270,7 +13270,7 @@
         <v>1</v>
       </c>
       <c r="L262" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="M262" t="n">
         <v>157</v>
@@ -13289,7 +13289,7 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C263" t="n">
         <v>12</v>
@@ -13319,7 +13319,7 @@
         <v>0</v>
       </c>
       <c r="L263" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M263" t="n">
         <v>171</v>
@@ -13338,7 +13338,7 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C264" t="n">
         <v>13</v>
@@ -13347,7 +13347,7 @@
         <v>13</v>
       </c>
       <c r="E264" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F264" t="n">
         <v>8</v>
@@ -13368,7 +13368,7 @@
         <v>1</v>
       </c>
       <c r="L264" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M264" t="n">
         <v>189</v>
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C265" t="n">
         <v>11</v>
@@ -13396,7 +13396,7 @@
         <v>25</v>
       </c>
       <c r="E265" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F265" t="n">
         <v>18</v>
@@ -13417,7 +13417,7 @@
         <v>0</v>
       </c>
       <c r="L265" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M265" t="n">
         <v>268</v>
@@ -13494,13 +13494,13 @@
         <v>7</v>
       </c>
       <c r="E267" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F267" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G267" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H267" t="n">
         <v>6</v>
@@ -13515,7 +13515,7 @@
         <v>0</v>
       </c>
       <c r="L267" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M267" t="n">
         <v>131</v>
@@ -13534,7 +13534,7 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C268" t="n">
         <v>1</v>
@@ -13564,7 +13564,7 @@
         <v>1</v>
       </c>
       <c r="L268" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M268" t="n">
         <v>66</v>
@@ -13696,7 +13696,7 @@
         <v>11</v>
       </c>
       <c r="G271" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H271" t="n">
         <v>1</v>
@@ -13711,7 +13711,7 @@
         <v>0</v>
       </c>
       <c r="L271" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M271" t="n">
         <v>49</v>
@@ -13779,7 +13779,7 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C273" t="n">
         <v>0</v>
@@ -13809,7 +13809,7 @@
         <v>0</v>
       </c>
       <c r="L273" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M273" t="n">
         <v>29</v>
@@ -13828,7 +13828,7 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C274" t="n">
         <v>6</v>
@@ -13840,13 +13840,13 @@
         <v>14</v>
       </c>
       <c r="F274" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G274" t="n">
         <v>29</v>
       </c>
       <c r="H274" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I274" t="n">
         <v>4</v>
@@ -13858,7 +13858,7 @@
         <v>0</v>
       </c>
       <c r="L274" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="M274" t="n">
         <v>228</v>
@@ -13877,13 +13877,13 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C275" t="n">
         <v>12</v>
       </c>
       <c r="D275" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E275" t="n">
         <v>26</v>
@@ -13907,7 +13907,7 @@
         <v>1</v>
       </c>
       <c r="L275" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M275" t="n">
         <v>269</v>
@@ -13935,19 +13935,19 @@
         <v>10</v>
       </c>
       <c r="E276" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F276" t="n">
         <v>10</v>
       </c>
       <c r="G276" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H276" t="n">
         <v>4</v>
       </c>
       <c r="I276" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J276" t="n">
         <v>1</v>
@@ -13956,7 +13956,7 @@
         <v>0</v>
       </c>
       <c r="L276" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="M276" t="n">
         <v>85</v>
@@ -13990,7 +13990,7 @@
         <v>8</v>
       </c>
       <c r="G277" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H277" t="n">
         <v>2</v>
@@ -14005,7 +14005,7 @@
         <v>0</v>
       </c>
       <c r="L277" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M277" t="n">
         <v>100</v>
@@ -14122,7 +14122,7 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C280" t="n">
         <v>2</v>
@@ -14131,7 +14131,7 @@
         <v>8</v>
       </c>
       <c r="E280" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F280" t="n">
         <v>3</v>
@@ -14143,7 +14143,7 @@
         <v>3</v>
       </c>
       <c r="I280" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J280" t="n">
         <v>4</v>
@@ -14152,7 +14152,7 @@
         <v>0</v>
       </c>
       <c r="L280" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M280" t="n">
         <v>140</v>
@@ -14171,7 +14171,7 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C281" t="n">
         <v>12</v>
@@ -14192,7 +14192,7 @@
         <v>1</v>
       </c>
       <c r="I281" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J281" t="n">
         <v>1</v>
@@ -14201,7 +14201,7 @@
         <v>2</v>
       </c>
       <c r="L281" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M281" t="n">
         <v>155</v>
@@ -14223,7 +14223,7 @@
         <v>8</v>
       </c>
       <c r="C282" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D282" t="n">
         <v>10</v>
@@ -14250,7 +14250,7 @@
         <v>0</v>
       </c>
       <c r="L282" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M282" t="n">
         <v>96</v>
@@ -14324,7 +14324,7 @@
         <v>0</v>
       </c>
       <c r="D284" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E284" t="n">
         <v>22</v>
@@ -14348,7 +14348,7 @@
         <v>1</v>
       </c>
       <c r="L284" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M284" t="n">
         <v>94</v>
@@ -14382,7 +14382,7 @@
         <v>17</v>
       </c>
       <c r="G285" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H285" t="n">
         <v>2</v>
@@ -14397,7 +14397,7 @@
         <v>0</v>
       </c>
       <c r="L285" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M285" t="n">
         <v>117</v>
@@ -14416,19 +14416,19 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C286" t="n">
         <v>13</v>
       </c>
       <c r="D286" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E286" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F286" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G286" t="n">
         <v>12</v>
@@ -14440,13 +14440,13 @@
         <v>3</v>
       </c>
       <c r="J286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K286" t="n">
         <v>1</v>
       </c>
       <c r="L286" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="M286" t="n">
         <v>291</v>
@@ -14563,7 +14563,7 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C289" t="n">
         <v>1</v>
@@ -14593,7 +14593,7 @@
         <v>1</v>
       </c>
       <c r="L289" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M289" t="n">
         <v>100</v>
@@ -14618,7 +14618,7 @@
         <v>11</v>
       </c>
       <c r="D290" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E290" t="n">
         <v>20</v>
@@ -14642,7 +14642,7 @@
         <v>1</v>
       </c>
       <c r="L290" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M290" t="n">
         <v>302</v>
@@ -14664,13 +14664,13 @@
         <v>46</v>
       </c>
       <c r="C291" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D291" t="n">
         <v>12</v>
       </c>
       <c r="E291" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F291" t="n">
         <v>11</v>
@@ -14691,7 +14691,7 @@
         <v>1</v>
       </c>
       <c r="L291" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M291" t="n">
         <v>122</v>
@@ -14857,22 +14857,22 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C295" t="n">
         <v>1</v>
       </c>
       <c r="D295" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E295" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F295" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G295" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H295" t="n">
         <v>7</v>
@@ -14887,7 +14887,7 @@
         <v>0</v>
       </c>
       <c r="L295" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="M295" t="n">
         <v>134</v>
@@ -14906,13 +14906,13 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C296" t="n">
         <v>1</v>
       </c>
       <c r="D296" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E296" t="n">
         <v>29</v>
@@ -14936,7 +14936,7 @@
         <v>0</v>
       </c>
       <c r="L296" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M296" t="n">
         <v>122</v>
@@ -15368,7 +15368,7 @@
         <v>7</v>
       </c>
       <c r="I305" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J305" t="n">
         <v>3</v>
@@ -15377,7 +15377,7 @@
         <v>0</v>
       </c>
       <c r="L305" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M305" t="n">
         <v>72</v>
@@ -15405,7 +15405,7 @@
         <v>4</v>
       </c>
       <c r="E306" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F306" t="n">
         <v>12</v>
@@ -15426,7 +15426,7 @@
         <v>2</v>
       </c>
       <c r="L306" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M306" t="n">
         <v>78</v>
@@ -15604,7 +15604,7 @@
         <v>7</v>
       </c>
       <c r="F310" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G310" t="n">
         <v>71</v>
@@ -15622,7 +15622,7 @@
         <v>0</v>
       </c>
       <c r="L310" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M310" t="n">
         <v>109</v>
@@ -15702,10 +15702,10 @@
         <v>22</v>
       </c>
       <c r="F312" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G312" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H312" t="n">
         <v>13</v>
@@ -15720,7 +15720,7 @@
         <v>1</v>
       </c>
       <c r="L312" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M312" t="n">
         <v>149</v>
@@ -15751,10 +15751,10 @@
         <v>34</v>
       </c>
       <c r="F313" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G313" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H313" t="n">
         <v>18</v>
@@ -15769,7 +15769,7 @@
         <v>1</v>
       </c>
       <c r="L313" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M313" t="n">
         <v>232</v>
@@ -15791,19 +15791,19 @@
         <v>12</v>
       </c>
       <c r="C314" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D314" t="n">
         <v>16</v>
       </c>
       <c r="E314" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F314" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G314" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H314" t="n">
         <v>9</v>
@@ -15818,7 +15818,7 @@
         <v>0</v>
       </c>
       <c r="L314" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="M314" t="n">
         <v>210</v>
@@ -15990,10 +15990,10 @@
         <v>4</v>
       </c>
       <c r="D318" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E318" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F318" t="n">
         <v>9</v>
@@ -16014,7 +16014,7 @@
         <v>0</v>
       </c>
       <c r="L318" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M318" t="n">
         <v>91</v>
@@ -16189,7 +16189,7 @@
         <v>0</v>
       </c>
       <c r="E322" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F322" t="n">
         <v>1</v>
@@ -16210,7 +16210,7 @@
         <v>0</v>
       </c>
       <c r="L322" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M322" t="n">
         <v>16</v>
@@ -16327,7 +16327,7 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C325" t="n">
         <v>0</v>
@@ -16348,7 +16348,7 @@
         <v>1</v>
       </c>
       <c r="I325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J325" t="n">
         <v>0</v>
@@ -16357,7 +16357,7 @@
         <v>1</v>
       </c>
       <c r="L325" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M325" t="n">
         <v>20</v>
@@ -16587,10 +16587,10 @@
         <v>1</v>
       </c>
       <c r="G330" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H330" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I330" t="n">
         <v>3</v>
@@ -16602,7 +16602,7 @@
         <v>1</v>
       </c>
       <c r="L330" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="M330" t="n">
         <v>58</v>
@@ -16633,7 +16633,7 @@
         <v>12</v>
       </c>
       <c r="F331" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G331" t="n">
         <v>7</v>
@@ -16651,7 +16651,7 @@
         <v>0</v>
       </c>
       <c r="L331" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M331" t="n">
         <v>118</v>
@@ -16670,7 +16670,7 @@
         </is>
       </c>
       <c r="B332" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C332" t="n">
         <v>0</v>
@@ -16700,7 +16700,7 @@
         <v>0</v>
       </c>
       <c r="L332" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M332" t="n">
         <v>45</v>
@@ -17656,7 +17656,7 @@
         <v>0</v>
       </c>
       <c r="D352" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E352" t="n">
         <v>1</v>
@@ -17680,7 +17680,7 @@
         <v>0</v>
       </c>
       <c r="L352" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M352" t="n">
         <v>46</v>
@@ -17754,7 +17754,7 @@
         <v>0</v>
       </c>
       <c r="D354" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E354" t="n">
         <v>2</v>
@@ -17778,7 +17778,7 @@
         <v>0</v>
       </c>
       <c r="L354" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M354" t="n">
         <v>41</v>
@@ -17803,7 +17803,7 @@
         <v>0</v>
       </c>
       <c r="D355" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E355" t="n">
         <v>0</v>
@@ -17827,7 +17827,7 @@
         <v>1</v>
       </c>
       <c r="L355" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M355" t="n">
         <v>23</v>
@@ -17852,7 +17852,7 @@
         <v>0</v>
       </c>
       <c r="D356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E356" t="n">
         <v>0</v>
@@ -17861,13 +17861,13 @@
         <v>0</v>
       </c>
       <c r="G356" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H356" t="n">
         <v>4</v>
       </c>
       <c r="I356" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J356" t="n">
         <v>2</v>
@@ -17876,7 +17876,7 @@
         <v>0</v>
       </c>
       <c r="L356" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="M356" t="n">
         <v>44</v>
@@ -17956,16 +17956,16 @@
         <v>12</v>
       </c>
       <c r="F358" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G358" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H358" t="n">
         <v>6</v>
       </c>
       <c r="I358" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J358" t="n">
         <v>3</v>
@@ -17974,7 +17974,7 @@
         <v>0</v>
       </c>
       <c r="L358" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="M358" t="n">
         <v>125</v>
@@ -17999,7 +17999,7 @@
         <v>1</v>
       </c>
       <c r="D359" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E359" t="n">
         <v>5</v>
@@ -18023,7 +18023,7 @@
         <v>0</v>
       </c>
       <c r="L359" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M359" t="n">
         <v>91</v>
@@ -18195,7 +18195,7 @@
         <v>0</v>
       </c>
       <c r="D363" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E363" t="n">
         <v>0</v>
@@ -18219,7 +18219,7 @@
         <v>0</v>
       </c>
       <c r="L363" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M363" t="n">
         <v>9</v>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -512,19 +512,19 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -558,25 +558,25 @@
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
         <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -607,13 +607,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -665,10 +665,10 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -705,10 +705,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -803,13 +803,13 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -855,10 +855,10 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -907,16 +907,16 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -999,10 +999,10 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1140,16 +1140,16 @@
         <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
         <v>2</v>
@@ -1296,13 +1296,13 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1342,13 +1342,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1385,13 +1385,13 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1440,13 +1440,13 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
@@ -1636,19 +1636,19 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1685,10 +1685,10 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1728,28 +1728,28 @@
         <v>12</v>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1774,22 +1774,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1832,19 +1832,19 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1924,14 +1924,14 @@
         <v>17</v>
       </c>
       <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
         <v>4</v>
       </c>
-      <c r="D31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" t="n">
-        <v>2</v>
-      </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
@@ -1939,10 +1939,10 @@
         <v>3</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1970,28 +1970,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2028,22 +2028,22 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" t="n">
         <v>2</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
@@ -2077,13 +2077,13 @@
         <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -2175,16 +2175,16 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -2221,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -2230,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C39" t="n">
         <v>1</v>
@@ -2325,22 +2325,22 @@
         <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -2371,16 +2371,16 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G40" t="n">
         <v>4</v>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -2435,13 +2435,13 @@
         <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>15</v>
@@ -2475,10 +2475,10 @@
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -2570,13 +2570,13 @@
         <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -2622,10 +2622,10 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" t="n">
         <v>1</v>
@@ -2665,13 +2665,13 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -2717,13 +2717,13 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
         <v>2</v>
@@ -2760,19 +2760,19 @@
         <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
         <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
@@ -2809,10 +2809,10 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F49" t="n">
         <v>1</v>
@@ -2824,7 +2824,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2852,16 +2852,16 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -2910,22 +2910,22 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -3057,19 +3057,19 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" t="n">
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" t="n">
         <v>4</v>
-      </c>
-      <c r="I54" t="n">
-        <v>3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -3097,7 +3097,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -3109,13 +3109,13 @@
         <v>2</v>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
@@ -3155,10 +3155,10 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
         <v>4</v>
@@ -3167,13 +3167,13 @@
         <v>3</v>
       </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J56" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" t="n">
         <v>1</v>
@@ -3195,25 +3195,25 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C57" t="n">
         <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" t="n">
         <v>4</v>
       </c>
       <c r="H57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
@@ -3247,7 +3247,7 @@
         <v>15</v>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D58" t="n">
         <v>2</v>
@@ -3256,7 +3256,7 @@
         <v>3</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G58" t="n">
         <v>2</v>
@@ -3299,13 +3299,13 @@
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
         <v>3</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" t="n">
         <v>1</v>
@@ -3348,13 +3348,13 @@
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -3403,10 +3403,10 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C62" t="n">
         <v>1</v>
@@ -3449,13 +3449,13 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
         <v>1</v>
@@ -3593,19 +3593,19 @@
         <v>0</v>
       </c>
       <c r="D65" t="n">
+        <v>3</v>
+      </c>
+      <c r="E65" t="n">
         <v>4</v>
       </c>
-      <c r="E65" t="n">
-        <v>3</v>
-      </c>
       <c r="F65" t="n">
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" t="n">
         <v>1</v>
@@ -3642,16 +3642,16 @@
         <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -3694,10 +3694,10 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
         <v>3</v>
@@ -3743,13 +3743,13 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -3792,13 +3792,13 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F69" t="n">
         <v>2</v>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -3841,16 +3841,16 @@
         <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
         <v>4</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70" t="n">
         <v>1</v>
@@ -3991,19 +3991,19 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -4034,25 +4034,25 @@
         <v>2</v>
       </c>
       <c r="D74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G74" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74" t="n">
         <v>2</v>
       </c>
       <c r="J74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -4086,13 +4086,13 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" t="n">
         <v>2</v>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -4132,10 +4132,10 @@
         <v>3</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76" t="n">
         <v>1</v>
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C77" t="n">
         <v>1</v>
@@ -4184,13 +4184,13 @@
         <v>2</v>
       </c>
       <c r="E77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77" t="n">
+        <v>2</v>
+      </c>
+      <c r="G77" t="n">
         <v>4</v>
-      </c>
-      <c r="G77" t="n">
-        <v>2</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -4273,16 +4273,16 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F79" t="n">
         <v>2</v>
@@ -4291,10 +4291,10 @@
         <v>1</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -4331,10 +4331,10 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
         <v>1</v>
@@ -4343,13 +4343,13 @@
         <v>2</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -4377,22 +4377,22 @@
         <v>4</v>
       </c>
       <c r="D81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H81" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>1</v>
@@ -4429,19 +4429,19 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -4469,19 +4469,19 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G83" t="n">
         <v>1</v>
@@ -4637,10 +4637,10 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -4674,10 +4674,10 @@
         <v>5</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G87" t="n">
         <v>1</v>
@@ -4714,7 +4714,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C88" t="n">
         <v>2</v>
@@ -4726,10 +4726,10 @@
         <v>1</v>
       </c>
       <c r="F88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H88" t="n">
         <v>1</v>
@@ -4769,16 +4769,16 @@
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -4873,10 +4873,10 @@
         <v>1</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -5014,13 +5014,13 @@
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G94" t="n">
         <v>5</v>
@@ -5032,10 +5032,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
@@ -5112,16 +5112,16 @@
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -5173,10 +5173,10 @@
         <v>1</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -5210,16 +5210,16 @@
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -5256,19 +5256,19 @@
         <v>8</v>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D99" t="n">
         <v>1</v>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C100" t="n">
         <v>2</v>
@@ -5311,7 +5311,7 @@
         <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100" t="n">
         <v>2</v>
@@ -5360,13 +5360,13 @@
         <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -5409,19 +5409,19 @@
         <v>1</v>
       </c>
       <c r="E102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -5455,19 +5455,19 @@
         <v>2</v>
       </c>
       <c r="D103" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E103" t="n">
         <v>3</v>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G103" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H103" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I103" t="n">
         <v>2</v>
@@ -5504,13 +5504,13 @@
         <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E104" t="n">
         <v>2</v>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -5559,13 +5559,13 @@
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I105" t="n">
         <v>1</v>
@@ -5605,13 +5605,13 @@
         <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F106" t="n">
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -5648,13 +5648,13 @@
         <v>16</v>
       </c>
       <c r="C107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D107" t="n">
         <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" t="n">
         <v>1</v>
@@ -5703,13 +5703,13 @@
         <v>3</v>
       </c>
       <c r="E108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -5844,7 +5844,7 @@
         <v>20</v>
       </c>
       <c r="C111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D111" t="n">
         <v>1</v>
@@ -5853,7 +5853,7 @@
         <v>2</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G111" t="n">
         <v>2</v>
@@ -5899,10 +5899,10 @@
         <v>0</v>
       </c>
       <c r="E112" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -5994,7 +5994,7 @@
         <v>1</v>
       </c>
       <c r="D114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E114" t="n">
         <v>1</v>
@@ -6012,7 +6012,7 @@
         <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K114" t="n">
         <v>0</v>
@@ -6095,10 +6095,10 @@
         <v>0</v>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C119" t="n">
         <v>1</v>
@@ -6242,25 +6242,25 @@
         <v>1</v>
       </c>
       <c r="E119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F119" t="n">
         <v>3</v>
       </c>
       <c r="G119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I119" t="n">
         <v>1</v>
       </c>
       <c r="J119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -6337,13 +6337,13 @@
         <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E121" t="n">
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G121" t="n">
         <v>3</v>
@@ -6432,22 +6432,22 @@
         <v>23</v>
       </c>
       <c r="C123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E123" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F123" t="n">
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I123" t="n">
         <v>1</v>
@@ -6487,22 +6487,22 @@
         <v>6</v>
       </c>
       <c r="E124" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F124" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H124" t="n">
         <v>1</v>
       </c>
       <c r="I124" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
@@ -6527,7 +6527,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C125" t="n">
         <v>1</v>
@@ -6536,13 +6536,13 @@
         <v>3</v>
       </c>
       <c r="E125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -6585,13 +6585,13 @@
         <v>0</v>
       </c>
       <c r="E126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F126" t="n">
         <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -6634,10 +6634,10 @@
         <v>0</v>
       </c>
       <c r="E127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -6674,7 +6674,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C128" t="n">
         <v>4</v>
@@ -6686,10 +6686,10 @@
         <v>8</v>
       </c>
       <c r="F128" t="n">
+        <v>2</v>
+      </c>
+      <c r="G128" t="n">
         <v>4</v>
-      </c>
-      <c r="G128" t="n">
-        <v>1</v>
       </c>
       <c r="H128" t="n">
         <v>1</v>
@@ -6775,13 +6775,13 @@
         <v>25</v>
       </c>
       <c r="C130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D130" t="n">
         <v>3</v>
       </c>
       <c r="E130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F130" t="n">
         <v>0</v>
@@ -6842,10 +6842,10 @@
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
@@ -6879,19 +6879,19 @@
         <v>1</v>
       </c>
       <c r="E132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J132" t="n">
         <v>1</v>
@@ -6919,22 +6919,22 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C133" t="n">
         <v>3</v>
       </c>
       <c r="D133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E133" t="n">
+        <v>6</v>
+      </c>
+      <c r="F133" t="n">
+        <v>4</v>
+      </c>
+      <c r="G133" t="n">
         <v>5</v>
-      </c>
-      <c r="F133" t="n">
-        <v>3</v>
-      </c>
-      <c r="G133" t="n">
-        <v>3</v>
       </c>
       <c r="H133" t="n">
         <v>1</v>
@@ -7023,13 +7023,13 @@
         <v>1</v>
       </c>
       <c r="D135" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E135" t="n">
         <v>2</v>
       </c>
       <c r="F135" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -7127,10 +7127,10 @@
         <v>2</v>
       </c>
       <c r="F137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -7167,19 +7167,19 @@
         <v>22</v>
       </c>
       <c r="C138" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D138" t="n">
         <v>0</v>
       </c>
       <c r="E138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -7222,16 +7222,16 @@
         <v>0</v>
       </c>
       <c r="E139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F139" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G139" t="n">
         <v>2</v>
       </c>
       <c r="H139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I139" t="n">
         <v>0</v>
@@ -7277,10 +7277,10 @@
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I140" t="n">
         <v>1</v>
@@ -7314,19 +7314,19 @@
         <v>63</v>
       </c>
       <c r="C141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D141" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C142" t="n">
         <v>1</v>
@@ -7369,7 +7369,7 @@
         <v>1</v>
       </c>
       <c r="E142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F142" t="n">
         <v>1</v>
@@ -7418,19 +7418,19 @@
         <v>0</v>
       </c>
       <c r="E143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -7458,7 +7458,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C144" t="n">
         <v>4</v>
@@ -7467,13 +7467,13 @@
         <v>2</v>
       </c>
       <c r="E144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -7528,10 +7528,10 @@
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K145" t="n">
         <v>0</v>
@@ -7577,10 +7577,10 @@
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K146" t="n">
         <v>0</v>
@@ -7611,10 +7611,10 @@
         <v>3</v>
       </c>
       <c r="D147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F147" t="n">
         <v>1</v>
@@ -7660,13 +7660,13 @@
         <v>1</v>
       </c>
       <c r="D148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E148" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G148" t="n">
         <v>1</v>
@@ -7709,22 +7709,22 @@
         <v>4</v>
       </c>
       <c r="D149" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E149" t="n">
         <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I149" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J149" t="n">
         <v>1</v>
@@ -7752,13 +7752,13 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C150" t="n">
         <v>1</v>
       </c>
       <c r="D150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E150" t="n">
         <v>3</v>
@@ -7767,16 +7767,16 @@
         <v>2</v>
       </c>
       <c r="G150" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
       </c>
       <c r="I150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K150" t="n">
         <v>0</v>
@@ -7807,19 +7807,19 @@
         <v>2</v>
       </c>
       <c r="D151" t="n">
+        <v>3</v>
+      </c>
+      <c r="E151" t="n">
         <v>4</v>
       </c>
-      <c r="E151" t="n">
-        <v>3</v>
-      </c>
       <c r="F151" t="n">
         <v>1</v>
       </c>
       <c r="G151" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I151" t="n">
         <v>0</v>
@@ -7831,7 +7831,7 @@
         <v>0</v>
       </c>
       <c r="L151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
         <v>27</v>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C152" t="n">
         <v>1</v>
@@ -7859,19 +7859,19 @@
         <v>1</v>
       </c>
       <c r="E152" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F152" t="n">
         <v>3</v>
       </c>
       <c r="G152" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H152" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I152" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -7905,22 +7905,22 @@
         <v>2</v>
       </c>
       <c r="D153" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E153" t="n">
         <v>4</v>
       </c>
       <c r="F153" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G153" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H153" t="n">
         <v>4</v>
       </c>
       <c r="I153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J153" t="n">
         <v>2</v>
@@ -7954,22 +7954,22 @@
         <v>1</v>
       </c>
       <c r="D154" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E154" t="n">
         <v>10</v>
       </c>
       <c r="F154" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G154" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H154" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I154" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J154" t="n">
         <v>2</v>
@@ -8003,28 +8003,28 @@
         <v>1</v>
       </c>
       <c r="D155" t="n">
+        <v>2</v>
+      </c>
+      <c r="E155" t="n">
         <v>4</v>
       </c>
-      <c r="E155" t="n">
+      <c r="F155" t="n">
         <v>5</v>
       </c>
-      <c r="F155" t="n">
-        <v>1</v>
-      </c>
       <c r="G155" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H155" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I155" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J155" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L155" t="n">
         <v>0</v>
@@ -8046,31 +8046,31 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C156" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D156" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E156" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F156" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G156" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H156" t="n">
         <v>4</v>
       </c>
       <c r="I156" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K156" t="n">
         <v>1</v>
@@ -8116,10 +8116,10 @@
         <v>0</v>
       </c>
       <c r="I157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K157" t="n">
         <v>0</v>
@@ -8162,10 +8162,10 @@
         <v>11</v>
       </c>
       <c r="H158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I158" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -8193,31 +8193,31 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C159" t="n">
         <v>1</v>
       </c>
       <c r="D159" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E159" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F159" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G159" t="n">
         <v>8</v>
       </c>
       <c r="H159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K159" t="n">
         <v>1</v>
@@ -8242,7 +8242,7 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C160" t="n">
         <v>3</v>
@@ -8251,16 +8251,16 @@
         <v>1</v>
       </c>
       <c r="E160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F160" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G160" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I160" t="n">
         <v>0</v>
@@ -8297,25 +8297,25 @@
         <v>4</v>
       </c>
       <c r="D161" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E161" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F161" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G161" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K161" t="n">
         <v>0</v>
@@ -8343,34 +8343,34 @@
         <v>45</v>
       </c>
       <c r="C162" t="n">
+        <v>4</v>
+      </c>
+      <c r="D162" t="n">
+        <v>3</v>
+      </c>
+      <c r="E162" t="n">
+        <v>13</v>
+      </c>
+      <c r="F162" t="n">
         <v>5</v>
       </c>
-      <c r="D162" t="n">
-        <v>5</v>
-      </c>
-      <c r="E162" t="n">
-        <v>10</v>
-      </c>
-      <c r="F162" t="n">
-        <v>8</v>
-      </c>
       <c r="G162" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I162" t="n">
         <v>1</v>
       </c>
       <c r="J162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K162" t="n">
         <v>0</v>
       </c>
       <c r="L162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M162" t="n">
         <v>84</v>
@@ -8398,19 +8398,19 @@
         <v>2</v>
       </c>
       <c r="E163" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F163" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G163" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -8453,10 +8453,10 @@
         <v>2</v>
       </c>
       <c r="G164" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I164" t="n">
         <v>0</v>
@@ -8493,25 +8493,25 @@
         <v>4</v>
       </c>
       <c r="D165" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E165" t="n">
+        <v>7</v>
+      </c>
+      <c r="F165" t="n">
+        <v>9</v>
+      </c>
+      <c r="G165" t="n">
         <v>6</v>
       </c>
-      <c r="F165" t="n">
-        <v>7</v>
-      </c>
-      <c r="G165" t="n">
-        <v>7</v>
-      </c>
       <c r="H165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I165" t="n">
         <v>2</v>
       </c>
       <c r="J165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K165" t="n">
         <v>1</v>
@@ -8551,10 +8551,10 @@
         <v>2</v>
       </c>
       <c r="G166" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I166" t="n">
         <v>1</v>
@@ -8585,16 +8585,16 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C167" t="n">
         <v>1</v>
       </c>
       <c r="D167" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E167" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F167" t="n">
         <v>1</v>
@@ -8640,22 +8640,22 @@
         <v>2</v>
       </c>
       <c r="D168" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F168" t="n">
         <v>2</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H168" t="n">
         <v>1</v>
       </c>
       <c r="I168" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -8686,16 +8686,16 @@
         <v>10</v>
       </c>
       <c r="C169" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D169" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E169" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F169" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G169" t="n">
         <v>4</v>
@@ -8732,28 +8732,28 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C170" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D170" t="n">
         <v>1</v>
       </c>
       <c r="E170" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F170" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G170" t="n">
         <v>7</v>
       </c>
       <c r="H170" t="n">
+        <v>2</v>
+      </c>
+      <c r="I170" t="n">
         <v>4</v>
-      </c>
-      <c r="I170" t="n">
-        <v>2</v>
       </c>
       <c r="J170" t="n">
         <v>1</v>
@@ -8784,7 +8784,7 @@
         <v>1</v>
       </c>
       <c r="C171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D171" t="n">
         <v>1</v>
@@ -8793,7 +8793,7 @@
         <v>7</v>
       </c>
       <c r="F171" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G171" t="n">
         <v>6</v>
@@ -8830,28 +8830,28 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C172" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D172" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E172" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F172" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G172" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I172" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -8882,16 +8882,16 @@
         <v>3</v>
       </c>
       <c r="C173" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D173" t="n">
         <v>4</v>
       </c>
       <c r="E173" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F173" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G173" t="n">
         <v>5</v>
@@ -8900,7 +8900,7 @@
         <v>2</v>
       </c>
       <c r="I173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -8928,28 +8928,28 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C174" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D174" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E174" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F174" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G174" t="n">
         <v>7</v>
       </c>
       <c r="H174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I174" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -8977,7 +8977,7 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C175" t="n">
         <v>2</v>
@@ -8986,19 +8986,19 @@
         <v>5</v>
       </c>
       <c r="E175" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F175" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G175" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H175" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -9026,22 +9026,22 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C176" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D176" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E176" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F176" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G176" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H176" t="n">
         <v>4</v>
@@ -9050,13 +9050,13 @@
         <v>2</v>
       </c>
       <c r="J176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K176" t="n">
         <v>0</v>
       </c>
       <c r="L176" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M176" t="n">
         <v>69</v>
@@ -9075,25 +9075,25 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C177" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D177" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E177" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F177" t="n">
         <v>11</v>
       </c>
       <c r="G177" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I177" t="n">
         <v>2</v>
@@ -9127,19 +9127,19 @@
         <v>14</v>
       </c>
       <c r="C178" t="n">
+        <v>5</v>
+      </c>
+      <c r="D178" t="n">
         <v>6</v>
       </c>
-      <c r="D178" t="n">
+      <c r="E178" t="n">
+        <v>10</v>
+      </c>
+      <c r="F178" t="n">
+        <v>5</v>
+      </c>
+      <c r="G178" t="n">
         <v>9</v>
-      </c>
-      <c r="E178" t="n">
-        <v>8</v>
-      </c>
-      <c r="F178" t="n">
-        <v>2</v>
-      </c>
-      <c r="G178" t="n">
-        <v>10</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -9176,25 +9176,25 @@
         <v>15</v>
       </c>
       <c r="C179" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D179" t="n">
         <v>3</v>
       </c>
       <c r="E179" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F179" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G179" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H179" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -9222,34 +9222,34 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C180" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D180" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E180" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F180" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G180" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H180" t="n">
+        <v>7</v>
+      </c>
+      <c r="I180" t="n">
+        <v>1</v>
+      </c>
+      <c r="J180" t="n">
         <v>4</v>
       </c>
-      <c r="I180" t="n">
-        <v>1</v>
-      </c>
-      <c r="J180" t="n">
-        <v>2</v>
-      </c>
       <c r="K180" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L180" t="n">
         <v>0</v>
@@ -9271,28 +9271,28 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C181" t="n">
         <v>13</v>
       </c>
       <c r="D181" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E181" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F181" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G181" t="n">
         <v>4</v>
       </c>
       <c r="H181" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>0</v>
       </c>
       <c r="L181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M181" t="n">
         <v>115</v>
@@ -9320,19 +9320,19 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D182" t="n">
+        <v>3</v>
+      </c>
+      <c r="E182" t="n">
+        <v>13</v>
+      </c>
+      <c r="F182" t="n">
         <v>4</v>
-      </c>
-      <c r="E182" t="n">
-        <v>10</v>
-      </c>
-      <c r="F182" t="n">
-        <v>3</v>
       </c>
       <c r="G182" t="n">
         <v>6</v>
@@ -9381,10 +9381,10 @@
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -9418,28 +9418,28 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C184" t="n">
         <v>8</v>
       </c>
       <c r="D184" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E184" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F184" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G184" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H184" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I184" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -9467,34 +9467,34 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C185" t="n">
         <v>12</v>
       </c>
       <c r="D185" t="n">
+        <v>14</v>
+      </c>
+      <c r="E185" t="n">
+        <v>23</v>
+      </c>
+      <c r="F185" t="n">
+        <v>10</v>
+      </c>
+      <c r="G185" t="n">
         <v>15</v>
       </c>
-      <c r="E185" t="n">
-        <v>18</v>
-      </c>
-      <c r="F185" t="n">
-        <v>13</v>
-      </c>
-      <c r="G185" t="n">
-        <v>13</v>
-      </c>
       <c r="H185" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J185" t="n">
         <v>1</v>
       </c>
       <c r="K185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L185" t="n">
         <v>0</v>
@@ -9516,7 +9516,7 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C186" t="n">
         <v>6</v>
@@ -9525,19 +9525,19 @@
         <v>1</v>
       </c>
       <c r="E186" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F186" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G186" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -9565,28 +9565,28 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C187" t="n">
+        <v>4</v>
+      </c>
+      <c r="D187" t="n">
         <v>5</v>
       </c>
-      <c r="D187" t="n">
+      <c r="E187" t="n">
+        <v>13</v>
+      </c>
+      <c r="F187" t="n">
         <v>6</v>
       </c>
-      <c r="E187" t="n">
-        <v>12</v>
-      </c>
-      <c r="F187" t="n">
-        <v>7</v>
-      </c>
       <c r="G187" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H187" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I187" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J187" t="n">
         <v>2</v>
@@ -9620,16 +9620,16 @@
         <v>2</v>
       </c>
       <c r="D188" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E188" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F188" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G188" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H188" t="n">
         <v>1</v>
@@ -9638,7 +9638,7 @@
         <v>0</v>
       </c>
       <c r="J188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K188" t="n">
         <v>0</v>
@@ -9678,10 +9678,10 @@
         <v>0</v>
       </c>
       <c r="G189" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H189" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I189" t="n">
         <v>0</v>
@@ -9712,31 +9712,31 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C190" t="n">
         <v>10</v>
       </c>
       <c r="D190" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E190" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F190" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G190" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H190" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I190" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J190" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K190" t="n">
         <v>1</v>
@@ -9761,34 +9761,34 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C191" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D191" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E191" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F191" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G191" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H191" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I191" t="n">
         <v>2</v>
       </c>
       <c r="J191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L191" t="n">
         <v>2</v>
@@ -9859,34 +9859,34 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C193" t="n">
         <v>4</v>
       </c>
       <c r="D193" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E193" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F193" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G193" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H193" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I193" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K193" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L193" t="n">
         <v>0</v>
@@ -9908,34 +9908,34 @@
         </is>
       </c>
       <c r="B194" t="n">
+        <v>8</v>
+      </c>
+      <c r="C194" t="n">
+        <v>3</v>
+      </c>
+      <c r="D194" t="n">
+        <v>4</v>
+      </c>
+      <c r="E194" t="n">
+        <v>16</v>
+      </c>
+      <c r="F194" t="n">
         <v>10</v>
       </c>
-      <c r="C194" t="n">
-        <v>4</v>
-      </c>
-      <c r="D194" t="n">
-        <v>6</v>
-      </c>
-      <c r="E194" t="n">
-        <v>11</v>
-      </c>
-      <c r="F194" t="n">
-        <v>7</v>
-      </c>
       <c r="G194" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H194" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I194" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L194" t="n">
         <v>1</v>
@@ -10009,28 +10009,28 @@
         <v>21</v>
       </c>
       <c r="C196" t="n">
+        <v>6</v>
+      </c>
+      <c r="D196" t="n">
         <v>9</v>
       </c>
-      <c r="D196" t="n">
-        <v>10</v>
-      </c>
       <c r="E196" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F196" t="n">
         <v>14</v>
       </c>
       <c r="G196" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H196" t="n">
         <v>5</v>
       </c>
       <c r="I196" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K196" t="n">
         <v>0</v>
@@ -10055,28 +10055,28 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C197" t="n">
         <v>5</v>
       </c>
       <c r="D197" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E197" t="n">
+        <v>12</v>
+      </c>
+      <c r="F197" t="n">
         <v>11</v>
       </c>
-      <c r="F197" t="n">
-        <v>8</v>
-      </c>
       <c r="G197" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H197" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I197" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -10104,25 +10104,25 @@
         </is>
       </c>
       <c r="B198" t="n">
+        <v>15</v>
+      </c>
+      <c r="C198" t="n">
+        <v>7</v>
+      </c>
+      <c r="D198" t="n">
+        <v>7</v>
+      </c>
+      <c r="E198" t="n">
         <v>16</v>
       </c>
-      <c r="C198" t="n">
-        <v>9</v>
-      </c>
-      <c r="D198" t="n">
+      <c r="F198" t="n">
+        <v>6</v>
+      </c>
+      <c r="G198" t="n">
         <v>8</v>
       </c>
-      <c r="E198" t="n">
-        <v>12</v>
-      </c>
-      <c r="F198" t="n">
-        <v>8</v>
-      </c>
-      <c r="G198" t="n">
-        <v>5</v>
-      </c>
       <c r="H198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I198" t="n">
         <v>1</v>
@@ -10153,22 +10153,22 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C199" t="n">
         <v>7</v>
       </c>
       <c r="D199" t="n">
+        <v>4</v>
+      </c>
+      <c r="E199" t="n">
+        <v>19</v>
+      </c>
+      <c r="F199" t="n">
+        <v>7</v>
+      </c>
+      <c r="G199" t="n">
         <v>9</v>
-      </c>
-      <c r="E199" t="n">
-        <v>13</v>
-      </c>
-      <c r="F199" t="n">
-        <v>3</v>
-      </c>
-      <c r="G199" t="n">
-        <v>11</v>
       </c>
       <c r="H199" t="n">
         <v>1</v>
@@ -10202,19 +10202,19 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C200" t="n">
         <v>4</v>
       </c>
       <c r="D200" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E200" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F200" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G200" t="n">
         <v>3</v>
@@ -10223,7 +10223,7 @@
         <v>1</v>
       </c>
       <c r="I200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -10232,7 +10232,7 @@
         <v>0</v>
       </c>
       <c r="L200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M200" t="n">
         <v>44</v>
@@ -10303,37 +10303,37 @@
         <v>22</v>
       </c>
       <c r="C202" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D202" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E202" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F202" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G202" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H202" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I202" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J202" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K202" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L202" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M202" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N202" t="n">
         <v>182</v>
@@ -10367,10 +10367,10 @@
         <v>0</v>
       </c>
       <c r="H203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -10398,31 +10398,31 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C204" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D204" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E204" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F204" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G204" t="n">
         <v>20</v>
       </c>
       <c r="H204" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I204" t="n">
         <v>4</v>
       </c>
       <c r="J204" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K204" t="n">
         <v>0</v>
@@ -10431,7 +10431,7 @@
         <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N204" t="n">
         <v>105</v>
@@ -10447,28 +10447,28 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C205" t="n">
+        <v>6</v>
+      </c>
+      <c r="D205" t="n">
+        <v>3</v>
+      </c>
+      <c r="E205" t="n">
+        <v>23</v>
+      </c>
+      <c r="F205" t="n">
+        <v>8</v>
+      </c>
+      <c r="G205" t="n">
+        <v>35</v>
+      </c>
+      <c r="H205" t="n">
         <v>7</v>
       </c>
-      <c r="D205" t="n">
-        <v>6</v>
-      </c>
-      <c r="E205" t="n">
-        <v>10</v>
-      </c>
-      <c r="F205" t="n">
-        <v>12</v>
-      </c>
-      <c r="G205" t="n">
-        <v>37</v>
-      </c>
-      <c r="H205" t="n">
-        <v>8</v>
-      </c>
       <c r="I205" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J205" t="n">
         <v>1</v>
@@ -10517,10 +10517,10 @@
         <v>2</v>
       </c>
       <c r="I206" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J206" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K206" t="n">
         <v>2</v>
@@ -10557,13 +10557,13 @@
         <v>0</v>
       </c>
       <c r="F207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G207" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I207" t="n">
         <v>1</v>
@@ -10606,16 +10606,16 @@
         <v>0</v>
       </c>
       <c r="F208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G208" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H208" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J208" t="n">
         <v>1</v>
@@ -10655,13 +10655,13 @@
         <v>1</v>
       </c>
       <c r="F209" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G209" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H209" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I209" t="n">
         <v>1</v>
@@ -10701,19 +10701,19 @@
         <v>0</v>
       </c>
       <c r="E210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F210" t="n">
         <v>1</v>
       </c>
       <c r="G210" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H210" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J210" t="n">
         <v>1</v>
@@ -10750,28 +10750,28 @@
         <v>0</v>
       </c>
       <c r="E211" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F211" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G211" t="n">
         <v>12</v>
       </c>
       <c r="H211" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I211" t="n">
         <v>1</v>
       </c>
       <c r="J211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K211" t="n">
         <v>0</v>
       </c>
       <c r="L211" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M211" t="n">
         <v>24</v>
@@ -10848,16 +10848,16 @@
         <v>2</v>
       </c>
       <c r="E213" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F213" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G213" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I213" t="n">
         <v>1</v>
@@ -10946,22 +10946,22 @@
         <v>0</v>
       </c>
       <c r="E215" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F215" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G215" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H215" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I215" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J215" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K215" t="n">
         <v>1</v>
@@ -10995,19 +10995,19 @@
         <v>0</v>
       </c>
       <c r="E216" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F216" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G216" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H216" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I216" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J216" t="n">
         <v>2</v>
@@ -11047,10 +11047,10 @@
         <v>0</v>
       </c>
       <c r="F217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -11084,31 +11084,31 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C218" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D218" t="n">
         <v>2</v>
       </c>
       <c r="E218" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F218" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G218" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H218" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I218" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J218" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K218" t="n">
         <v>0</v>
@@ -11139,28 +11139,28 @@
         <v>0</v>
       </c>
       <c r="D219" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E219" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F219" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G219" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H219" t="n">
         <v>3</v>
       </c>
       <c r="I219" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J219" t="n">
         <v>1</v>
       </c>
       <c r="K219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L219" t="n">
         <v>0</v>
@@ -11191,13 +11191,13 @@
         <v>0</v>
       </c>
       <c r="E220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F220" t="n">
         <v>0</v>
       </c>
       <c r="G220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -11280,31 +11280,31 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C222" t="n">
         <v>0</v>
       </c>
       <c r="D222" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E222" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F222" t="n">
         <v>5</v>
       </c>
       <c r="G222" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H222" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I222" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J222" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K222" t="n">
         <v>1</v>
@@ -11338,22 +11338,22 @@
         <v>1</v>
       </c>
       <c r="E223" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F223" t="n">
         <v>4</v>
       </c>
       <c r="G223" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H223" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I223" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J223" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K223" t="n">
         <v>0</v>
@@ -11381,19 +11381,19 @@
         <v>0</v>
       </c>
       <c r="C224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E224" t="n">
+        <v>9</v>
+      </c>
+      <c r="F224" t="n">
         <v>5</v>
       </c>
-      <c r="F224" t="n">
-        <v>2</v>
-      </c>
       <c r="G224" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H224" t="n">
         <v>2</v>
@@ -11402,7 +11402,7 @@
         <v>2</v>
       </c>
       <c r="J224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K224" t="n">
         <v>1</v>
@@ -11436,19 +11436,19 @@
         <v>0</v>
       </c>
       <c r="E225" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F225" t="n">
         <v>4</v>
       </c>
       <c r="G225" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H225" t="n">
         <v>6</v>
       </c>
       <c r="I225" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J225" t="n">
         <v>1</v>
@@ -11476,7 +11476,7 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C226" t="n">
         <v>3</v>
@@ -11485,13 +11485,13 @@
         <v>3</v>
       </c>
       <c r="E226" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F226" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G226" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -11577,22 +11577,22 @@
         <v>3</v>
       </c>
       <c r="C228" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D228" t="n">
         <v>2</v>
       </c>
       <c r="E228" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F228" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G228" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H228" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I228" t="n">
         <v>4</v>
@@ -11607,7 +11607,7 @@
         <v>0</v>
       </c>
       <c r="M228" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N228" t="n">
         <v>47</v>
@@ -11632,22 +11632,22 @@
         <v>0</v>
       </c>
       <c r="E229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F229" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G229" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H229" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I229" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J229" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K229" t="n">
         <v>1</v>
@@ -11672,7 +11672,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C230" t="n">
         <v>0</v>
@@ -11681,22 +11681,22 @@
         <v>0</v>
       </c>
       <c r="E230" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F230" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G230" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H230" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I230" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J230" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K230" t="n">
         <v>0</v>
@@ -11721,28 +11721,28 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C231" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D231" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E231" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F231" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G231" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H231" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I231" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J231" t="n">
         <v>2</v>
@@ -11785,10 +11785,10 @@
         <v>0</v>
       </c>
       <c r="G232" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I232" t="n">
         <v>0</v>
@@ -11819,7 +11819,7 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C233" t="n">
         <v>1</v>
@@ -11828,16 +11828,16 @@
         <v>4</v>
       </c>
       <c r="E233" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F233" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G233" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H233" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I233" t="n">
         <v>3</v>
@@ -11874,25 +11874,25 @@
         <v>1</v>
       </c>
       <c r="D234" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E234" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F234" t="n">
         <v>8</v>
       </c>
       <c r="G234" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H234" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I234" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J234" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K234" t="n">
         <v>1</v>
@@ -11920,28 +11920,28 @@
         <v>5</v>
       </c>
       <c r="C235" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E235" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F235" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G235" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="H235" t="n">
         <v>5</v>
       </c>
       <c r="I235" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J235" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K235" t="n">
         <v>1</v>
@@ -11966,37 +11966,37 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C236" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D236" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E236" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F236" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G236" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="H236" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I236" t="n">
         <v>8</v>
       </c>
       <c r="J236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K236" t="n">
         <v>0</v>
       </c>
       <c r="L236" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M236" t="n">
         <v>187</v>
@@ -12015,28 +12015,28 @@
         </is>
       </c>
       <c r="B237" t="n">
+        <v>6</v>
+      </c>
+      <c r="C237" t="n">
+        <v>6</v>
+      </c>
+      <c r="D237" t="n">
         <v>5</v>
       </c>
-      <c r="C237" t="n">
-        <v>7</v>
-      </c>
-      <c r="D237" t="n">
-        <v>6</v>
-      </c>
       <c r="E237" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F237" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G237" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H237" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I237" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -12048,7 +12048,7 @@
         <v>1</v>
       </c>
       <c r="M237" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N237" t="n">
         <v>94</v>
@@ -12064,25 +12064,25 @@
         </is>
       </c>
       <c r="B238" t="n">
+        <v>5</v>
+      </c>
+      <c r="C238" t="n">
+        <v>9</v>
+      </c>
+      <c r="D238" t="n">
         <v>8</v>
       </c>
-      <c r="C238" t="n">
-        <v>10</v>
-      </c>
-      <c r="D238" t="n">
-        <v>12</v>
-      </c>
       <c r="E238" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F238" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G238" t="n">
         <v>24</v>
       </c>
       <c r="H238" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I238" t="n">
         <v>3</v>
@@ -12094,7 +12094,7 @@
         <v>0</v>
       </c>
       <c r="L238" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M238" t="n">
         <v>120</v>
@@ -12125,10 +12125,10 @@
         <v>0</v>
       </c>
       <c r="F239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -12162,34 +12162,34 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C240" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D240" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E240" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F240" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G240" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="H240" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I240" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K240" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L240" t="n">
         <v>0</v>
@@ -12217,19 +12217,19 @@
         <v>1</v>
       </c>
       <c r="D241" t="n">
+        <v>7</v>
+      </c>
+      <c r="E241" t="n">
+        <v>24</v>
+      </c>
+      <c r="F241" t="n">
+        <v>13</v>
+      </c>
+      <c r="G241" t="n">
         <v>9</v>
       </c>
-      <c r="E241" t="n">
-        <v>21</v>
-      </c>
-      <c r="F241" t="n">
-        <v>14</v>
-      </c>
-      <c r="G241" t="n">
-        <v>11</v>
-      </c>
       <c r="H241" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I241" t="n">
         <v>2</v>
@@ -12266,16 +12266,16 @@
         <v>3</v>
       </c>
       <c r="D242" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E242" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F242" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G242" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H242" t="n">
         <v>6</v>
@@ -12318,22 +12318,22 @@
         <v>2</v>
       </c>
       <c r="E243" t="n">
+        <v>8</v>
+      </c>
+      <c r="F243" t="n">
+        <v>10</v>
+      </c>
+      <c r="G243" t="n">
+        <v>9</v>
+      </c>
+      <c r="H243" t="n">
         <v>5</v>
       </c>
-      <c r="F243" t="n">
-        <v>9</v>
-      </c>
-      <c r="G243" t="n">
-        <v>15</v>
-      </c>
-      <c r="H243" t="n">
-        <v>4</v>
-      </c>
       <c r="I243" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J243" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K243" t="n">
         <v>0</v>
@@ -12367,19 +12367,19 @@
         <v>1</v>
       </c>
       <c r="E244" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F244" t="n">
+        <v>8</v>
+      </c>
+      <c r="G244" t="n">
+        <v>16</v>
+      </c>
+      <c r="H244" t="n">
         <v>5</v>
       </c>
-      <c r="G244" t="n">
-        <v>23</v>
-      </c>
-      <c r="H244" t="n">
-        <v>1</v>
-      </c>
       <c r="I244" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -12422,10 +12422,10 @@
         <v>0</v>
       </c>
       <c r="G245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I245" t="n">
         <v>0</v>
@@ -12462,31 +12462,31 @@
         <v>4</v>
       </c>
       <c r="D246" t="n">
+        <v>10</v>
+      </c>
+      <c r="E246" t="n">
+        <v>48</v>
+      </c>
+      <c r="F246" t="n">
+        <v>32</v>
+      </c>
+      <c r="G246" t="n">
+        <v>38</v>
+      </c>
+      <c r="H246" t="n">
         <v>13</v>
       </c>
-      <c r="E246" t="n">
-        <v>42</v>
-      </c>
-      <c r="F246" t="n">
-        <v>22</v>
-      </c>
-      <c r="G246" t="n">
-        <v>51</v>
-      </c>
-      <c r="H246" t="n">
-        <v>11</v>
-      </c>
       <c r="I246" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J246" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L246" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M246" t="n">
         <v>175</v>
@@ -12514,25 +12514,25 @@
         <v>2</v>
       </c>
       <c r="E247" t="n">
+        <v>6</v>
+      </c>
+      <c r="F247" t="n">
+        <v>11</v>
+      </c>
+      <c r="G247" t="n">
+        <v>12</v>
+      </c>
+      <c r="H247" t="n">
         <v>4</v>
-      </c>
-      <c r="F247" t="n">
-        <v>3</v>
-      </c>
-      <c r="G247" t="n">
-        <v>24</v>
-      </c>
-      <c r="H247" t="n">
-        <v>2</v>
       </c>
       <c r="I247" t="n">
         <v>4</v>
       </c>
       <c r="J247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L247" t="n">
         <v>0</v>
@@ -12554,28 +12554,28 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C248" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D248" t="n">
         <v>2</v>
       </c>
       <c r="E248" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F248" t="n">
         <v>3</v>
       </c>
       <c r="G248" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H248" t="n">
         <v>2</v>
       </c>
       <c r="I248" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -12609,19 +12609,19 @@
         <v>1</v>
       </c>
       <c r="D249" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E249" t="n">
         <v>10</v>
       </c>
       <c r="F249" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G249" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H249" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I249" t="n">
         <v>0</v>
@@ -12661,19 +12661,19 @@
         <v>0</v>
       </c>
       <c r="E250" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F250" t="n">
         <v>3</v>
       </c>
       <c r="G250" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H250" t="n">
         <v>4</v>
       </c>
       <c r="I250" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J250" t="n">
         <v>1</v>
@@ -12863,7 +12863,7 @@
         <v>1</v>
       </c>
       <c r="G254" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H254" t="n">
         <v>12</v>
@@ -12875,7 +12875,7 @@
         <v>6</v>
       </c>
       <c r="K254" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L254" t="n">
         <v>2</v>
@@ -12897,28 +12897,28 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C255" t="n">
         <v>3</v>
       </c>
       <c r="D255" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E255" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F255" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G255" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H255" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I255" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J255" t="n">
         <v>1</v>
@@ -12946,34 +12946,34 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C256" t="n">
+        <v>14</v>
+      </c>
+      <c r="D256" t="n">
         <v>19</v>
       </c>
-      <c r="D256" t="n">
+      <c r="E256" t="n">
+        <v>45</v>
+      </c>
+      <c r="F256" t="n">
         <v>24</v>
       </c>
-      <c r="E256" t="n">
-        <v>41</v>
-      </c>
-      <c r="F256" t="n">
-        <v>17</v>
-      </c>
       <c r="G256" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H256" t="n">
+        <v>7</v>
+      </c>
+      <c r="I256" t="n">
         <v>6</v>
       </c>
-      <c r="I256" t="n">
-        <v>5</v>
-      </c>
       <c r="J256" t="n">
         <v>2</v>
       </c>
       <c r="K256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L256" t="n">
         <v>5</v>
@@ -13001,19 +13001,19 @@
         <v>0</v>
       </c>
       <c r="D257" t="n">
+        <v>3</v>
+      </c>
+      <c r="E257" t="n">
+        <v>5</v>
+      </c>
+      <c r="F257" t="n">
+        <v>11</v>
+      </c>
+      <c r="G257" t="n">
+        <v>24</v>
+      </c>
+      <c r="H257" t="n">
         <v>4</v>
-      </c>
-      <c r="E257" t="n">
-        <v>2</v>
-      </c>
-      <c r="F257" t="n">
-        <v>7</v>
-      </c>
-      <c r="G257" t="n">
-        <v>28</v>
-      </c>
-      <c r="H257" t="n">
-        <v>6</v>
       </c>
       <c r="I257" t="n">
         <v>3</v>
@@ -13142,40 +13142,40 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C260" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D260" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E260" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F260" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G260" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H260" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I260" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J260" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K260" t="n">
         <v>3</v>
       </c>
       <c r="L260" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M260" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="N260" t="n">
         <v>295</v>
@@ -13191,40 +13191,40 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>797</v>
+        <v>784</v>
       </c>
       <c r="C261" t="n">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D261" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="E261" t="n">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="F261" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G261" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H261" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I261" t="n">
         <v>3</v>
       </c>
       <c r="J261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K261" t="n">
         <v>0</v>
       </c>
       <c r="L261" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M261" t="n">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="N261" t="n">
         <v>1170</v>
@@ -13240,19 +13240,19 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C262" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D262" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E262" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F262" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G262" t="n">
         <v>15</v>
@@ -13289,22 +13289,22 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C263" t="n">
+        <v>10</v>
+      </c>
+      <c r="D263" t="n">
+        <v>14</v>
+      </c>
+      <c r="E263" t="n">
+        <v>27</v>
+      </c>
+      <c r="F263" t="n">
         <v>12</v>
       </c>
-      <c r="D263" t="n">
-        <v>19</v>
-      </c>
-      <c r="E263" t="n">
-        <v>18</v>
-      </c>
-      <c r="F263" t="n">
-        <v>11</v>
-      </c>
       <c r="G263" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H263" t="n">
         <v>2</v>
@@ -13322,7 +13322,7 @@
         <v>8</v>
       </c>
       <c r="M263" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N263" t="n">
         <v>173</v>
@@ -13338,25 +13338,25 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C264" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D264" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E264" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F264" t="n">
         <v>8</v>
       </c>
       <c r="G264" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H264" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I264" t="n">
         <v>2</v>
@@ -13371,7 +13371,7 @@
         <v>1</v>
       </c>
       <c r="M264" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N264" t="n">
         <v>191</v>
@@ -13387,37 +13387,37 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C265" t="n">
         <v>11</v>
       </c>
       <c r="D265" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E265" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F265" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G265" t="n">
         <v>29</v>
       </c>
       <c r="H265" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I265" t="n">
         <v>1</v>
       </c>
       <c r="J265" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K265" t="n">
         <v>0</v>
       </c>
       <c r="L265" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M265" t="n">
         <v>268</v>
@@ -13436,22 +13436,22 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C266" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D266" t="n">
         <v>2</v>
       </c>
       <c r="E266" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F266" t="n">
         <v>0</v>
       </c>
       <c r="G266" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H266" t="n">
         <v>1</v>
@@ -13485,25 +13485,25 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C267" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D267" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E267" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F267" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G267" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H267" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I267" t="n">
         <v>3</v>
@@ -13537,25 +13537,25 @@
         <v>5</v>
       </c>
       <c r="C268" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D268" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E268" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F268" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G268" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H268" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I268" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J268" t="n">
         <v>1</v>
@@ -13595,19 +13595,19 @@
         <v>0</v>
       </c>
       <c r="F269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G269" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H269" t="n">
         <v>2</v>
       </c>
       <c r="I269" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J269" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K269" t="n">
         <v>0</v>
@@ -13641,19 +13641,19 @@
         <v>2</v>
       </c>
       <c r="E270" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F270" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G270" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H270" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J270" t="n">
         <v>1</v>
@@ -13662,7 +13662,7 @@
         <v>0</v>
       </c>
       <c r="L270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M270" t="n">
         <v>64</v>
@@ -13684,34 +13684,34 @@
         <v>2</v>
       </c>
       <c r="C271" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D271" t="n">
         <v>3</v>
       </c>
       <c r="E271" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F271" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G271" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H271" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I271" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K271" t="n">
         <v>0</v>
       </c>
       <c r="L271" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M271" t="n">
         <v>49</v>
@@ -13828,37 +13828,37 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C274" t="n">
         <v>6</v>
       </c>
       <c r="D274" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E274" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F274" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G274" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H274" t="n">
         <v>4</v>
       </c>
       <c r="I274" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K274" t="n">
         <v>0</v>
       </c>
       <c r="L274" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M274" t="n">
         <v>228</v>
@@ -13877,25 +13877,25 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C275" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D275" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E275" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F275" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G275" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H275" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I275" t="n">
         <v>2</v>
@@ -13907,10 +13907,10 @@
         <v>1</v>
       </c>
       <c r="L275" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M275" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N275" t="n">
         <v>271</v>
@@ -13926,31 +13926,31 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C276" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D276" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E276" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F276" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G276" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H276" t="n">
+        <v>2</v>
+      </c>
+      <c r="I276" t="n">
         <v>4</v>
       </c>
-      <c r="I276" t="n">
-        <v>2</v>
-      </c>
       <c r="J276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K276" t="n">
         <v>0</v>
@@ -13975,31 +13975,31 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C277" t="n">
         <v>9</v>
       </c>
       <c r="D277" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E277" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F277" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G277" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H277" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I277" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K277" t="n">
         <v>0</v>
@@ -14030,22 +14030,22 @@
         <v>2</v>
       </c>
       <c r="D278" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E278" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F278" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G278" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H278" t="n">
         <v>3</v>
       </c>
       <c r="I278" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J278" t="n">
         <v>0</v>
@@ -14057,7 +14057,7 @@
         <v>27</v>
       </c>
       <c r="M278" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N278" t="n">
         <v>93</v>
@@ -14091,10 +14091,10 @@
         <v>0</v>
       </c>
       <c r="H279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J279" t="n">
         <v>0</v>
@@ -14122,40 +14122,40 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C280" t="n">
         <v>2</v>
       </c>
       <c r="D280" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E280" t="n">
         <v>9</v>
       </c>
       <c r="F280" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G280" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H280" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I280" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J280" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L280" t="n">
         <v>9</v>
       </c>
       <c r="M280" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N280" t="n">
         <v>143</v>
@@ -14171,37 +14171,37 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C281" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D281" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E281" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F281" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G281" t="n">
         <v>14</v>
       </c>
       <c r="H281" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I281" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J281" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K281" t="n">
         <v>2</v>
       </c>
       <c r="L281" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M281" t="n">
         <v>155</v>
@@ -14229,19 +14229,19 @@
         <v>10</v>
       </c>
       <c r="E282" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F282" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G282" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H282" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J282" t="n">
         <v>0</v>
@@ -14253,7 +14253,7 @@
         <v>32</v>
       </c>
       <c r="M282" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N282" t="n">
         <v>101</v>
@@ -14272,16 +14272,16 @@
         <v>49</v>
       </c>
       <c r="C283" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D283" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E283" t="n">
         <v>9</v>
       </c>
       <c r="F283" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G283" t="n">
         <v>9</v>
@@ -14318,28 +14318,28 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C284" t="n">
         <v>0</v>
       </c>
       <c r="D284" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E284" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F284" t="n">
         <v>10</v>
       </c>
       <c r="G284" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H284" t="n">
         <v>3</v>
       </c>
       <c r="I284" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J284" t="n">
         <v>1</v>
@@ -14348,7 +14348,7 @@
         <v>1</v>
       </c>
       <c r="L284" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M284" t="n">
         <v>94</v>
@@ -14373,22 +14373,22 @@
         <v>4</v>
       </c>
       <c r="D285" t="n">
+        <v>3</v>
+      </c>
+      <c r="E285" t="n">
+        <v>19</v>
+      </c>
+      <c r="F285" t="n">
+        <v>18</v>
+      </c>
+      <c r="G285" t="n">
+        <v>23</v>
+      </c>
+      <c r="H285" t="n">
         <v>4</v>
       </c>
-      <c r="E285" t="n">
-        <v>17</v>
-      </c>
-      <c r="F285" t="n">
-        <v>17</v>
-      </c>
-      <c r="G285" t="n">
-        <v>26</v>
-      </c>
-      <c r="H285" t="n">
-        <v>2</v>
-      </c>
       <c r="I285" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J285" t="n">
         <v>0</v>
@@ -14416,25 +14416,25 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C286" t="n">
         <v>13</v>
       </c>
       <c r="D286" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E286" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F286" t="n">
+        <v>14</v>
+      </c>
+      <c r="G286" t="n">
         <v>13</v>
       </c>
-      <c r="G286" t="n">
-        <v>12</v>
-      </c>
       <c r="H286" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I286" t="n">
         <v>3</v>
@@ -14446,7 +14446,7 @@
         <v>1</v>
       </c>
       <c r="L286" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M286" t="n">
         <v>291</v>
@@ -14474,7 +14474,7 @@
         <v>0</v>
       </c>
       <c r="E287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F287" t="n">
         <v>0</v>
@@ -14486,10 +14486,10 @@
         <v>0</v>
       </c>
       <c r="I287" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J287" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K287" t="n">
         <v>1</v>
@@ -14523,16 +14523,16 @@
         <v>0</v>
       </c>
       <c r="E288" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F288" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G288" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H288" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I288" t="n">
         <v>3</v>
@@ -14569,22 +14569,22 @@
         <v>1</v>
       </c>
       <c r="D289" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E289" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F289" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G289" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H289" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I289" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J289" t="n">
         <v>0</v>
@@ -14593,7 +14593,7 @@
         <v>1</v>
       </c>
       <c r="L289" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M289" t="n">
         <v>100</v>
@@ -14612,37 +14612,37 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C290" t="n">
+        <v>8</v>
+      </c>
+      <c r="D290" t="n">
         <v>11</v>
       </c>
-      <c r="D290" t="n">
-        <v>14</v>
-      </c>
       <c r="E290" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F290" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G290" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H290" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I290" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K290" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L290" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M290" t="n">
         <v>302</v>
@@ -14661,25 +14661,25 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C291" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D291" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E291" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F291" t="n">
+        <v>7</v>
+      </c>
+      <c r="G291" t="n">
         <v>11</v>
       </c>
-      <c r="G291" t="n">
-        <v>12</v>
-      </c>
       <c r="H291" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I291" t="n">
         <v>1</v>
@@ -14725,7 +14725,7 @@
         <v>0</v>
       </c>
       <c r="G292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H292" t="n">
         <v>1</v>
@@ -14734,7 +14734,7 @@
         <v>2</v>
       </c>
       <c r="J292" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K292" t="n">
         <v>0</v>
@@ -14774,7 +14774,7 @@
         <v>0</v>
       </c>
       <c r="G293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H293" t="n">
         <v>2</v>
@@ -14783,7 +14783,7 @@
         <v>1</v>
       </c>
       <c r="J293" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K293" t="n">
         <v>0</v>
@@ -14826,10 +14826,10 @@
         <v>0</v>
       </c>
       <c r="H294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J294" t="n">
         <v>0</v>
@@ -14869,13 +14869,13 @@
         <v>30</v>
       </c>
       <c r="F295" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G295" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H295" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I295" t="n">
         <v>6</v>
@@ -14887,7 +14887,7 @@
         <v>0</v>
       </c>
       <c r="L295" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M295" t="n">
         <v>134</v>
@@ -14912,19 +14912,19 @@
         <v>1</v>
       </c>
       <c r="D296" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E296" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F296" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G296" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H296" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I296" t="n">
         <v>3</v>
@@ -14936,7 +14936,7 @@
         <v>0</v>
       </c>
       <c r="L296" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M296" t="n">
         <v>122</v>
@@ -14964,28 +14964,28 @@
         <v>0</v>
       </c>
       <c r="E297" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F297" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G297" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H297" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I297" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K297" t="n">
         <v>1</v>
       </c>
       <c r="L297" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M297" t="n">
         <v>46</v>
@@ -15071,10 +15071,10 @@
         <v>0</v>
       </c>
       <c r="H299" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J299" t="n">
         <v>1</v>
@@ -15157,13 +15157,13 @@
         <v>0</v>
       </c>
       <c r="D301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E301" t="n">
         <v>0</v>
       </c>
       <c r="F301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G301" t="n">
         <v>0</v>
@@ -15258,28 +15258,28 @@
         <v>0</v>
       </c>
       <c r="E303" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F303" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G303" t="n">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="H303" t="n">
+        <v>20</v>
+      </c>
+      <c r="I303" t="n">
+        <v>20</v>
+      </c>
+      <c r="J303" t="n">
+        <v>2</v>
+      </c>
+      <c r="K303" t="n">
+        <v>3</v>
+      </c>
+      <c r="L303" t="n">
         <v>15</v>
-      </c>
-      <c r="I303" t="n">
-        <v>11</v>
-      </c>
-      <c r="J303" t="n">
-        <v>3</v>
-      </c>
-      <c r="K303" t="n">
-        <v>5</v>
-      </c>
-      <c r="L303" t="n">
-        <v>17</v>
       </c>
       <c r="M303" t="n">
         <v>158</v>
@@ -15298,7 +15298,7 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C304" t="n">
         <v>0</v>
@@ -15307,22 +15307,22 @@
         <v>0</v>
       </c>
       <c r="E304" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F304" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G304" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H304" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I304" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J304" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K304" t="n">
         <v>0</v>
@@ -15356,19 +15356,19 @@
         <v>0</v>
       </c>
       <c r="E305" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F305" t="n">
+        <v>6</v>
+      </c>
+      <c r="G305" t="n">
+        <v>20</v>
+      </c>
+      <c r="H305" t="n">
         <v>5</v>
       </c>
-      <c r="G305" t="n">
-        <v>26</v>
-      </c>
-      <c r="H305" t="n">
-        <v>7</v>
-      </c>
       <c r="I305" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J305" t="n">
         <v>3</v>
@@ -15377,7 +15377,7 @@
         <v>0</v>
       </c>
       <c r="L305" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M305" t="n">
         <v>72</v>
@@ -15396,31 +15396,31 @@
         </is>
       </c>
       <c r="B306" t="n">
+        <v>5</v>
+      </c>
+      <c r="C306" t="n">
+        <v>1</v>
+      </c>
+      <c r="D306" t="n">
+        <v>2</v>
+      </c>
+      <c r="E306" t="n">
+        <v>17</v>
+      </c>
+      <c r="F306" t="n">
         <v>7</v>
       </c>
-      <c r="C306" t="n">
-        <v>3</v>
-      </c>
-      <c r="D306" t="n">
-        <v>4</v>
-      </c>
-      <c r="E306" t="n">
-        <v>12</v>
-      </c>
-      <c r="F306" t="n">
-        <v>12</v>
-      </c>
       <c r="G306" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H306" t="n">
         <v>5</v>
       </c>
       <c r="I306" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J306" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K306" t="n">
         <v>2</v>
@@ -15454,13 +15454,13 @@
         <v>0</v>
       </c>
       <c r="E307" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F307" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G307" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -15475,7 +15475,7 @@
         <v>0</v>
       </c>
       <c r="L307" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M307" t="n">
         <v>13</v>
@@ -15500,22 +15500,22 @@
         <v>0</v>
       </c>
       <c r="D308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E308" t="n">
         <v>1</v>
       </c>
       <c r="F308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G308" t="n">
         <v>1</v>
       </c>
       <c r="H308" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I308" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J308" t="n">
         <v>1</v>
@@ -15543,7 +15543,7 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C309" t="n">
         <v>0</v>
@@ -15552,22 +15552,22 @@
         <v>2</v>
       </c>
       <c r="E309" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F309" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G309" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H309" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I309" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J309" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K309" t="n">
         <v>1</v>
@@ -15598,22 +15598,22 @@
         <v>1</v>
       </c>
       <c r="D310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E310" t="n">
+        <v>14</v>
+      </c>
+      <c r="F310" t="n">
+        <v>18</v>
+      </c>
+      <c r="G310" t="n">
+        <v>57</v>
+      </c>
+      <c r="H310" t="n">
         <v>7</v>
       </c>
-      <c r="F310" t="n">
-        <v>13</v>
-      </c>
-      <c r="G310" t="n">
-        <v>71</v>
-      </c>
-      <c r="H310" t="n">
-        <v>6</v>
-      </c>
       <c r="I310" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J310" t="n">
         <v>1</v>
@@ -15656,22 +15656,22 @@
         <v>2</v>
       </c>
       <c r="G311" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H311" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I311" t="n">
         <v>1</v>
       </c>
       <c r="J311" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K311" t="n">
         <v>1</v>
       </c>
       <c r="L311" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M311" t="n">
         <v>36</v>
@@ -15690,37 +15690,37 @@
         </is>
       </c>
       <c r="B312" t="n">
+        <v>3</v>
+      </c>
+      <c r="C312" t="n">
         <v>4</v>
       </c>
-      <c r="C312" t="n">
-        <v>5</v>
-      </c>
       <c r="D312" t="n">
+        <v>9</v>
+      </c>
+      <c r="E312" t="n">
+        <v>30</v>
+      </c>
+      <c r="F312" t="n">
+        <v>29</v>
+      </c>
+      <c r="G312" t="n">
+        <v>51</v>
+      </c>
+      <c r="H312" t="n">
         <v>12</v>
       </c>
-      <c r="E312" t="n">
-        <v>22</v>
-      </c>
-      <c r="F312" t="n">
-        <v>28</v>
-      </c>
-      <c r="G312" t="n">
-        <v>57</v>
-      </c>
-      <c r="H312" t="n">
-        <v>13</v>
-      </c>
       <c r="I312" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J312" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K312" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L312" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M312" t="n">
         <v>149</v>
@@ -15739,37 +15739,37 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C313" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D313" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E313" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="F313" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G313" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H313" t="n">
         <v>18</v>
       </c>
       <c r="I313" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J313" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L313" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M313" t="n">
         <v>232</v>
@@ -15791,28 +15791,28 @@
         <v>12</v>
       </c>
       <c r="C314" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D314" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E314" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F314" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G314" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="H314" t="n">
         <v>9</v>
       </c>
       <c r="I314" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J314" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K314" t="n">
         <v>0</v>
@@ -15840,34 +15840,34 @@
         <v>10</v>
       </c>
       <c r="C315" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D315" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E315" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F315" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G315" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H315" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I315" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J315" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K315" t="n">
         <v>0</v>
       </c>
       <c r="L315" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M315" t="n">
         <v>127</v>
@@ -15889,25 +15889,25 @@
         <v>2</v>
       </c>
       <c r="C316" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D316" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E316" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F316" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G316" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H316" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I316" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J316" t="n">
         <v>1</v>
@@ -15938,28 +15938,28 @@
         <v>3</v>
       </c>
       <c r="C317" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D317" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E317" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F317" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G317" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H317" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I317" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J317" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K317" t="n">
         <v>0</v>
@@ -15990,22 +15990,22 @@
         <v>4</v>
       </c>
       <c r="D318" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E318" t="n">
+        <v>4</v>
+      </c>
+      <c r="F318" t="n">
+        <v>15</v>
+      </c>
+      <c r="G318" t="n">
+        <v>35</v>
+      </c>
+      <c r="H318" t="n">
         <v>5</v>
       </c>
-      <c r="F318" t="n">
-        <v>9</v>
-      </c>
-      <c r="G318" t="n">
-        <v>36</v>
-      </c>
-      <c r="H318" t="n">
-        <v>6</v>
-      </c>
       <c r="I318" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J318" t="n">
         <v>0</v>
@@ -16039,25 +16039,25 @@
         <v>2</v>
       </c>
       <c r="D319" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E319" t="n">
         <v>1</v>
       </c>
       <c r="F319" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G319" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H319" t="n">
         <v>4</v>
       </c>
       <c r="I319" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J319" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K319" t="n">
         <v>0</v>
@@ -16082,37 +16082,37 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C320" t="n">
         <v>1</v>
       </c>
       <c r="D320" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E320" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F320" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G320" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H320" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I320" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J320" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K320" t="n">
         <v>1</v>
       </c>
       <c r="L320" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M320" t="n">
         <v>30</v>
@@ -16140,31 +16140,31 @@
         <v>3</v>
       </c>
       <c r="E321" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F321" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G321" t="n">
         <v>4</v>
       </c>
       <c r="H321" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I321" t="n">
         <v>1</v>
       </c>
       <c r="J321" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K321" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L321" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M321" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N321" t="n">
         <v>39</v>
@@ -16192,7 +16192,7 @@
         <v>3</v>
       </c>
       <c r="F322" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G322" t="n">
         <v>5</v>
@@ -16210,7 +16210,7 @@
         <v>0</v>
       </c>
       <c r="L322" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M322" t="n">
         <v>16</v>
@@ -16235,16 +16235,16 @@
         <v>0</v>
       </c>
       <c r="D323" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E323" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F323" t="n">
         <v>2</v>
       </c>
       <c r="G323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -16259,7 +16259,7 @@
         <v>0</v>
       </c>
       <c r="L323" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M323" t="n">
         <v>13</v>
@@ -16287,19 +16287,19 @@
         <v>0</v>
       </c>
       <c r="E324" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F324" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G324" t="n">
         <v>4</v>
       </c>
       <c r="H324" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I324" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J324" t="n">
         <v>0</v>
@@ -16333,13 +16333,13 @@
         <v>0</v>
       </c>
       <c r="D325" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E325" t="n">
         <v>0</v>
       </c>
       <c r="F325" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G325" t="n">
         <v>5</v>
@@ -16388,19 +16388,19 @@
         <v>5</v>
       </c>
       <c r="F326" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G326" t="n">
         <v>6</v>
       </c>
       <c r="H326" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I326" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J326" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K326" t="n">
         <v>1</v>
@@ -16434,13 +16434,13 @@
         <v>0</v>
       </c>
       <c r="E327" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F327" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G327" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -16492,7 +16492,7 @@
         <v>1</v>
       </c>
       <c r="H328" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I328" t="n">
         <v>0</v>
@@ -16501,7 +16501,7 @@
         <v>1</v>
       </c>
       <c r="K328" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L328" t="n">
         <v>4</v>
@@ -16535,10 +16535,10 @@
         <v>0</v>
       </c>
       <c r="F329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G329" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H329" t="n">
         <v>1</v>
@@ -16581,22 +16581,22 @@
         <v>0</v>
       </c>
       <c r="E330" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F330" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G330" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H330" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I330" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J330" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K330" t="n">
         <v>1</v>
@@ -16605,13 +16605,13 @@
         <v>10</v>
       </c>
       <c r="M330" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N330" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O330" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="331">
@@ -16621,28 +16621,28 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C331" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D331" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E331" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F331" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G331" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H331" t="n">
         <v>3</v>
       </c>
       <c r="I331" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J331" t="n">
         <v>0</v>
@@ -16679,22 +16679,22 @@
         <v>2</v>
       </c>
       <c r="E332" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F332" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G332" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H332" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I332" t="n">
         <v>3</v>
       </c>
       <c r="J332" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K332" t="n">
         <v>0</v>
@@ -16731,16 +16731,16 @@
         <v>0</v>
       </c>
       <c r="F333" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G333" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H333" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I333" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J333" t="n">
         <v>0</v>
@@ -16749,7 +16749,7 @@
         <v>0</v>
       </c>
       <c r="L333" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M333" t="n">
         <v>23</v>
@@ -16768,7 +16768,7 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C334" t="n">
         <v>0</v>
@@ -16780,16 +16780,16 @@
         <v>0</v>
       </c>
       <c r="F334" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G334" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H334" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I334" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J334" t="n">
         <v>1</v>
@@ -16798,7 +16798,7 @@
         <v>0</v>
       </c>
       <c r="L334" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M334" t="n">
         <v>31</v>
@@ -16832,7 +16832,7 @@
         <v>0</v>
       </c>
       <c r="G335" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -16847,7 +16847,7 @@
         <v>0</v>
       </c>
       <c r="L335" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M335" t="n">
         <v>4</v>
@@ -16878,10 +16878,10 @@
         <v>0</v>
       </c>
       <c r="F336" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G336" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -16927,13 +16927,13 @@
         <v>0</v>
       </c>
       <c r="F337" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G337" t="n">
         <v>0</v>
       </c>
       <c r="H337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I337" t="n">
         <v>0</v>
@@ -16973,28 +16973,28 @@
         <v>0</v>
       </c>
       <c r="E338" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F338" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G338" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H338" t="n">
         <v>9</v>
       </c>
       <c r="I338" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J338" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K338" t="n">
         <v>1</v>
       </c>
       <c r="L338" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M338" t="n">
         <v>49</v>
@@ -17025,10 +17025,10 @@
         <v>0</v>
       </c>
       <c r="F339" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G339" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -17037,10 +17037,10 @@
         <v>0</v>
       </c>
       <c r="J339" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K339" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L339" t="n">
         <v>12</v>
@@ -17120,10 +17120,10 @@
         <v>0</v>
       </c>
       <c r="E341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G341" t="n">
         <v>1</v>
@@ -17166,7 +17166,7 @@
         <v>0</v>
       </c>
       <c r="D342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E342" t="n">
         <v>0</v>
@@ -17175,16 +17175,16 @@
         <v>0</v>
       </c>
       <c r="G342" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
       </c>
       <c r="I342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K342" t="n">
         <v>0</v>
@@ -17258,7 +17258,7 @@
         </is>
       </c>
       <c r="B344" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C344" t="n">
         <v>0</v>
@@ -17267,13 +17267,13 @@
         <v>0</v>
       </c>
       <c r="E344" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F344" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G344" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H344" t="n">
         <v>9</v>
@@ -17282,7 +17282,7 @@
         <v>6</v>
       </c>
       <c r="J344" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K344" t="n">
         <v>1</v>
@@ -17316,22 +17316,22 @@
         <v>0</v>
       </c>
       <c r="E345" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F345" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G345" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H345" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I345" t="n">
         <v>3</v>
       </c>
       <c r="J345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K345" t="n">
         <v>0</v>
@@ -17365,7 +17365,7 @@
         <v>0</v>
       </c>
       <c r="E346" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F346" t="n">
         <v>4</v>
@@ -17374,7 +17374,7 @@
         <v>21</v>
       </c>
       <c r="H346" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I346" t="n">
         <v>5</v>
@@ -17386,7 +17386,7 @@
         <v>0</v>
       </c>
       <c r="L346" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M346" t="n">
         <v>51</v>
@@ -17414,13 +17414,13 @@
         <v>0</v>
       </c>
       <c r="E347" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F347" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G347" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H347" t="n">
         <v>1</v>
@@ -17435,7 +17435,7 @@
         <v>0</v>
       </c>
       <c r="L347" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M347" t="n">
         <v>24</v>
@@ -17457,28 +17457,28 @@
         <v>1</v>
       </c>
       <c r="C348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E348" t="n">
         <v>1</v>
       </c>
       <c r="F348" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G348" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H348" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I348" t="n">
         <v>1</v>
       </c>
       <c r="J348" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K348" t="n">
         <v>0</v>
@@ -17512,19 +17512,19 @@
         <v>0</v>
       </c>
       <c r="E349" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F349" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G349" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H349" t="n">
         <v>3</v>
       </c>
       <c r="I349" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J349" t="n">
         <v>1</v>
@@ -17533,7 +17533,7 @@
         <v>0</v>
       </c>
       <c r="L349" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M349" t="n">
         <v>30</v>
@@ -17567,13 +17567,13 @@
         <v>0</v>
       </c>
       <c r="G350" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H350" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I350" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J350" t="n">
         <v>0</v>
@@ -17613,16 +17613,16 @@
         <v>2</v>
       </c>
       <c r="F351" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G351" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H351" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I351" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J351" t="n">
         <v>0</v>
@@ -17631,7 +17631,7 @@
         <v>1</v>
       </c>
       <c r="L351" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M351" t="n">
         <v>46</v>
@@ -17650,37 +17650,37 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C352" t="n">
         <v>0</v>
       </c>
       <c r="D352" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E352" t="n">
         <v>1</v>
       </c>
       <c r="F352" t="n">
+        <v>9</v>
+      </c>
+      <c r="G352" t="n">
+        <v>20</v>
+      </c>
+      <c r="H352" t="n">
         <v>5</v>
       </c>
-      <c r="G352" t="n">
-        <v>13</v>
-      </c>
-      <c r="H352" t="n">
-        <v>3</v>
-      </c>
       <c r="I352" t="n">
+        <v>3</v>
+      </c>
+      <c r="J352" t="n">
+        <v>3</v>
+      </c>
+      <c r="K352" t="n">
+        <v>0</v>
+      </c>
+      <c r="L352" t="n">
         <v>4</v>
-      </c>
-      <c r="J352" t="n">
-        <v>2</v>
-      </c>
-      <c r="K352" t="n">
-        <v>0</v>
-      </c>
-      <c r="L352" t="n">
-        <v>14</v>
       </c>
       <c r="M352" t="n">
         <v>46</v>
@@ -17711,25 +17711,25 @@
         <v>2</v>
       </c>
       <c r="F353" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G353" t="n">
+        <v>18</v>
+      </c>
+      <c r="H353" t="n">
+        <v>3</v>
+      </c>
+      <c r="I353" t="n">
+        <v>3</v>
+      </c>
+      <c r="J353" t="n">
+        <v>3</v>
+      </c>
+      <c r="K353" t="n">
+        <v>0</v>
+      </c>
+      <c r="L353" t="n">
         <v>12</v>
-      </c>
-      <c r="H353" t="n">
-        <v>1</v>
-      </c>
-      <c r="I353" t="n">
-        <v>3</v>
-      </c>
-      <c r="J353" t="n">
-        <v>2</v>
-      </c>
-      <c r="K353" t="n">
-        <v>1</v>
-      </c>
-      <c r="L353" t="n">
-        <v>22</v>
       </c>
       <c r="M353" t="n">
         <v>44</v>
@@ -17748,13 +17748,13 @@
         </is>
       </c>
       <c r="B354" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C354" t="n">
         <v>0</v>
       </c>
       <c r="D354" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E354" t="n">
         <v>2</v>
@@ -17763,22 +17763,22 @@
         <v>2</v>
       </c>
       <c r="G354" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H354" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I354" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J354" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K354" t="n">
         <v>0</v>
       </c>
       <c r="L354" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M354" t="n">
         <v>41</v>
@@ -17803,19 +17803,19 @@
         <v>0</v>
       </c>
       <c r="D355" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E355" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F355" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G355" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H355" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I355" t="n">
         <v>4</v>
@@ -17827,7 +17827,7 @@
         <v>1</v>
       </c>
       <c r="L355" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M355" t="n">
         <v>23</v>
@@ -17852,31 +17852,31 @@
         <v>0</v>
       </c>
       <c r="D356" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F356" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G356" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H356" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I356" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J356" t="n">
         <v>2</v>
       </c>
       <c r="K356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L356" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="M356" t="n">
         <v>44</v>
@@ -17910,22 +17910,22 @@
         <v>0</v>
       </c>
       <c r="G357" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H357" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I357" t="n">
         <v>1</v>
       </c>
       <c r="J357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K357" t="n">
         <v>0</v>
       </c>
       <c r="L357" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M357" t="n">
         <v>8</v>
@@ -17944,37 +17944,37 @@
         </is>
       </c>
       <c r="B358" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C358" t="n">
         <v>0</v>
       </c>
       <c r="D358" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E358" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F358" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G358" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="H358" t="n">
+        <v>8</v>
+      </c>
+      <c r="I358" t="n">
         <v>6</v>
       </c>
-      <c r="I358" t="n">
-        <v>8</v>
-      </c>
       <c r="J358" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L358" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="M358" t="n">
         <v>125</v>
@@ -17993,37 +17993,37 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D359" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E359" t="n">
         <v>5</v>
       </c>
       <c r="F359" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G359" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H359" t="n">
         <v>6</v>
       </c>
       <c r="I359" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J359" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K359" t="n">
         <v>0</v>
       </c>
       <c r="L359" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="M359" t="n">
         <v>91</v>
@@ -18054,10 +18054,10 @@
         <v>1</v>
       </c>
       <c r="F360" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G360" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H360" t="n">
         <v>2</v>
@@ -18091,34 +18091,34 @@
         </is>
       </c>
       <c r="B361" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C361" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D361" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E361" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F361" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G361" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H361" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I361" t="n">
         <v>1</v>
       </c>
       <c r="J361" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K361" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L361" t="n">
         <v>16</v>
@@ -18155,10 +18155,10 @@
         <v>1</v>
       </c>
       <c r="G362" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H362" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I362" t="n">
         <v>0</v>
@@ -18195,13 +18195,13 @@
         <v>0</v>
       </c>
       <c r="D363" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E363" t="n">
         <v>0</v>
       </c>
       <c r="F363" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G363" t="n">
         <v>2</v>
@@ -18244,31 +18244,31 @@
         <v>0</v>
       </c>
       <c r="D364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E364" t="n">
         <v>2</v>
       </c>
       <c r="F364" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G364" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H364" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I364" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J364" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K364" t="n">
         <v>0</v>
       </c>
       <c r="L364" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M364" t="n">
         <v>51</v>
@@ -18296,19 +18296,19 @@
         <v>0</v>
       </c>
       <c r="E365" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F365" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G365" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H365" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I365" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J365" t="n">
         <v>1</v>
@@ -18342,25 +18342,25 @@
         <v>0</v>
       </c>
       <c r="D366" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E366" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F366" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G366" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H366" t="n">
         <v>6</v>
       </c>
       <c r="I366" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J366" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K366" t="n">
         <v>1</v>
@@ -18385,46 +18385,46 @@
         </is>
       </c>
       <c r="B367" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C367" t="n">
         <v>0</v>
       </c>
       <c r="D367" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E367" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F367" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G367" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H367" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I367" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J367" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K367" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L367" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M367" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="N367" t="n">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="O367" t="n">
-        <v>1</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O367"/>
+  <dimension ref="A1:O368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18121,16 +18121,16 @@
         <v>0</v>
       </c>
       <c r="L361" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M361" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N361" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O361" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="362">
@@ -18425,6 +18425,55 @@
       </c>
       <c r="O367" t="n">
         <v>105</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>7</v>
+      </c>
+      <c r="C368" t="n">
+        <v>5</v>
+      </c>
+      <c r="D368" t="n">
+        <v>6</v>
+      </c>
+      <c r="E368" t="n">
+        <v>24</v>
+      </c>
+      <c r="F368" t="n">
+        <v>17</v>
+      </c>
+      <c r="G368" t="n">
+        <v>25</v>
+      </c>
+      <c r="H368" t="n">
+        <v>2</v>
+      </c>
+      <c r="I368" t="n">
+        <v>4</v>
+      </c>
+      <c r="J368" t="n">
+        <v>0</v>
+      </c>
+      <c r="K368" t="n">
+        <v>1</v>
+      </c>
+      <c r="L368" t="n">
+        <v>10</v>
+      </c>
+      <c r="M368" t="n">
+        <v>101</v>
+      </c>
+      <c r="N368" t="n">
+        <v>123</v>
+      </c>
+      <c r="O368" t="n">
+        <v>153</v>
       </c>
     </row>
   </sheetData>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O368"/>
+  <dimension ref="A1:O372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18476,6 +18476,202 @@
         <v>153</v>
       </c>
     </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>10</v>
+      </c>
+      <c r="C369" t="n">
+        <v>2</v>
+      </c>
+      <c r="D369" t="n">
+        <v>3</v>
+      </c>
+      <c r="E369" t="n">
+        <v>40</v>
+      </c>
+      <c r="F369" t="n">
+        <v>24</v>
+      </c>
+      <c r="G369" t="n">
+        <v>43</v>
+      </c>
+      <c r="H369" t="n">
+        <v>11</v>
+      </c>
+      <c r="I369" t="n">
+        <v>3</v>
+      </c>
+      <c r="J369" t="n">
+        <v>2</v>
+      </c>
+      <c r="K369" t="n">
+        <v>2</v>
+      </c>
+      <c r="L369" t="n">
+        <v>9</v>
+      </c>
+      <c r="M369" t="n">
+        <v>149</v>
+      </c>
+      <c r="N369" t="n">
+        <v>170</v>
+      </c>
+      <c r="O369" t="n">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>0</v>
+      </c>
+      <c r="C370" t="n">
+        <v>0</v>
+      </c>
+      <c r="D370" t="n">
+        <v>0</v>
+      </c>
+      <c r="E370" t="n">
+        <v>0</v>
+      </c>
+      <c r="F370" t="n">
+        <v>0</v>
+      </c>
+      <c r="G370" t="n">
+        <v>0</v>
+      </c>
+      <c r="H370" t="n">
+        <v>2</v>
+      </c>
+      <c r="I370" t="n">
+        <v>1</v>
+      </c>
+      <c r="J370" t="n">
+        <v>0</v>
+      </c>
+      <c r="K370" t="n">
+        <v>1</v>
+      </c>
+      <c r="L370" t="n">
+        <v>7</v>
+      </c>
+      <c r="M370" t="n">
+        <v>11</v>
+      </c>
+      <c r="N370" t="n">
+        <v>11</v>
+      </c>
+      <c r="O370" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>0</v>
+      </c>
+      <c r="C371" t="n">
+        <v>1</v>
+      </c>
+      <c r="D371" t="n">
+        <v>1</v>
+      </c>
+      <c r="E371" t="n">
+        <v>19</v>
+      </c>
+      <c r="F371" t="n">
+        <v>26</v>
+      </c>
+      <c r="G371" t="n">
+        <v>68</v>
+      </c>
+      <c r="H371" t="n">
+        <v>6</v>
+      </c>
+      <c r="I371" t="n">
+        <v>3</v>
+      </c>
+      <c r="J371" t="n">
+        <v>2</v>
+      </c>
+      <c r="K371" t="n">
+        <v>0</v>
+      </c>
+      <c r="L371" t="n">
+        <v>22</v>
+      </c>
+      <c r="M371" t="n">
+        <v>148</v>
+      </c>
+      <c r="N371" t="n">
+        <v>163</v>
+      </c>
+      <c r="O371" t="n">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>0</v>
+      </c>
+      <c r="C372" t="n">
+        <v>0</v>
+      </c>
+      <c r="D372" t="n">
+        <v>0</v>
+      </c>
+      <c r="E372" t="n">
+        <v>12</v>
+      </c>
+      <c r="F372" t="n">
+        <v>16</v>
+      </c>
+      <c r="G372" t="n">
+        <v>24</v>
+      </c>
+      <c r="H372" t="n">
+        <v>41</v>
+      </c>
+      <c r="I372" t="n">
+        <v>18</v>
+      </c>
+      <c r="J372" t="n">
+        <v>2</v>
+      </c>
+      <c r="K372" t="n">
+        <v>1</v>
+      </c>
+      <c r="L372" t="n">
+        <v>15</v>
+      </c>
+      <c r="M372" t="n">
+        <v>129</v>
+      </c>
+      <c r="N372" t="n">
+        <v>139</v>
+      </c>
+      <c r="O372" t="n">
+        <v>153</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O372"/>
+  <dimension ref="A1:O373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18672,6 +18672,55 @@
         <v>153</v>
       </c>
     </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>0</v>
+      </c>
+      <c r="C373" t="n">
+        <v>0</v>
+      </c>
+      <c r="D373" t="n">
+        <v>0</v>
+      </c>
+      <c r="E373" t="n">
+        <v>0</v>
+      </c>
+      <c r="F373" t="n">
+        <v>0</v>
+      </c>
+      <c r="G373" t="n">
+        <v>1</v>
+      </c>
+      <c r="H373" t="n">
+        <v>8</v>
+      </c>
+      <c r="I373" t="n">
+        <v>3</v>
+      </c>
+      <c r="J373" t="n">
+        <v>1</v>
+      </c>
+      <c r="K373" t="n">
+        <v>1</v>
+      </c>
+      <c r="L373" t="n">
+        <v>4</v>
+      </c>
+      <c r="M373" t="n">
+        <v>18</v>
+      </c>
+      <c r="N373" t="n">
+        <v>18</v>
+      </c>
+      <c r="O373" t="n">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -19033,37 +19033,37 @@
         <v>0</v>
       </c>
       <c r="E373">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F373">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G373">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H373">
+        <v>19</v>
+      </c>
+      <c r="I373">
         <v>8</v>
       </c>
-      <c r="I373">
-        <v>3</v>
-      </c>
       <c r="J373">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K373">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L373">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M373">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="N373">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="O373">
-        <v>18</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O373"/>
+  <dimension ref="A1:O374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18721,6 +18721,55 @@
         <v>71</v>
       </c>
     </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>2</v>
+      </c>
+      <c r="C374" t="n">
+        <v>0</v>
+      </c>
+      <c r="D374" t="n">
+        <v>2</v>
+      </c>
+      <c r="E374" t="n">
+        <v>43</v>
+      </c>
+      <c r="F374" t="n">
+        <v>34</v>
+      </c>
+      <c r="G374" t="n">
+        <v>50</v>
+      </c>
+      <c r="H374" t="n">
+        <v>15</v>
+      </c>
+      <c r="I374" t="n">
+        <v>11</v>
+      </c>
+      <c r="J374" t="n">
+        <v>4</v>
+      </c>
+      <c r="K374" t="n">
+        <v>1</v>
+      </c>
+      <c r="L374" t="n">
+        <v>21</v>
+      </c>
+      <c r="M374" t="n">
+        <v>183</v>
+      </c>
+      <c r="N374" t="n">
+        <v>217</v>
+      </c>
+      <c r="O374" t="n">
+        <v>247</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O374"/>
+  <dimension ref="A1:O375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18317,16 +18317,16 @@
         <v>0</v>
       </c>
       <c r="L365" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M365" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N365" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O365" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="366">
@@ -18385,7 +18385,7 @@
         </is>
       </c>
       <c r="B367" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C367" t="n">
         <v>0</v>
@@ -18415,16 +18415,16 @@
         <v>2</v>
       </c>
       <c r="L367" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M367" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N367" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="O367" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="368">
@@ -18434,7 +18434,7 @@
         </is>
       </c>
       <c r="B368" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C368" t="n">
         <v>5</v>
@@ -18467,13 +18467,13 @@
         <v>10</v>
       </c>
       <c r="M368" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N368" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O368" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="369">
@@ -18768,6 +18768,55 @@
       </c>
       <c r="O374" t="n">
         <v>247</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>1</v>
+      </c>
+      <c r="C375" t="n">
+        <v>1</v>
+      </c>
+      <c r="D375" t="n">
+        <v>1</v>
+      </c>
+      <c r="E375" t="n">
+        <v>30</v>
+      </c>
+      <c r="F375" t="n">
+        <v>33</v>
+      </c>
+      <c r="G375" t="n">
+        <v>50</v>
+      </c>
+      <c r="H375" t="n">
+        <v>8</v>
+      </c>
+      <c r="I375" t="n">
+        <v>12</v>
+      </c>
+      <c r="J375" t="n">
+        <v>0</v>
+      </c>
+      <c r="K375" t="n">
+        <v>0</v>
+      </c>
+      <c r="L375" t="n">
+        <v>17</v>
+      </c>
+      <c r="M375" t="n">
+        <v>153</v>
+      </c>
+      <c r="N375" t="n">
+        <v>207</v>
+      </c>
+      <c r="O375" t="n">
+        <v>230</v>
       </c>
     </row>
   </sheetData>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O375"/>
+  <dimension ref="A1:O378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12618,7 +12618,7 @@
         <v>12</v>
       </c>
       <c r="G249" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H249" t="n">
         <v>6</v>
@@ -12633,7 +12633,7 @@
         <v>1</v>
       </c>
       <c r="L249" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M249" t="n">
         <v>59</v>
@@ -12667,7 +12667,7 @@
         <v>3</v>
       </c>
       <c r="G250" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H250" t="n">
         <v>4</v>
@@ -12682,7 +12682,7 @@
         <v>1</v>
       </c>
       <c r="L250" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M250" t="n">
         <v>38</v>
@@ -15852,7 +15852,7 @@
         <v>20</v>
       </c>
       <c r="G315" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H315" t="n">
         <v>2</v>
@@ -15867,7 +15867,7 @@
         <v>0</v>
       </c>
       <c r="L315" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M315" t="n">
         <v>127</v>
@@ -15999,7 +15999,7 @@
         <v>15</v>
       </c>
       <c r="G318" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H318" t="n">
         <v>5</v>
@@ -16014,7 +16014,7 @@
         <v>0</v>
       </c>
       <c r="L318" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M318" t="n">
         <v>91</v>
@@ -16734,7 +16734,7 @@
         <v>3</v>
       </c>
       <c r="G333" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H333" t="n">
         <v>4</v>
@@ -16749,7 +16749,7 @@
         <v>0</v>
       </c>
       <c r="L333" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M333" t="n">
         <v>23</v>
@@ -16979,7 +16979,7 @@
         <v>2</v>
       </c>
       <c r="G338" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H338" t="n">
         <v>9</v>
@@ -16994,7 +16994,7 @@
         <v>1</v>
       </c>
       <c r="L338" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M338" t="n">
         <v>49</v>
@@ -17328,7 +17328,7 @@
         <v>8</v>
       </c>
       <c r="I345" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J345" t="n">
         <v>1</v>
@@ -17337,7 +17337,7 @@
         <v>0</v>
       </c>
       <c r="L345" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M345" t="n">
         <v>65</v>
@@ -18100,7 +18100,7 @@
         <v>3</v>
       </c>
       <c r="E361" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F361" t="n">
         <v>11</v>
@@ -18109,7 +18109,7 @@
         <v>18</v>
       </c>
       <c r="H361" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I361" t="n">
         <v>1</v>
@@ -18121,7 +18121,7 @@
         <v>0</v>
       </c>
       <c r="L361" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M361" t="n">
         <v>70</v>
@@ -18247,13 +18247,13 @@
         <v>0</v>
       </c>
       <c r="E364" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F364" t="n">
         <v>8</v>
       </c>
       <c r="G364" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H364" t="n">
         <v>4</v>
@@ -18268,7 +18268,7 @@
         <v>0</v>
       </c>
       <c r="L364" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M364" t="n">
         <v>51</v>
@@ -18351,7 +18351,7 @@
         <v>10</v>
       </c>
       <c r="G366" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H366" t="n">
         <v>6</v>
@@ -18366,7 +18366,7 @@
         <v>1</v>
       </c>
       <c r="L366" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M366" t="n">
         <v>82</v>
@@ -18400,7 +18400,7 @@
         <v>20</v>
       </c>
       <c r="G367" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H367" t="n">
         <v>6</v>
@@ -18415,7 +18415,7 @@
         <v>2</v>
       </c>
       <c r="L367" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M367" t="n">
         <v>78</v>
@@ -18434,7 +18434,7 @@
         </is>
       </c>
       <c r="B368" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C368" t="n">
         <v>5</v>
@@ -18464,7 +18464,7 @@
         <v>1</v>
       </c>
       <c r="L368" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M368" t="n">
         <v>100</v>
@@ -18495,13 +18495,13 @@
         <v>40</v>
       </c>
       <c r="F369" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G369" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H369" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I369" t="n">
         <v>3</v>
@@ -18513,7 +18513,7 @@
         <v>2</v>
       </c>
       <c r="L369" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M369" t="n">
         <v>149</v>
@@ -18532,7 +18532,7 @@
         </is>
       </c>
       <c r="B370" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C370" t="n">
         <v>0</v>
@@ -18562,7 +18562,7 @@
         <v>1</v>
       </c>
       <c r="L370" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M370" t="n">
         <v>11</v>
@@ -18590,16 +18590,16 @@
         <v>1</v>
       </c>
       <c r="E371" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F371" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G371" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H371" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I371" t="n">
         <v>3</v>
@@ -18611,7 +18611,7 @@
         <v>0</v>
       </c>
       <c r="L371" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="M371" t="n">
         <v>148</v>
@@ -18639,7 +18639,7 @@
         <v>0</v>
       </c>
       <c r="E372" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F372" t="n">
         <v>16</v>
@@ -18648,7 +18648,7 @@
         <v>24</v>
       </c>
       <c r="H372" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I372" t="n">
         <v>18</v>
@@ -18660,7 +18660,7 @@
         <v>1</v>
       </c>
       <c r="L372" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="M372" t="n">
         <v>129</v>
@@ -18685,7 +18685,7 @@
         <v>0</v>
       </c>
       <c r="D373" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E373" t="n">
         <v>2</v>
@@ -18697,7 +18697,7 @@
         <v>11</v>
       </c>
       <c r="H373" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I373" t="n">
         <v>8</v>
@@ -18709,7 +18709,7 @@
         <v>3</v>
       </c>
       <c r="L373" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M373" t="n">
         <v>62</v>
@@ -18783,10 +18783,10 @@
         <v>1</v>
       </c>
       <c r="D375" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E375" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F375" t="n">
         <v>33</v>
@@ -18798,16 +18798,16 @@
         <v>8</v>
       </c>
       <c r="I375" t="n">
+        <v>13</v>
+      </c>
+      <c r="J375" t="n">
+        <v>0</v>
+      </c>
+      <c r="K375" t="n">
+        <v>0</v>
+      </c>
+      <c r="L375" t="n">
         <v>12</v>
-      </c>
-      <c r="J375" t="n">
-        <v>0</v>
-      </c>
-      <c r="K375" t="n">
-        <v>0</v>
-      </c>
-      <c r="L375" t="n">
-        <v>17</v>
       </c>
       <c r="M375" t="n">
         <v>153</v>
@@ -18817,6 +18817,153 @@
       </c>
       <c r="O375" t="n">
         <v>230</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>4</v>
+      </c>
+      <c r="C376" t="n">
+        <v>1</v>
+      </c>
+      <c r="D376" t="n">
+        <v>3</v>
+      </c>
+      <c r="E376" t="n">
+        <v>25</v>
+      </c>
+      <c r="F376" t="n">
+        <v>23</v>
+      </c>
+      <c r="G376" t="n">
+        <v>36</v>
+      </c>
+      <c r="H376" t="n">
+        <v>7</v>
+      </c>
+      <c r="I376" t="n">
+        <v>8</v>
+      </c>
+      <c r="J376" t="n">
+        <v>2</v>
+      </c>
+      <c r="K376" t="n">
+        <v>0</v>
+      </c>
+      <c r="L376" t="n">
+        <v>28</v>
+      </c>
+      <c r="M376" t="n">
+        <v>137</v>
+      </c>
+      <c r="N376" t="n">
+        <v>157</v>
+      </c>
+      <c r="O376" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>2</v>
+      </c>
+      <c r="C377" t="n">
+        <v>0</v>
+      </c>
+      <c r="D377" t="n">
+        <v>1</v>
+      </c>
+      <c r="E377" t="n">
+        <v>3</v>
+      </c>
+      <c r="F377" t="n">
+        <v>7</v>
+      </c>
+      <c r="G377" t="n">
+        <v>35</v>
+      </c>
+      <c r="H377" t="n">
+        <v>11</v>
+      </c>
+      <c r="I377" t="n">
+        <v>5</v>
+      </c>
+      <c r="J377" t="n">
+        <v>2</v>
+      </c>
+      <c r="K377" t="n">
+        <v>0</v>
+      </c>
+      <c r="L377" t="n">
+        <v>19</v>
+      </c>
+      <c r="M377" t="n">
+        <v>85</v>
+      </c>
+      <c r="N377" t="n">
+        <v>87</v>
+      </c>
+      <c r="O377" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>0</v>
+      </c>
+      <c r="C378" t="n">
+        <v>0</v>
+      </c>
+      <c r="D378" t="n">
+        <v>1</v>
+      </c>
+      <c r="E378" t="n">
+        <v>16</v>
+      </c>
+      <c r="F378" t="n">
+        <v>47</v>
+      </c>
+      <c r="G378" t="n">
+        <v>112</v>
+      </c>
+      <c r="H378" t="n">
+        <v>19</v>
+      </c>
+      <c r="I378" t="n">
+        <v>9</v>
+      </c>
+      <c r="J378" t="n">
+        <v>0</v>
+      </c>
+      <c r="K378" t="n">
+        <v>1</v>
+      </c>
+      <c r="L378" t="n">
+        <v>50</v>
+      </c>
+      <c r="M378" t="n">
+        <v>255</v>
+      </c>
+      <c r="N378" t="n">
+        <v>290</v>
+      </c>
+      <c r="O378" t="n">
+        <v>311</v>
       </c>
     </row>
   </sheetData>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O378"/>
+  <dimension ref="A1:O379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,7 +512,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
@@ -530,7 +530,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>14</v>
@@ -5216,7 +5216,7 @@
         <v>1</v>
       </c>
       <c r="F98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -5234,7 +5234,7 @@
         <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M98" t="n">
         <v>13</v>
@@ -6438,7 +6438,7 @@
         <v>2</v>
       </c>
       <c r="E123" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F123" t="n">
         <v>1</v>
@@ -6459,7 +6459,7 @@
         <v>0</v>
       </c>
       <c r="L123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M123" t="n">
         <v>40</v>
@@ -6490,10 +6490,10 @@
         <v>5</v>
       </c>
       <c r="F124" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H124" t="n">
         <v>1</v>
@@ -9277,10 +9277,10 @@
         <v>13</v>
       </c>
       <c r="D181" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E181" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F181" t="n">
         <v>11</v>
@@ -11929,10 +11929,10 @@
         <v>17</v>
       </c>
       <c r="F235" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G235" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H235" t="n">
         <v>5</v>
@@ -11975,7 +11975,7 @@
         <v>5</v>
       </c>
       <c r="E236" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F236" t="n">
         <v>40</v>
@@ -11996,7 +11996,7 @@
         <v>0</v>
       </c>
       <c r="L236" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M236" t="n">
         <v>187</v>
@@ -12027,7 +12027,7 @@
         <v>19</v>
       </c>
       <c r="F237" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G237" t="n">
         <v>28</v>
@@ -12045,7 +12045,7 @@
         <v>0</v>
       </c>
       <c r="L237" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M237" t="n">
         <v>87</v>
@@ -12076,10 +12076,10 @@
         <v>35</v>
       </c>
       <c r="F238" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G238" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H238" t="n">
         <v>6</v>
@@ -12174,10 +12174,10 @@
         <v>30</v>
       </c>
       <c r="F240" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G240" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H240" t="n">
         <v>11</v>
@@ -12272,10 +12272,10 @@
         <v>17</v>
       </c>
       <c r="F242" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G242" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H242" t="n">
         <v>6</v>
@@ -12462,7 +12462,7 @@
         <v>4</v>
       </c>
       <c r="D246" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E246" t="n">
         <v>48</v>
@@ -12486,7 +12486,7 @@
         <v>0</v>
       </c>
       <c r="L246" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M246" t="n">
         <v>175</v>
@@ -12511,7 +12511,7 @@
         <v>1</v>
       </c>
       <c r="D247" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E247" t="n">
         <v>6</v>
@@ -12535,7 +12535,7 @@
         <v>1</v>
       </c>
       <c r="L247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M247" t="n">
         <v>43</v>
@@ -13203,7 +13203,7 @@
         <v>116</v>
       </c>
       <c r="F261" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G261" t="n">
         <v>55</v>
@@ -13221,7 +13221,7 @@
         <v>0</v>
       </c>
       <c r="L261" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M261" t="n">
         <v>1164</v>
@@ -13687,7 +13687,7 @@
         <v>0</v>
       </c>
       <c r="D271" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E271" t="n">
         <v>11</v>
@@ -13711,7 +13711,7 @@
         <v>0</v>
       </c>
       <c r="L271" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M271" t="n">
         <v>49</v>
@@ -13834,7 +13834,7 @@
         <v>6</v>
       </c>
       <c r="D274" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E274" t="n">
         <v>22</v>
@@ -13858,7 +13858,7 @@
         <v>0</v>
       </c>
       <c r="L274" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M274" t="n">
         <v>228</v>
@@ -13877,7 +13877,7 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C275" t="n">
         <v>10</v>
@@ -13907,7 +13907,7 @@
         <v>1</v>
       </c>
       <c r="L275" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M275" t="n">
         <v>270</v>
@@ -13932,13 +13932,13 @@
         <v>4</v>
       </c>
       <c r="D276" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E276" t="n">
         <v>23</v>
       </c>
       <c r="F276" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G276" t="n">
         <v>12</v>
@@ -14122,7 +14122,7 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C280" t="n">
         <v>2</v>
@@ -14152,7 +14152,7 @@
         <v>1</v>
       </c>
       <c r="L280" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M280" t="n">
         <v>141</v>
@@ -14171,7 +14171,7 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C281" t="n">
         <v>10</v>
@@ -14183,7 +14183,7 @@
         <v>35</v>
       </c>
       <c r="F281" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G281" t="n">
         <v>14</v>
@@ -14269,7 +14269,7 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C283" t="n">
         <v>3</v>
@@ -14299,7 +14299,7 @@
         <v>0</v>
       </c>
       <c r="L283" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M283" t="n">
         <v>102</v>
@@ -14367,7 +14367,7 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C285" t="n">
         <v>4</v>
@@ -14379,10 +14379,10 @@
         <v>19</v>
       </c>
       <c r="F285" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G285" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H285" t="n">
         <v>4</v>
@@ -14397,7 +14397,7 @@
         <v>0</v>
       </c>
       <c r="L285" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M285" t="n">
         <v>117</v>
@@ -14416,10 +14416,10 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C286" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D286" t="n">
         <v>23</v>
@@ -14428,7 +14428,7 @@
         <v>27</v>
       </c>
       <c r="F286" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G286" t="n">
         <v>13</v>
@@ -14446,7 +14446,7 @@
         <v>1</v>
       </c>
       <c r="L286" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="M286" t="n">
         <v>291</v>
@@ -14575,10 +14575,10 @@
         <v>18</v>
       </c>
       <c r="F289" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G289" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H289" t="n">
         <v>6</v>
@@ -14593,7 +14593,7 @@
         <v>1</v>
       </c>
       <c r="L289" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M289" t="n">
         <v>100</v>
@@ -14615,19 +14615,19 @@
         <v>214</v>
       </c>
       <c r="C290" t="n">
+        <v>11</v>
+      </c>
+      <c r="D290" t="n">
+        <v>12</v>
+      </c>
+      <c r="E290" t="n">
+        <v>23</v>
+      </c>
+      <c r="F290" t="n">
         <v>8</v>
       </c>
-      <c r="D290" t="n">
-        <v>11</v>
-      </c>
-      <c r="E290" t="n">
-        <v>30</v>
-      </c>
-      <c r="F290" t="n">
-        <v>6</v>
-      </c>
       <c r="G290" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H290" t="n">
         <v>5</v>
@@ -14642,7 +14642,7 @@
         <v>0</v>
       </c>
       <c r="L290" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M290" t="n">
         <v>302</v>
@@ -14664,19 +14664,19 @@
         <v>44</v>
       </c>
       <c r="C291" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D291" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E291" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F291" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G291" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H291" t="n">
         <v>5</v>
@@ -14691,7 +14691,7 @@
         <v>1</v>
       </c>
       <c r="L291" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M291" t="n">
         <v>122</v>
@@ -14826,10 +14826,10 @@
         <v>0</v>
       </c>
       <c r="H294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J294" t="n">
         <v>0</v>
@@ -14863,19 +14863,19 @@
         <v>1</v>
       </c>
       <c r="D295" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E295" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F295" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G295" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H295" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I295" t="n">
         <v>6</v>
@@ -14887,7 +14887,7 @@
         <v>0</v>
       </c>
       <c r="L295" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M295" t="n">
         <v>134</v>
@@ -14918,16 +14918,16 @@
         <v>31</v>
       </c>
       <c r="F296" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G296" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H296" t="n">
         <v>4</v>
       </c>
       <c r="I296" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J296" t="n">
         <v>2</v>
@@ -14936,7 +14936,7 @@
         <v>0</v>
       </c>
       <c r="L296" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M296" t="n">
         <v>122</v>
@@ -14955,7 +14955,7 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C297" t="n">
         <v>1</v>
@@ -14964,13 +14964,13 @@
         <v>0</v>
       </c>
       <c r="E297" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F297" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G297" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H297" t="n">
         <v>6</v>
@@ -14985,7 +14985,7 @@
         <v>1</v>
       </c>
       <c r="L297" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M297" t="n">
         <v>46</v>
@@ -15004,7 +15004,7 @@
         </is>
       </c>
       <c r="B298" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C298" t="n">
         <v>0</v>
@@ -15034,7 +15034,7 @@
         <v>0</v>
       </c>
       <c r="L298" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M298" t="n">
         <v>20</v>
@@ -15102,7 +15102,7 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C300" t="n">
         <v>0</v>
@@ -15132,7 +15132,7 @@
         <v>0</v>
       </c>
       <c r="L300" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M300" t="n">
         <v>19</v>
@@ -15151,7 +15151,7 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C301" t="n">
         <v>0</v>
@@ -15181,7 +15181,7 @@
         <v>0</v>
       </c>
       <c r="L301" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M301" t="n">
         <v>26</v>
@@ -15261,16 +15261,16 @@
         <v>9</v>
       </c>
       <c r="F303" t="n">
+        <v>16</v>
+      </c>
+      <c r="G303" t="n">
+        <v>74</v>
+      </c>
+      <c r="H303" t="n">
         <v>17</v>
       </c>
-      <c r="G303" t="n">
-        <v>69</v>
-      </c>
-      <c r="H303" t="n">
-        <v>20</v>
-      </c>
       <c r="I303" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J303" t="n">
         <v>2</v>
@@ -15279,7 +15279,7 @@
         <v>3</v>
       </c>
       <c r="L303" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M303" t="n">
         <v>158</v>
@@ -15298,7 +15298,7 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C304" t="n">
         <v>0</v>
@@ -15307,7 +15307,7 @@
         <v>0</v>
       </c>
       <c r="E304" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F304" t="n">
         <v>4</v>
@@ -15328,7 +15328,7 @@
         <v>0</v>
       </c>
       <c r="L304" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="M304" t="n">
         <v>46</v>
@@ -15359,10 +15359,10 @@
         <v>7</v>
       </c>
       <c r="F305" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G305" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H305" t="n">
         <v>5</v>
@@ -15377,7 +15377,7 @@
         <v>0</v>
       </c>
       <c r="L305" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M305" t="n">
         <v>72</v>
@@ -15396,25 +15396,25 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C306" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D306" t="n">
         <v>2</v>
       </c>
       <c r="E306" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F306" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G306" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H306" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I306" t="n">
         <v>5</v>
@@ -15426,7 +15426,7 @@
         <v>2</v>
       </c>
       <c r="L306" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="M306" t="n">
         <v>78</v>
@@ -15494,7 +15494,7 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C308" t="n">
         <v>0</v>
@@ -15524,7 +15524,7 @@
         <v>1</v>
       </c>
       <c r="L308" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M308" t="n">
         <v>15</v>
@@ -15543,7 +15543,7 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C309" t="n">
         <v>0</v>
@@ -15552,19 +15552,19 @@
         <v>2</v>
       </c>
       <c r="E309" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F309" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G309" t="n">
         <v>29</v>
       </c>
       <c r="H309" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I309" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J309" t="n">
         <v>5</v>
@@ -15573,7 +15573,7 @@
         <v>1</v>
       </c>
       <c r="L309" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M309" t="n">
         <v>78</v>
@@ -15604,7 +15604,7 @@
         <v>14</v>
       </c>
       <c r="F310" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G310" t="n">
         <v>57</v>
@@ -15622,7 +15622,7 @@
         <v>0</v>
       </c>
       <c r="L310" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M310" t="n">
         <v>109</v>
@@ -15641,7 +15641,7 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C311" t="n">
         <v>1</v>
@@ -15671,7 +15671,7 @@
         <v>1</v>
       </c>
       <c r="L311" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M311" t="n">
         <v>36</v>
@@ -15690,25 +15690,25 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C312" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D312" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E312" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F312" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G312" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H312" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I312" t="n">
         <v>6</v>
@@ -15742,19 +15742,19 @@
         <v>5</v>
       </c>
       <c r="C313" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D313" t="n">
         <v>13</v>
       </c>
       <c r="E313" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F313" t="n">
         <v>36</v>
       </c>
       <c r="G313" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H313" t="n">
         <v>18</v>
@@ -15769,7 +15769,7 @@
         <v>0</v>
       </c>
       <c r="L313" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M313" t="n">
         <v>232</v>
@@ -15788,7 +15788,7 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C314" t="n">
         <v>7</v>
@@ -15800,7 +15800,7 @@
         <v>40</v>
       </c>
       <c r="F314" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G314" t="n">
         <v>63</v>
@@ -15809,7 +15809,7 @@
         <v>9</v>
       </c>
       <c r="I314" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J314" t="n">
         <v>3</v>
@@ -15818,7 +15818,7 @@
         <v>0</v>
       </c>
       <c r="L314" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M314" t="n">
         <v>210</v>
@@ -15886,7 +15886,7 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C316" t="n">
         <v>1</v>
@@ -15895,10 +15895,10 @@
         <v>4</v>
       </c>
       <c r="E316" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F316" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G316" t="n">
         <v>22</v>
@@ -15916,7 +15916,7 @@
         <v>0</v>
       </c>
       <c r="L316" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M316" t="n">
         <v>59</v>
@@ -15935,16 +15935,16 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C317" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D317" t="n">
         <v>2</v>
       </c>
       <c r="E317" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F317" t="n">
         <v>9</v>
@@ -15965,7 +15965,7 @@
         <v>0</v>
       </c>
       <c r="L317" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M317" t="n">
         <v>82</v>
@@ -15987,10 +15987,10 @@
         <v>4</v>
       </c>
       <c r="C318" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D318" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E318" t="n">
         <v>4</v>
@@ -16014,7 +16014,7 @@
         <v>0</v>
       </c>
       <c r="L318" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M318" t="n">
         <v>91</v>
@@ -16082,7 +16082,7 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C320" t="n">
         <v>1</v>
@@ -16112,7 +16112,7 @@
         <v>1</v>
       </c>
       <c r="L320" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M320" t="n">
         <v>30</v>
@@ -16131,19 +16131,19 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C321" t="n">
         <v>1</v>
       </c>
       <c r="D321" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E321" t="n">
         <v>4</v>
       </c>
       <c r="F321" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G321" t="n">
         <v>4</v>
@@ -16161,7 +16161,7 @@
         <v>1</v>
       </c>
       <c r="L321" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M321" t="n">
         <v>32</v>
@@ -16229,7 +16229,7 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C323" t="n">
         <v>0</v>
@@ -16259,7 +16259,7 @@
         <v>0</v>
       </c>
       <c r="L323" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M323" t="n">
         <v>13</v>
@@ -16281,7 +16281,7 @@
         <v>0</v>
       </c>
       <c r="C324" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D324" t="n">
         <v>0</v>
@@ -16308,7 +16308,7 @@
         <v>0</v>
       </c>
       <c r="L324" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M324" t="n">
         <v>22</v>
@@ -16327,7 +16327,7 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C325" t="n">
         <v>0</v>
@@ -16357,7 +16357,7 @@
         <v>1</v>
       </c>
       <c r="L325" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M325" t="n">
         <v>20</v>
@@ -16425,7 +16425,7 @@
         </is>
       </c>
       <c r="B327" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C327" t="n">
         <v>0</v>
@@ -16455,7 +16455,7 @@
         <v>0</v>
       </c>
       <c r="L327" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M327" t="n">
         <v>22</v>
@@ -16474,7 +16474,7 @@
         </is>
       </c>
       <c r="B328" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C328" t="n">
         <v>0</v>
@@ -16504,7 +16504,7 @@
         <v>3</v>
       </c>
       <c r="L328" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M328" t="n">
         <v>18</v>
@@ -16768,7 +16768,7 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C334" t="n">
         <v>0</v>
@@ -16783,7 +16783,7 @@
         <v>2</v>
       </c>
       <c r="G334" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H334" t="n">
         <v>2</v>
@@ -17307,7 +17307,7 @@
         </is>
       </c>
       <c r="B345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C345" t="n">
         <v>0</v>
@@ -17322,7 +17322,7 @@
         <v>6</v>
       </c>
       <c r="G345" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H345" t="n">
         <v>8</v>
@@ -17337,7 +17337,7 @@
         <v>0</v>
       </c>
       <c r="L345" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M345" t="n">
         <v>65</v>
@@ -17417,7 +17417,7 @@
         <v>0</v>
       </c>
       <c r="F347" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G347" t="n">
         <v>7</v>
@@ -17435,7 +17435,7 @@
         <v>0</v>
       </c>
       <c r="L347" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M347" t="n">
         <v>24</v>
@@ -17466,10 +17466,10 @@
         <v>1</v>
       </c>
       <c r="F348" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G348" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H348" t="n">
         <v>6</v>
@@ -17616,10 +17616,10 @@
         <v>4</v>
       </c>
       <c r="G351" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H351" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I351" t="n">
         <v>6</v>
@@ -17861,10 +17861,10 @@
         <v>2</v>
       </c>
       <c r="G356" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H356" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I356" t="n">
         <v>6</v>
@@ -17996,7 +17996,7 @@
         <v>1</v>
       </c>
       <c r="C359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D359" t="n">
         <v>4</v>
@@ -18008,7 +18008,7 @@
         <v>18</v>
       </c>
       <c r="G359" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H359" t="n">
         <v>6</v>
@@ -18091,7 +18091,7 @@
         </is>
       </c>
       <c r="B361" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C361" t="n">
         <v>0</v>
@@ -18100,13 +18100,13 @@
         <v>3</v>
       </c>
       <c r="E361" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F361" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G361" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H361" t="n">
         <v>2</v>
@@ -18385,7 +18385,7 @@
         </is>
       </c>
       <c r="B367" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C367" t="n">
         <v>0</v>
@@ -18400,7 +18400,7 @@
         <v>20</v>
       </c>
       <c r="G367" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H367" t="n">
         <v>6</v>
@@ -18415,7 +18415,7 @@
         <v>2</v>
       </c>
       <c r="L367" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M367" t="n">
         <v>78</v>
@@ -18440,16 +18440,16 @@
         <v>5</v>
       </c>
       <c r="D368" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E368" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F368" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G368" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H368" t="n">
         <v>2</v>
@@ -18492,10 +18492,10 @@
         <v>3</v>
       </c>
       <c r="E369" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F369" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G369" t="n">
         <v>45</v>
@@ -18532,7 +18532,7 @@
         </is>
       </c>
       <c r="B370" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C370" t="n">
         <v>0</v>
@@ -18562,7 +18562,7 @@
         <v>1</v>
       </c>
       <c r="L370" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M370" t="n">
         <v>11</v>
@@ -18596,7 +18596,7 @@
         <v>28</v>
       </c>
       <c r="G371" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H371" t="n">
         <v>9</v>
@@ -18611,7 +18611,7 @@
         <v>0</v>
       </c>
       <c r="L371" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M371" t="n">
         <v>148</v>
@@ -18651,7 +18651,7 @@
         <v>44</v>
       </c>
       <c r="I372" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J372" t="n">
         <v>2</v>
@@ -18660,7 +18660,7 @@
         <v>1</v>
       </c>
       <c r="L372" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M372" t="n">
         <v>129</v>
@@ -18694,10 +18694,10 @@
         <v>3</v>
       </c>
       <c r="G373" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H373" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I373" t="n">
         <v>8</v>
@@ -18737,19 +18737,19 @@
         <v>2</v>
       </c>
       <c r="E374" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F374" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G374" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H374" t="n">
         <v>15</v>
       </c>
       <c r="I374" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J374" t="n">
         <v>4</v>
@@ -18758,7 +18758,7 @@
         <v>1</v>
       </c>
       <c r="L374" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M374" t="n">
         <v>183</v>
@@ -18777,7 +18777,7 @@
         </is>
       </c>
       <c r="B375" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C375" t="n">
         <v>1</v>
@@ -18786,7 +18786,7 @@
         <v>2</v>
       </c>
       <c r="E375" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F375" t="n">
         <v>33</v>
@@ -18807,7 +18807,7 @@
         <v>0</v>
       </c>
       <c r="L375" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M375" t="n">
         <v>153</v>
@@ -18841,10 +18841,10 @@
         <v>23</v>
       </c>
       <c r="G376" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H376" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I376" t="n">
         <v>8</v>
@@ -18936,10 +18936,10 @@
         <v>16</v>
       </c>
       <c r="F378" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G378" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H378" t="n">
         <v>19</v>
@@ -18964,6 +18964,55 @@
       </c>
       <c r="O378" t="n">
         <v>311</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>0</v>
+      </c>
+      <c r="C379" t="n">
+        <v>0</v>
+      </c>
+      <c r="D379" t="n">
+        <v>1</v>
+      </c>
+      <c r="E379" t="n">
+        <v>8</v>
+      </c>
+      <c r="F379" t="n">
+        <v>16</v>
+      </c>
+      <c r="G379" t="n">
+        <v>41</v>
+      </c>
+      <c r="H379" t="n">
+        <v>6</v>
+      </c>
+      <c r="I379" t="n">
+        <v>6</v>
+      </c>
+      <c r="J379" t="n">
+        <v>1</v>
+      </c>
+      <c r="K379" t="n">
+        <v>2</v>
+      </c>
+      <c r="L379" t="n">
+        <v>21</v>
+      </c>
+      <c r="M379" t="n">
+        <v>102</v>
+      </c>
+      <c r="N379" t="n">
+        <v>109</v>
+      </c>
+      <c r="O379" t="n">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -18973,46 +18973,46 @@
         </is>
       </c>
       <c r="B379" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C379" t="n">
         <v>0</v>
       </c>
       <c r="D379" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E379" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F379" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="G379" t="n">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="H379" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I379" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J379" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K379" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L379" t="n">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="M379" t="n">
-        <v>102</v>
+        <v>234</v>
       </c>
       <c r="N379" t="n">
-        <v>109</v>
+        <v>263</v>
       </c>
       <c r="O379" t="n">
-        <v>113</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O379"/>
+  <dimension ref="A1:O381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15999,7 +15999,7 @@
         <v>15</v>
       </c>
       <c r="G318" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H318" t="n">
         <v>5</v>
@@ -16014,7 +16014,7 @@
         <v>0</v>
       </c>
       <c r="L318" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M318" t="n">
         <v>91</v>
@@ -16639,10 +16639,10 @@
         <v>10</v>
       </c>
       <c r="H331" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I331" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J331" t="n">
         <v>0</v>
@@ -16982,7 +16982,7 @@
         <v>16</v>
       </c>
       <c r="H338" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I338" t="n">
         <v>8</v>
@@ -16994,7 +16994,7 @@
         <v>1</v>
       </c>
       <c r="L338" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M338" t="n">
         <v>49</v>
@@ -17374,10 +17374,10 @@
         <v>21</v>
       </c>
       <c r="H346" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I346" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J346" t="n">
         <v>2</v>
@@ -17472,10 +17472,10 @@
         <v>27</v>
       </c>
       <c r="H348" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I348" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J348" t="n">
         <v>2</v>
@@ -18103,10 +18103,10 @@
         <v>21</v>
       </c>
       <c r="F361" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G361" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H361" t="n">
         <v>2</v>
@@ -18397,10 +18397,10 @@
         <v>10</v>
       </c>
       <c r="F367" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G367" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H367" t="n">
         <v>6</v>
@@ -18492,16 +18492,16 @@
         <v>3</v>
       </c>
       <c r="E369" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F369" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G369" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H369" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I369" t="n">
         <v>3</v>
@@ -18550,10 +18550,10 @@
         <v>0</v>
       </c>
       <c r="H370" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I370" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J370" t="n">
         <v>0</v>
@@ -18587,22 +18587,22 @@
         <v>1</v>
       </c>
       <c r="D371" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E371" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F371" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G371" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H371" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I371" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J371" t="n">
         <v>2</v>
@@ -18642,13 +18642,13 @@
         <v>15</v>
       </c>
       <c r="F372" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G372" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H372" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I372" t="n">
         <v>17</v>
@@ -18694,13 +18694,13 @@
         <v>3</v>
       </c>
       <c r="G373" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H373" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I373" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J373" t="n">
         <v>4</v>
@@ -18709,7 +18709,7 @@
         <v>3</v>
       </c>
       <c r="L373" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M373" t="n">
         <v>62</v>
@@ -18740,16 +18740,16 @@
         <v>45</v>
       </c>
       <c r="F374" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G374" t="n">
         <v>51</v>
       </c>
       <c r="H374" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I374" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J374" t="n">
         <v>4</v>
@@ -18789,16 +18789,16 @@
         <v>35</v>
       </c>
       <c r="F375" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G375" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H375" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I375" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J375" t="n">
         <v>0</v>
@@ -18835,16 +18835,16 @@
         <v>3</v>
       </c>
       <c r="E376" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F376" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G376" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H376" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I376" t="n">
         <v>8</v>
@@ -18856,7 +18856,7 @@
         <v>0</v>
       </c>
       <c r="L376" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M376" t="n">
         <v>137</v>
@@ -18884,13 +18884,13 @@
         <v>1</v>
       </c>
       <c r="E377" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F377" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G377" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H377" t="n">
         <v>11</v>
@@ -18905,16 +18905,16 @@
         <v>0</v>
       </c>
       <c r="L377" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M377" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N377" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O377" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="378">
@@ -18933,13 +18933,13 @@
         <v>1</v>
       </c>
       <c r="E378" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F378" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G378" t="n">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="H378" t="n">
         <v>19</v>
@@ -18948,13 +18948,13 @@
         <v>9</v>
       </c>
       <c r="J378" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K378" t="n">
         <v>1</v>
       </c>
       <c r="L378" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="M378" t="n">
         <v>255</v>
@@ -18976,25 +18976,25 @@
         <v>2</v>
       </c>
       <c r="C379" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D379" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E379" t="n">
         <v>31</v>
       </c>
       <c r="F379" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G379" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H379" t="n">
         <v>13</v>
       </c>
       <c r="I379" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J379" t="n">
         <v>3</v>
@@ -19003,7 +19003,7 @@
         <v>3</v>
       </c>
       <c r="L379" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="M379" t="n">
         <v>234</v>
@@ -19013,6 +19013,104 @@
       </c>
       <c r="O379" t="n">
         <v>281</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>2</v>
+      </c>
+      <c r="C380" t="n">
+        <v>1</v>
+      </c>
+      <c r="D380" t="n">
+        <v>0</v>
+      </c>
+      <c r="E380" t="n">
+        <v>13</v>
+      </c>
+      <c r="F380" t="n">
+        <v>20</v>
+      </c>
+      <c r="G380" t="n">
+        <v>40</v>
+      </c>
+      <c r="H380" t="n">
+        <v>5</v>
+      </c>
+      <c r="I380" t="n">
+        <v>3</v>
+      </c>
+      <c r="J380" t="n">
+        <v>0</v>
+      </c>
+      <c r="K380" t="n">
+        <v>0</v>
+      </c>
+      <c r="L380" t="n">
+        <v>48</v>
+      </c>
+      <c r="M380" t="n">
+        <v>132</v>
+      </c>
+      <c r="N380" t="n">
+        <v>154</v>
+      </c>
+      <c r="O380" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>1</v>
+      </c>
+      <c r="C381" t="n">
+        <v>1</v>
+      </c>
+      <c r="D381" t="n">
+        <v>0</v>
+      </c>
+      <c r="E381" t="n">
+        <v>25</v>
+      </c>
+      <c r="F381" t="n">
+        <v>25</v>
+      </c>
+      <c r="G381" t="n">
+        <v>20</v>
+      </c>
+      <c r="H381" t="n">
+        <v>3</v>
+      </c>
+      <c r="I381" t="n">
+        <v>2</v>
+      </c>
+      <c r="J381" t="n">
+        <v>0</v>
+      </c>
+      <c r="K381" t="n">
+        <v>0</v>
+      </c>
+      <c r="L381" t="n">
+        <v>26</v>
+      </c>
+      <c r="M381" t="n">
+        <v>103</v>
+      </c>
+      <c r="N381" t="n">
+        <v>113</v>
+      </c>
+      <c r="O381" t="n">
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -19424,46 +19424,46 @@
         <v>394</v>
       </c>
       <c r="B381">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C381">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D381">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E381">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="F381">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="G381">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="H381">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I381">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J381">
         <v>0</v>
       </c>
       <c r="K381">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L381">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="M381">
-        <v>103</v>
+        <v>275</v>
       </c>
       <c r="N381">
-        <v>113</v>
+        <v>320</v>
       </c>
       <c r="O381">
-        <v>127</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="387">
   <si>
     <t>Date</t>
   </si>
@@ -808,15 +808,6 @@
     <t>2026-06-12</t>
   </si>
   <si>
-    <t>2026-06-13</t>
-  </si>
-  <si>
-    <t>2026-06-14</t>
-  </si>
-  <si>
-    <t>2026-06-15</t>
-  </si>
-  <si>
     <t>2026-06-16</t>
   </si>
   <si>
@@ -829,12 +820,6 @@
     <t>2026-06-19</t>
   </si>
   <si>
-    <t>2026-06-20</t>
-  </si>
-  <si>
-    <t>2026-06-21</t>
-  </si>
-  <si>
     <t>2026-06-22</t>
   </si>
   <si>
@@ -874,9 +859,6 @@
     <t>2026-07-04</t>
   </si>
   <si>
-    <t>2026-07-05</t>
-  </si>
-  <si>
     <t>2026-07-06</t>
   </si>
   <si>
@@ -953,12 +935,6 @@
   </si>
   <si>
     <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>2026-08-01</t>
-  </si>
-  <si>
-    <t>2026-08-02</t>
   </si>
   <si>
     <t>2026-08-03</t>
@@ -1556,7 +1532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O381"/>
+  <dimension ref="A1:O373"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -2883,13 +2859,13 @@
         <v>8</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F29">
         <v>2</v>
@@ -3973,10 +3949,10 @@
         <v>1</v>
       </c>
       <c r="F52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H52">
         <v>1</v>
@@ -4164,10 +4140,10 @@
         <v>1</v>
       </c>
       <c r="G56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I56">
         <v>5</v>
@@ -4361,10 +4337,10 @@
         <v>0</v>
       </c>
       <c r="J60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -4581,10 +4557,10 @@
         <v>3</v>
       </c>
       <c r="E65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65">
         <v>2</v>
@@ -5239,10 +5215,10 @@
         <v>1</v>
       </c>
       <c r="E79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -5994,10 +5970,10 @@
         <v>1</v>
       </c>
       <c r="F95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95">
         <v>0</v>
@@ -6229,10 +6205,10 @@
         <v>1</v>
       </c>
       <c r="F100">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H100">
         <v>1</v>
@@ -6250,13 +6226,13 @@
         <v>1</v>
       </c>
       <c r="M100">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N100">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O100">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="101" spans="1:15">
@@ -6294,16 +6270,16 @@
         <v>0</v>
       </c>
       <c r="L101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M101">
+        <v>26</v>
+      </c>
+      <c r="N101">
         <v>27</v>
       </c>
-      <c r="N101">
-        <v>28</v>
-      </c>
       <c r="O101">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="102" spans="1:15">
@@ -6546,13 +6522,13 @@
         <v>120</v>
       </c>
       <c r="B107">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C107">
         <v>1</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E107">
         <v>2</v>
@@ -6705,10 +6681,10 @@
         <v>2</v>
       </c>
       <c r="H110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J110">
         <v>0</v>
@@ -7119,10 +7095,10 @@
         <v>1</v>
       </c>
       <c r="E119">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F119">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G119">
         <v>2</v>
@@ -7392,13 +7368,13 @@
         <v>138</v>
       </c>
       <c r="B125">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C125">
         <v>1</v>
       </c>
       <c r="D125">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E125">
         <v>1</v>
@@ -8767,10 +8743,10 @@
         <v>10</v>
       </c>
       <c r="F154">
+        <v>14</v>
+      </c>
+      <c r="G154">
         <v>13</v>
-      </c>
-      <c r="G154">
-        <v>14</v>
       </c>
       <c r="H154">
         <v>9</v>
@@ -8999,10 +8975,10 @@
         <v>1</v>
       </c>
       <c r="E159">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F159">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G159">
         <v>8</v>
@@ -9143,10 +9119,10 @@
         <v>13</v>
       </c>
       <c r="F162">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G162">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H162">
         <v>0</v>
@@ -9181,10 +9157,10 @@
         <v>11</v>
       </c>
       <c r="C163">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D163">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E163">
         <v>6</v>
@@ -9234,10 +9210,10 @@
         <v>0</v>
       </c>
       <c r="E164">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F164">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G164">
         <v>5</v>
@@ -9378,10 +9354,10 @@
         <v>5</v>
       </c>
       <c r="F167">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G167">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H167">
         <v>0</v>
@@ -9616,10 +9592,10 @@
         <v>11</v>
       </c>
       <c r="G172">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H172">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I172">
         <v>1</v>
@@ -9704,10 +9680,10 @@
         <v>12</v>
       </c>
       <c r="E174">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F174">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G174">
         <v>7</v>
@@ -9754,10 +9730,10 @@
         <v>6</v>
       </c>
       <c r="F175">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G175">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H175">
         <v>2</v>
@@ -9795,16 +9771,16 @@
         <v>6</v>
       </c>
       <c r="D176">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E176">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F176">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G176">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H176">
         <v>4</v>
@@ -9839,19 +9815,19 @@
         <v>15</v>
       </c>
       <c r="C177">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D177">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E177">
         <v>11</v>
       </c>
       <c r="F177">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G177">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H177">
         <v>1</v>
@@ -9889,16 +9865,16 @@
         <v>5</v>
       </c>
       <c r="D178">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E178">
+        <v>9</v>
+      </c>
+      <c r="F178">
+        <v>4</v>
+      </c>
+      <c r="G178">
         <v>10</v>
-      </c>
-      <c r="F178">
-        <v>5</v>
-      </c>
-      <c r="G178">
-        <v>9</v>
       </c>
       <c r="H178">
         <v>0</v>
@@ -9989,22 +9965,22 @@
         <v>38</v>
       </c>
       <c r="F180">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G180">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H180">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I180">
         <v>1</v>
       </c>
       <c r="J180">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K180">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L180">
         <v>0</v>
@@ -10036,10 +10012,10 @@
         <v>28</v>
       </c>
       <c r="F181">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G181">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H181">
         <v>3</v>
@@ -10077,10 +10053,10 @@
         <v>2</v>
       </c>
       <c r="D182">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E182">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F182">
         <v>4</v>
@@ -10180,10 +10156,10 @@
         <v>22</v>
       </c>
       <c r="G184">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H184">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I184">
         <v>2</v>
@@ -10212,7 +10188,7 @@
         <v>198</v>
       </c>
       <c r="B185">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C185">
         <v>12</v>
@@ -10221,7 +10197,7 @@
         <v>14</v>
       </c>
       <c r="E185">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F185">
         <v>10</v>
@@ -10265,13 +10241,13 @@
         <v>6</v>
       </c>
       <c r="D186">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E186">
         <v>9</v>
       </c>
       <c r="F186">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G186">
         <v>6</v>
@@ -10321,10 +10297,10 @@
         <v>6</v>
       </c>
       <c r="G187">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H187">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I187">
         <v>2</v>
@@ -10359,10 +10335,10 @@
         <v>2</v>
       </c>
       <c r="D188">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E188">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F188">
         <v>9</v>
@@ -10415,10 +10391,10 @@
         <v>0</v>
       </c>
       <c r="G189">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H189">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I189">
         <v>0</v>
@@ -10433,13 +10409,13 @@
         <v>0</v>
       </c>
       <c r="M189">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N189">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O189">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190" spans="1:15">
@@ -10506,10 +10482,10 @@
         <v>31</v>
       </c>
       <c r="F191">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G191">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H191">
         <v>1</v>
@@ -10541,7 +10517,7 @@
         <v>205</v>
       </c>
       <c r="B192">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C192">
         <v>0</v>
@@ -10574,13 +10550,13 @@
         <v>0</v>
       </c>
       <c r="M192">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N192">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O192">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:15">
@@ -10588,13 +10564,13 @@
         <v>206</v>
       </c>
       <c r="B193">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C193">
         <v>4</v>
       </c>
       <c r="D193">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E193">
         <v>22</v>
@@ -10603,31 +10579,31 @@
         <v>12</v>
       </c>
       <c r="G193">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H193">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I193">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J193">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K193">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L193">
         <v>0</v>
       </c>
       <c r="M193">
+        <v>81</v>
+      </c>
+      <c r="N193">
         <v>82</v>
       </c>
-      <c r="N193">
+      <c r="O193">
         <v>83</v>
-      </c>
-      <c r="O193">
-        <v>84</v>
       </c>
     </row>
     <row r="194" spans="1:15">
@@ -10665,16 +10641,16 @@
         <v>1</v>
       </c>
       <c r="L194">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M194">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N194">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O194">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="195" spans="1:15">
@@ -10738,13 +10714,13 @@
         <v>9</v>
       </c>
       <c r="E196">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F196">
         <v>14</v>
       </c>
       <c r="G196">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H196">
         <v>5</v>
@@ -10776,13 +10752,13 @@
         <v>210</v>
       </c>
       <c r="B197">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C197">
         <v>5</v>
       </c>
       <c r="D197">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E197">
         <v>12</v>
@@ -10832,10 +10808,10 @@
         <v>7</v>
       </c>
       <c r="E198">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F198">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G198">
         <v>8</v>
@@ -10879,16 +10855,16 @@
         <v>4</v>
       </c>
       <c r="E199">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F199">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G199">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H199">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I199">
         <v>0</v>
@@ -10917,13 +10893,13 @@
         <v>213</v>
       </c>
       <c r="B200">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C200">
         <v>4</v>
       </c>
       <c r="D200">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E200">
         <v>14</v>
@@ -11020,10 +10996,10 @@
         <v>13</v>
       </c>
       <c r="E202">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F202">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G202">
         <v>40</v>
@@ -11152,13 +11128,13 @@
         <v>218</v>
       </c>
       <c r="B205">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C205">
         <v>6</v>
       </c>
       <c r="D205">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E205">
         <v>23</v>
@@ -11167,10 +11143,10 @@
         <v>8</v>
       </c>
       <c r="G205">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H205">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I205">
         <v>3</v>
@@ -11352,10 +11328,10 @@
         <v>1</v>
       </c>
       <c r="F209">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G209">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H209">
         <v>3</v>
@@ -11402,10 +11378,10 @@
         <v>1</v>
       </c>
       <c r="G210">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H210">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I210">
         <v>2</v>
@@ -11446,10 +11422,10 @@
         <v>4</v>
       </c>
       <c r="F211">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G211">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H211">
         <v>0</v>
@@ -11775,10 +11751,10 @@
         <v>18</v>
       </c>
       <c r="F218">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G218">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H218">
         <v>3</v>
@@ -11951,7 +11927,7 @@
         <v>235</v>
       </c>
       <c r="B222">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C222">
         <v>0</v>
@@ -11963,7 +11939,7 @@
         <v>14</v>
       </c>
       <c r="F222">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G222">
         <v>16</v>
@@ -11981,16 +11957,16 @@
         <v>1</v>
       </c>
       <c r="L222">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M222">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="N222">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="O222">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="223" spans="1:15">
@@ -12013,10 +11989,10 @@
         <v>4</v>
       </c>
       <c r="G223">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H223">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I223">
         <v>1</v>
@@ -12057,10 +12033,10 @@
         <v>9</v>
       </c>
       <c r="F224">
+        <v>4</v>
+      </c>
+      <c r="G224">
         <v>5</v>
-      </c>
-      <c r="G224">
-        <v>4</v>
       </c>
       <c r="H224">
         <v>2</v>
@@ -12104,10 +12080,10 @@
         <v>6</v>
       </c>
       <c r="F225">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G225">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H225">
         <v>6</v>
@@ -12148,10 +12124,10 @@
         <v>3</v>
       </c>
       <c r="E226">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F226">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G226">
         <v>4</v>
@@ -12169,16 +12145,16 @@
         <v>0</v>
       </c>
       <c r="L226">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M226">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N226">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O226">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="227" spans="1:15">
@@ -12186,7 +12162,7 @@
         <v>240</v>
       </c>
       <c r="B227">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C227">
         <v>0</v>
@@ -12219,13 +12195,13 @@
         <v>0</v>
       </c>
       <c r="M227">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N227">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O227">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228" spans="1:15">
@@ -12245,16 +12221,16 @@
         <v>2</v>
       </c>
       <c r="F228">
+        <v>7</v>
+      </c>
+      <c r="G228">
+        <v>16</v>
+      </c>
+      <c r="H228">
+        <v>8</v>
+      </c>
+      <c r="I228">
         <v>6</v>
-      </c>
-      <c r="G228">
-        <v>18</v>
-      </c>
-      <c r="H228">
-        <v>9</v>
-      </c>
-      <c r="I228">
-        <v>4</v>
       </c>
       <c r="J228">
         <v>0</v>
@@ -12298,10 +12274,10 @@
         <v>10</v>
       </c>
       <c r="H229">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I229">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J229">
         <v>0</v>
@@ -12357,16 +12333,16 @@
         <v>0</v>
       </c>
       <c r="L230">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M230">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N230">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O230">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="231" spans="1:15">
@@ -12386,13 +12362,13 @@
         <v>9</v>
       </c>
       <c r="F231">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G231">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H231">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I231">
         <v>2</v>
@@ -12477,16 +12453,16 @@
         <v>4</v>
       </c>
       <c r="E233">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F233">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G233">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H233">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I233">
         <v>3</v>
@@ -12571,16 +12547,16 @@
         <v>2</v>
       </c>
       <c r="E235">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F235">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G235">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H235">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I235">
         <v>4</v>
@@ -12609,7 +12585,7 @@
         <v>249</v>
       </c>
       <c r="B236">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C236">
         <v>3</v>
@@ -12618,16 +12594,16 @@
         <v>5</v>
       </c>
       <c r="E236">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F236">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G236">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H236">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I236">
         <v>8</v>
@@ -12639,16 +12615,16 @@
         <v>0</v>
       </c>
       <c r="L236">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M236">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="N236">
+        <v>195</v>
+      </c>
+      <c r="O236">
         <v>197</v>
-      </c>
-      <c r="O236">
-        <v>199</v>
       </c>
     </row>
     <row r="237" spans="1:15">
@@ -12662,19 +12638,19 @@
         <v>6</v>
       </c>
       <c r="D237">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E237">
         <v>19</v>
       </c>
       <c r="F237">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G237">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H237">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I237">
         <v>3</v>
@@ -12686,16 +12662,16 @@
         <v>0</v>
       </c>
       <c r="L237">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M237">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N237">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O237">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="238" spans="1:15">
@@ -12709,16 +12685,16 @@
         <v>9</v>
       </c>
       <c r="D238">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E238">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F238">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G238">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H238">
         <v>6</v>
@@ -12733,16 +12709,16 @@
         <v>0</v>
       </c>
       <c r="L238">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M238">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N238">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O238">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="239" spans="1:15">
@@ -12780,16 +12756,16 @@
         <v>0</v>
       </c>
       <c r="L239">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M239">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N239">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O239">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="240" spans="1:15">
@@ -12847,16 +12823,16 @@
         <v>5</v>
       </c>
       <c r="C241">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D241">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E241">
         <v>24</v>
       </c>
       <c r="F241">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G241">
         <v>9</v>
@@ -12874,16 +12850,16 @@
         <v>0</v>
       </c>
       <c r="L241">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M241">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="N241">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="O241">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="242" spans="1:15">
@@ -12906,10 +12882,10 @@
         <v>16</v>
       </c>
       <c r="G242">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H242">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I242">
         <v>2</v>
@@ -12921,16 +12897,16 @@
         <v>1</v>
       </c>
       <c r="L242">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M242">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N242">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O242">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="243" spans="1:15">
@@ -12947,16 +12923,16 @@
         <v>2</v>
       </c>
       <c r="E243">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F243">
         <v>10</v>
       </c>
       <c r="G243">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H243">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I243">
         <v>3</v>
@@ -12997,10 +12973,10 @@
         <v>4</v>
       </c>
       <c r="F244">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G244">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H244">
         <v>5</v>
@@ -13032,7 +13008,7 @@
         <v>258</v>
       </c>
       <c r="B245">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -13065,13 +13041,13 @@
         <v>0</v>
       </c>
       <c r="M245">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N245">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O245">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="246" spans="1:15">
@@ -13088,37 +13064,37 @@
         <v>9</v>
       </c>
       <c r="E246">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F246">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G246">
         <v>38</v>
       </c>
       <c r="H246">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I246">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J246">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K246">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L246">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M246">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="N246">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="O246">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="247" spans="1:15">
@@ -13126,7 +13102,7 @@
         <v>260</v>
       </c>
       <c r="B247">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C247">
         <v>1</v>
@@ -13138,10 +13114,10 @@
         <v>6</v>
       </c>
       <c r="F247">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G247">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H247">
         <v>4</v>
@@ -13159,13 +13135,13 @@
         <v>1</v>
       </c>
       <c r="M247">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N247">
+        <v>46</v>
+      </c>
+      <c r="O247">
         <v>48</v>
-      </c>
-      <c r="O247">
-        <v>50</v>
       </c>
     </row>
     <row r="248" spans="1:15">
@@ -13182,10 +13158,10 @@
         <v>2</v>
       </c>
       <c r="E248">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F248">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G248">
         <v>12</v>
@@ -13203,16 +13179,16 @@
         <v>0</v>
       </c>
       <c r="L248">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M248">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N248">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O248">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="249" spans="1:15">
@@ -13235,13 +13211,13 @@
         <v>12</v>
       </c>
       <c r="G249">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H249">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I249">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J249">
         <v>0</v>
@@ -13267,7 +13243,7 @@
         <v>263</v>
       </c>
       <c r="B250">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C250">
         <v>0</v>
@@ -13297,16 +13273,16 @@
         <v>1</v>
       </c>
       <c r="L250">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M250">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N250">
+        <v>39</v>
+      </c>
+      <c r="O250">
         <v>41</v>
-      </c>
-      <c r="O250">
-        <v>43</v>
       </c>
     </row>
     <row r="251" spans="1:15">
@@ -13320,40 +13296,40 @@
         <v>0</v>
       </c>
       <c r="D251">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E251">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F251">
         <v>0</v>
       </c>
       <c r="G251">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H251">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I251">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J251">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K251">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L251">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M251">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="N251">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="O251">
-        <v>2</v>
+        <v>58</v>
       </c>
     </row>
     <row r="252" spans="1:15">
@@ -13361,46 +13337,46 @@
         <v>265</v>
       </c>
       <c r="B252">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="C252">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D252">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E252">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F252">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G252">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H252">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I252">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J252">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K252">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L252">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M252">
-        <v>1</v>
+        <v>143</v>
       </c>
       <c r="N252">
-        <v>1</v>
+        <v>147</v>
       </c>
       <c r="O252">
-        <v>1</v>
+        <v>151</v>
       </c>
     </row>
     <row r="253" spans="1:15">
@@ -13408,31 +13384,31 @@
         <v>266</v>
       </c>
       <c r="B253">
-        <v>1</v>
+        <v>76</v>
       </c>
       <c r="C253">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D253">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E253">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F253">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G253">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H253">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I253">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J253">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K253">
         <v>0</v>
@@ -13441,13 +13417,13 @@
         <v>1</v>
       </c>
       <c r="M253">
-        <v>2</v>
+        <v>217</v>
       </c>
       <c r="N253">
-        <v>2</v>
+        <v>227</v>
       </c>
       <c r="O253">
-        <v>2</v>
+        <v>231</v>
       </c>
     </row>
     <row r="254" spans="1:15">
@@ -13455,46 +13431,46 @@
         <v>267</v>
       </c>
       <c r="B254">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C254">
         <v>0</v>
       </c>
       <c r="D254">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E254">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F254">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G254">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="H254">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I254">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J254">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K254">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L254">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M254">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="N254">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="O254">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="255" spans="1:15">
@@ -13502,46 +13478,46 @@
         <v>268</v>
       </c>
       <c r="B255">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="C255">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D255">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E255">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F255">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G255">
         <v>41</v>
       </c>
       <c r="H255">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I255">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J255">
         <v>1</v>
       </c>
       <c r="K255">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L255">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M255">
-        <v>144</v>
+        <v>285</v>
       </c>
       <c r="N255">
-        <v>148</v>
+        <v>288</v>
       </c>
       <c r="O255">
-        <v>152</v>
+        <v>288</v>
       </c>
     </row>
     <row r="256" spans="1:15">
@@ -13549,46 +13525,46 @@
         <v>269</v>
       </c>
       <c r="B256">
-        <v>76</v>
+        <v>784</v>
       </c>
       <c r="C256">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="D256">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="E256">
-        <v>45</v>
+        <v>115</v>
       </c>
       <c r="F256">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="G256">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="H256">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I256">
+        <v>3</v>
+      </c>
+      <c r="J256">
+        <v>1</v>
+      </c>
+      <c r="K256">
+        <v>0</v>
+      </c>
+      <c r="L256">
         <v>6</v>
       </c>
-      <c r="J256">
-        <v>2</v>
-      </c>
-      <c r="K256">
-        <v>0</v>
-      </c>
-      <c r="L256">
-        <v>5</v>
-      </c>
       <c r="M256">
-        <v>222</v>
+        <v>1161</v>
       </c>
       <c r="N256">
-        <v>232</v>
+        <v>1167</v>
       </c>
       <c r="O256">
-        <v>236</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="257" spans="1:15">
@@ -13596,46 +13572,46 @@
         <v>270</v>
       </c>
       <c r="B257">
+        <v>90</v>
+      </c>
+      <c r="C257">
+        <v>16</v>
+      </c>
+      <c r="D257">
+        <v>9</v>
+      </c>
+      <c r="E257">
+        <v>16</v>
+      </c>
+      <c r="F257">
+        <v>6</v>
+      </c>
+      <c r="G257">
         <v>14</v>
       </c>
-      <c r="C257">
-        <v>0</v>
-      </c>
-      <c r="D257">
-        <v>3</v>
-      </c>
-      <c r="E257">
-        <v>5</v>
-      </c>
-      <c r="F257">
-        <v>11</v>
-      </c>
-      <c r="G257">
-        <v>24</v>
-      </c>
       <c r="H257">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I257">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J257">
         <v>0</v>
       </c>
       <c r="K257">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L257">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M257">
-        <v>67</v>
+        <v>156</v>
       </c>
       <c r="N257">
-        <v>72</v>
+        <v>160</v>
       </c>
       <c r="O257">
-        <v>72</v>
+        <v>160</v>
       </c>
     </row>
     <row r="258" spans="1:15">
@@ -13643,46 +13619,46 @@
         <v>271</v>
       </c>
       <c r="B258">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="C258">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D258">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E258">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F258">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G258">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H258">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I258">
         <v>0</v>
       </c>
       <c r="J258">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K258">
         <v>0</v>
       </c>
       <c r="L258">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M258">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="N258">
-        <v>6</v>
+        <v>171</v>
       </c>
       <c r="O258">
-        <v>6</v>
+        <v>171</v>
       </c>
     </row>
     <row r="259" spans="1:15">
@@ -13690,46 +13666,46 @@
         <v>272</v>
       </c>
       <c r="B259">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C259">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D259">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E259">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F259">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G259">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H259">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I259">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J259">
         <v>0</v>
       </c>
       <c r="K259">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L259">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M259">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="N259">
-        <v>6</v>
+        <v>191</v>
       </c>
       <c r="O259">
-        <v>6</v>
+        <v>192</v>
       </c>
     </row>
     <row r="260" spans="1:15">
@@ -13737,46 +13713,46 @@
         <v>273</v>
       </c>
       <c r="B260">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="C260">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D260">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E260">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F260">
+        <v>20</v>
+      </c>
+      <c r="G260">
         <v>30</v>
       </c>
-      <c r="G260">
-        <v>41</v>
-      </c>
       <c r="H260">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I260">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J260">
         <v>1</v>
       </c>
       <c r="K260">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L260">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M260">
-        <v>291</v>
+        <v>268</v>
       </c>
       <c r="N260">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="O260">
-        <v>295</v>
+        <v>269</v>
       </c>
     </row>
     <row r="261" spans="1:15">
@@ -13784,46 +13760,46 @@
         <v>274</v>
       </c>
       <c r="B261">
-        <v>784</v>
+        <v>47</v>
       </c>
       <c r="C261">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="D261">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="E261">
-        <v>116</v>
+        <v>3</v>
       </c>
       <c r="F261">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="G261">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="H261">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I261">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J261">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K261">
         <v>0</v>
       </c>
       <c r="L261">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M261">
-        <v>1164</v>
+        <v>58</v>
       </c>
       <c r="N261">
-        <v>1170</v>
+        <v>58</v>
       </c>
       <c r="O261">
-        <v>1170</v>
+        <v>58</v>
       </c>
     </row>
     <row r="262" spans="1:15">
@@ -13831,46 +13807,46 @@
         <v>275</v>
       </c>
       <c r="B262">
-        <v>90</v>
+        <v>8</v>
       </c>
       <c r="C262">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D262">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E262">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F262">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="G262">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="H262">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I262">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J262">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K262">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L262">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M262">
-        <v>157</v>
+        <v>127</v>
       </c>
       <c r="N262">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="O262">
-        <v>161</v>
+        <v>131</v>
       </c>
     </row>
     <row r="263" spans="1:15">
@@ -13878,46 +13854,46 @@
         <v>276</v>
       </c>
       <c r="B263">
-        <v>91</v>
+        <v>5</v>
       </c>
       <c r="C263">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D263">
+        <v>2</v>
+      </c>
+      <c r="E263">
+        <v>20</v>
+      </c>
+      <c r="F263">
         <v>14</v>
       </c>
-      <c r="E263">
-        <v>27</v>
-      </c>
-      <c r="F263">
-        <v>12</v>
-      </c>
       <c r="G263">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H263">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I263">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J263">
         <v>1</v>
       </c>
       <c r="K263">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L263">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M263">
-        <v>172</v>
+        <v>66</v>
       </c>
       <c r="N263">
-        <v>173</v>
+        <v>67</v>
       </c>
       <c r="O263">
-        <v>173</v>
+        <v>67</v>
       </c>
     </row>
     <row r="264" spans="1:15">
@@ -13925,46 +13901,46 @@
         <v>277</v>
       </c>
       <c r="B264">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="C264">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D264">
+        <v>0</v>
+      </c>
+      <c r="E264">
+        <v>0</v>
+      </c>
+      <c r="F264">
+        <v>1</v>
+      </c>
+      <c r="G264">
+        <v>4</v>
+      </c>
+      <c r="H264">
+        <v>2</v>
+      </c>
+      <c r="I264">
+        <v>1</v>
+      </c>
+      <c r="J264">
+        <v>2</v>
+      </c>
+      <c r="K264">
+        <v>0</v>
+      </c>
+      <c r="L264">
+        <v>0</v>
+      </c>
+      <c r="M264">
         <v>11</v>
       </c>
-      <c r="E264">
-        <v>16</v>
-      </c>
-      <c r="F264">
-        <v>8</v>
-      </c>
-      <c r="G264">
-        <v>14</v>
-      </c>
-      <c r="H264">
-        <v>2</v>
-      </c>
-      <c r="I264">
-        <v>2</v>
-      </c>
-      <c r="J264">
-        <v>0</v>
-      </c>
-      <c r="K264">
-        <v>1</v>
-      </c>
-      <c r="L264">
-        <v>1</v>
-      </c>
-      <c r="M264">
-        <v>188</v>
-      </c>
       <c r="N264">
-        <v>191</v>
+        <v>11</v>
       </c>
       <c r="O264">
-        <v>192</v>
+        <v>11</v>
       </c>
     </row>
     <row r="265" spans="1:15">
@@ -13972,25 +13948,25 @@
         <v>278</v>
       </c>
       <c r="B265">
-        <v>142</v>
+        <v>1</v>
       </c>
       <c r="C265">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D265">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E265">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F265">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G265">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H265">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I265">
         <v>1</v>
@@ -14005,13 +13981,13 @@
         <v>0</v>
       </c>
       <c r="M265">
-        <v>268</v>
+        <v>63</v>
       </c>
       <c r="N265">
-        <v>269</v>
+        <v>63</v>
       </c>
       <c r="O265">
-        <v>269</v>
+        <v>63</v>
       </c>
     </row>
     <row r="266" spans="1:15">
@@ -14019,7 +13995,7 @@
         <v>279</v>
       </c>
       <c r="B266">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="C266">
         <v>0</v>
@@ -14028,37 +14004,37 @@
         <v>2</v>
       </c>
       <c r="E266">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F266">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G266">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="H266">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I266">
         <v>0</v>
       </c>
       <c r="J266">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K266">
         <v>0</v>
       </c>
       <c r="L266">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M266">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="N266">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="O266">
-        <v>61</v>
+        <v>48</v>
       </c>
     </row>
     <row r="267" spans="1:15">
@@ -14066,46 +14042,46 @@
         <v>280</v>
       </c>
       <c r="B267">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C267">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D267">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E267">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F267">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G267">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H267">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I267">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J267">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K267">
         <v>0</v>
       </c>
       <c r="L267">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M267">
-        <v>131</v>
+        <v>1</v>
       </c>
       <c r="N267">
-        <v>135</v>
+        <v>1</v>
       </c>
       <c r="O267">
-        <v>135</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268" spans="1:15">
@@ -14113,46 +14089,46 @@
         <v>281</v>
       </c>
       <c r="B268">
+        <v>91</v>
+      </c>
+      <c r="C268">
+        <v>6</v>
+      </c>
+      <c r="D268">
+        <v>11</v>
+      </c>
+      <c r="E268">
+        <v>21</v>
+      </c>
+      <c r="F268">
+        <v>16</v>
+      </c>
+      <c r="G268">
+        <v>25</v>
+      </c>
+      <c r="H268">
         <v>5</v>
       </c>
-      <c r="C268">
-        <v>0</v>
-      </c>
-      <c r="D268">
-        <v>2</v>
-      </c>
-      <c r="E268">
-        <v>20</v>
-      </c>
-      <c r="F268">
-        <v>14</v>
-      </c>
-      <c r="G268">
-        <v>16</v>
-      </c>
-      <c r="H268">
-        <v>4</v>
-      </c>
       <c r="I268">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J268">
         <v>1</v>
       </c>
       <c r="K268">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L268">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M268">
-        <v>66</v>
+        <v>184</v>
       </c>
       <c r="N268">
-        <v>67</v>
+        <v>189</v>
       </c>
       <c r="O268">
-        <v>67</v>
+        <v>189</v>
       </c>
     </row>
     <row r="269" spans="1:15">
@@ -14160,46 +14136,46 @@
         <v>282</v>
       </c>
       <c r="B269">
-        <v>1</v>
+        <v>138</v>
       </c>
       <c r="C269">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D269">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E269">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F269">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="G269">
+        <v>19</v>
+      </c>
+      <c r="H269">
         <v>4</v>
       </c>
-      <c r="H269">
-        <v>2</v>
-      </c>
       <c r="I269">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J269">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K269">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L269">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M269">
-        <v>12</v>
+        <v>251</v>
       </c>
       <c r="N269">
-        <v>12</v>
+        <v>252</v>
       </c>
       <c r="O269">
-        <v>12</v>
+        <v>255</v>
       </c>
     </row>
     <row r="270" spans="1:15">
@@ -14207,46 +14183,46 @@
         <v>283</v>
       </c>
       <c r="B270">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C270">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D270">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E270">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F270">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G270">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H270">
+        <v>2</v>
+      </c>
+      <c r="I270">
         <v>4</v>
       </c>
-      <c r="I270">
-        <v>1</v>
-      </c>
       <c r="J270">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K270">
         <v>0</v>
       </c>
       <c r="L270">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M270">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="N270">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="O270">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="271" spans="1:15">
@@ -14254,25 +14230,25 @@
         <v>284</v>
       </c>
       <c r="B271">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C271">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D271">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E271">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F271">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G271">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H271">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I271">
         <v>0</v>
@@ -14284,16 +14260,16 @@
         <v>0</v>
       </c>
       <c r="L271">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M271">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="N271">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="O271">
-        <v>49</v>
+        <v>75</v>
       </c>
     </row>
     <row r="272" spans="1:15">
@@ -14301,28 +14277,28 @@
         <v>285</v>
       </c>
       <c r="B272">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C272">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D272">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E272">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F272">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G272">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H272">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I272">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J272">
         <v>0</v>
@@ -14331,16 +14307,16 @@
         <v>0</v>
       </c>
       <c r="L272">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="M272">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="N272">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="O272">
-        <v>26</v>
+        <v>57</v>
       </c>
     </row>
     <row r="273" spans="1:15">
@@ -14348,7 +14324,7 @@
         <v>286</v>
       </c>
       <c r="B273">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C273">
         <v>0</v>
@@ -14369,25 +14345,25 @@
         <v>0</v>
       </c>
       <c r="I273">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J273">
         <v>0</v>
       </c>
       <c r="K273">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L273">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="M273">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="N273">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="O273">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="274" spans="1:15">
@@ -14395,46 +14371,46 @@
         <v>287</v>
       </c>
       <c r="B274">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="C274">
+        <v>2</v>
+      </c>
+      <c r="D274">
         <v>6</v>
       </c>
-      <c r="D274">
-        <v>11</v>
-      </c>
       <c r="E274">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F274">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G274">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="H274">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I274">
         <v>6</v>
       </c>
       <c r="J274">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K274">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L274">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="M274">
-        <v>228</v>
+        <v>132</v>
       </c>
       <c r="N274">
-        <v>233</v>
+        <v>134</v>
       </c>
       <c r="O274">
-        <v>233</v>
+        <v>137</v>
       </c>
     </row>
     <row r="275" spans="1:15">
@@ -14442,22 +14418,22 @@
         <v>288</v>
       </c>
       <c r="B275">
-        <v>142</v>
+        <v>30</v>
       </c>
       <c r="C275">
         <v>10</v>
       </c>
       <c r="D275">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E275">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F275">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G275">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H275">
         <v>2</v>
@@ -14466,22 +14442,22 @@
         <v>2</v>
       </c>
       <c r="J275">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K275">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L275">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M275">
-        <v>270</v>
+        <v>125</v>
       </c>
       <c r="N275">
-        <v>271</v>
+        <v>125</v>
       </c>
       <c r="O275">
-        <v>274</v>
+        <v>125</v>
       </c>
     </row>
     <row r="276" spans="1:15">
@@ -14489,28 +14465,28 @@
         <v>289</v>
       </c>
       <c r="B276">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C276">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D276">
+        <v>10</v>
+      </c>
+      <c r="E276">
+        <v>18</v>
+      </c>
+      <c r="F276">
+        <v>6</v>
+      </c>
+      <c r="G276">
+        <v>13</v>
+      </c>
+      <c r="H276">
         <v>5</v>
       </c>
-      <c r="E276">
-        <v>23</v>
-      </c>
-      <c r="F276">
-        <v>7</v>
-      </c>
-      <c r="G276">
-        <v>12</v>
-      </c>
-      <c r="H276">
-        <v>2</v>
-      </c>
       <c r="I276">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J276">
         <v>0</v>
@@ -14519,16 +14495,16 @@
         <v>0</v>
       </c>
       <c r="L276">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M276">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="N276">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="O276">
-        <v>85</v>
+        <v>63</v>
       </c>
     </row>
     <row r="277" spans="1:15">
@@ -14536,46 +14512,46 @@
         <v>290</v>
       </c>
       <c r="B277">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="C277">
+        <v>2</v>
+      </c>
+      <c r="D277">
+        <v>7</v>
+      </c>
+      <c r="E277">
+        <v>8</v>
+      </c>
+      <c r="F277">
+        <v>8</v>
+      </c>
+      <c r="G277">
         <v>9</v>
       </c>
-      <c r="D277">
-        <v>5</v>
-      </c>
-      <c r="E277">
-        <v>21</v>
-      </c>
-      <c r="F277">
-        <v>9</v>
-      </c>
-      <c r="G277">
-        <v>15</v>
-      </c>
       <c r="H277">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I277">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J277">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K277">
         <v>0</v>
       </c>
       <c r="L277">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="M277">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="N277">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="O277">
-        <v>103</v>
+        <v>88</v>
       </c>
     </row>
     <row r="278" spans="1:15">
@@ -14583,46 +14559,46 @@
         <v>291</v>
       </c>
       <c r="B278">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C278">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D278">
+        <v>10</v>
+      </c>
+      <c r="E278">
+        <v>25</v>
+      </c>
+      <c r="F278">
+        <v>10</v>
+      </c>
+      <c r="G278">
+        <v>24</v>
+      </c>
+      <c r="H278">
         <v>4</v>
       </c>
-      <c r="E278">
-        <v>10</v>
-      </c>
-      <c r="F278">
-        <v>9</v>
-      </c>
-      <c r="G278">
-        <v>15</v>
-      </c>
-      <c r="H278">
-        <v>3</v>
-      </c>
       <c r="I278">
         <v>2</v>
       </c>
       <c r="J278">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K278">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L278">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="M278">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="N278">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="O278">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="279" spans="1:15">
@@ -14630,46 +14606,46 @@
         <v>292</v>
       </c>
       <c r="B279">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="C279">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D279">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E279">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F279">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G279">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H279">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I279">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J279">
         <v>0</v>
       </c>
       <c r="K279">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L279">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M279">
-        <v>3</v>
+        <v>98</v>
       </c>
       <c r="N279">
-        <v>3</v>
+        <v>101</v>
       </c>
       <c r="O279">
-        <v>5</v>
+        <v>103</v>
       </c>
     </row>
     <row r="280" spans="1:15">
@@ -14677,31 +14653,31 @@
         <v>293</v>
       </c>
       <c r="B280">
-        <v>89</v>
+        <v>166</v>
       </c>
       <c r="C280">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D280">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="E280">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F280">
+        <v>13</v>
+      </c>
+      <c r="G280">
+        <v>12</v>
+      </c>
+      <c r="H280">
         <v>4</v>
       </c>
-      <c r="G280">
-        <v>7</v>
-      </c>
-      <c r="H280">
-        <v>5</v>
-      </c>
       <c r="I280">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J280">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K280">
         <v>1</v>
@@ -14710,13 +14686,13 @@
         <v>10</v>
       </c>
       <c r="M280">
-        <v>141</v>
+        <v>272</v>
       </c>
       <c r="N280">
-        <v>143</v>
+        <v>274</v>
       </c>
       <c r="O280">
-        <v>146</v>
+        <v>278</v>
       </c>
     </row>
     <row r="281" spans="1:15">
@@ -14724,46 +14700,46 @@
         <v>294</v>
       </c>
       <c r="B281">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C281">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D281">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E281">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="F281">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G281">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H281">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I281">
         <v>2</v>
       </c>
       <c r="J281">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K281">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L281">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M281">
-        <v>155</v>
+        <v>4</v>
       </c>
       <c r="N281">
-        <v>155</v>
+        <v>5</v>
       </c>
       <c r="O281">
-        <v>155</v>
+        <v>9</v>
       </c>
     </row>
     <row r="282" spans="1:15">
@@ -14771,46 +14747,46 @@
         <v>295</v>
       </c>
       <c r="B282">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C282">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D282">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E282">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F282">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G282">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H282">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I282">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J282">
         <v>0</v>
       </c>
       <c r="K282">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L282">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="M282">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="N282">
-        <v>101</v>
+        <v>22</v>
       </c>
       <c r="O282">
-        <v>104</v>
+        <v>23</v>
       </c>
     </row>
     <row r="283" spans="1:15">
@@ -14818,26 +14794,26 @@
         <v>296</v>
       </c>
       <c r="B283">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="C283">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D283">
+        <v>1</v>
+      </c>
+      <c r="E283">
+        <v>18</v>
+      </c>
+      <c r="F283">
+        <v>24</v>
+      </c>
+      <c r="G283">
+        <v>32</v>
+      </c>
+      <c r="H283">
         <v>6</v>
       </c>
-      <c r="E283">
-        <v>9</v>
-      </c>
-      <c r="F283">
-        <v>8</v>
-      </c>
-      <c r="G283">
-        <v>9</v>
-      </c>
-      <c r="H283">
-        <v>1</v>
-      </c>
       <c r="I283">
         <v>2</v>
       </c>
@@ -14845,19 +14821,19 @@
         <v>0</v>
       </c>
       <c r="K283">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L283">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="M283">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="N283">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="O283">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="284" spans="1:15">
@@ -14865,46 +14841,46 @@
         <v>297</v>
       </c>
       <c r="B284">
-        <v>2</v>
+        <v>208</v>
       </c>
       <c r="C284">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D284">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E284">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F284">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G284">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H284">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I284">
+        <v>2</v>
+      </c>
+      <c r="J284">
+        <v>1</v>
+      </c>
+      <c r="K284">
+        <v>0</v>
+      </c>
+      <c r="L284">
         <v>4</v>
       </c>
-      <c r="J284">
-        <v>1</v>
-      </c>
-      <c r="K284">
-        <v>1</v>
-      </c>
-      <c r="L284">
-        <v>15</v>
-      </c>
       <c r="M284">
-        <v>94</v>
+        <v>283</v>
       </c>
       <c r="N284">
-        <v>101</v>
+        <v>291</v>
       </c>
       <c r="O284">
-        <v>101</v>
+        <v>292</v>
       </c>
     </row>
     <row r="285" spans="1:15">
@@ -14912,46 +14888,46 @@
         <v>298</v>
       </c>
       <c r="B285">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C285">
         <v>4</v>
       </c>
       <c r="D285">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E285">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F285">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="G285">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H285">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I285">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J285">
         <v>0</v>
       </c>
       <c r="K285">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L285">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="M285">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="N285">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="O285">
-        <v>122</v>
+        <v>108</v>
       </c>
     </row>
     <row r="286" spans="1:15">
@@ -14959,46 +14935,46 @@
         <v>299</v>
       </c>
       <c r="B286">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="C286">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D286">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E286">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F286">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G286">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H286">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I286">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J286">
         <v>1</v>
       </c>
       <c r="K286">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L286">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="M286">
-        <v>291</v>
+        <v>5</v>
       </c>
       <c r="N286">
-        <v>293</v>
+        <v>7</v>
       </c>
       <c r="O286">
-        <v>297</v>
+        <v>9</v>
       </c>
     </row>
     <row r="287" spans="1:15">
@@ -15006,7 +14982,7 @@
         <v>300</v>
       </c>
       <c r="B287">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C287">
         <v>0</v>
@@ -15015,37 +14991,37 @@
         <v>0</v>
       </c>
       <c r="E287">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F287">
         <v>0</v>
       </c>
       <c r="G287">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H287">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I287">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J287">
         <v>0</v>
       </c>
       <c r="K287">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L287">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M287">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="N287">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="O287">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="288" spans="1:15">
@@ -15053,7 +15029,7 @@
         <v>301</v>
       </c>
       <c r="B288">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C288">
         <v>0</v>
@@ -15065,34 +15041,34 @@
         <v>0</v>
       </c>
       <c r="F288">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G288">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H288">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I288">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J288">
         <v>0</v>
       </c>
       <c r="K288">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L288">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M288">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="N288">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="O288">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289" spans="1:15">
@@ -15100,7 +15076,7 @@
         <v>302</v>
       </c>
       <c r="B289">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C289">
         <v>1</v>
@@ -15109,37 +15085,37 @@
         <v>1</v>
       </c>
       <c r="E289">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F289">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G289">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H289">
+        <v>10</v>
+      </c>
+      <c r="I289">
         <v>6</v>
       </c>
-      <c r="I289">
-        <v>2</v>
-      </c>
       <c r="J289">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K289">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L289">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M289">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="N289">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="O289">
-        <v>110</v>
+        <v>120</v>
       </c>
     </row>
     <row r="290" spans="1:15">
@@ -15147,46 +15123,46 @@
         <v>303</v>
       </c>
       <c r="B290">
-        <v>214</v>
+        <v>4</v>
       </c>
       <c r="C290">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D290">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E290">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F290">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G290">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="H290">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I290">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J290">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K290">
         <v>0</v>
       </c>
       <c r="L290">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="M290">
-        <v>302</v>
+        <v>99</v>
       </c>
       <c r="N290">
-        <v>310</v>
+        <v>106</v>
       </c>
       <c r="O290">
-        <v>311</v>
+        <v>107</v>
       </c>
     </row>
     <row r="291" spans="1:15">
@@ -15194,46 +15170,46 @@
         <v>304</v>
       </c>
       <c r="B291">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="C291">
+        <v>0</v>
+      </c>
+      <c r="D291">
+        <v>0</v>
+      </c>
+      <c r="E291">
+        <v>2</v>
+      </c>
+      <c r="F291">
         <v>4</v>
       </c>
-      <c r="D291">
-        <v>10</v>
-      </c>
-      <c r="E291">
-        <v>26</v>
-      </c>
-      <c r="F291">
+      <c r="G291">
+        <v>7</v>
+      </c>
+      <c r="H291">
         <v>6</v>
       </c>
-      <c r="G291">
-        <v>9</v>
-      </c>
-      <c r="H291">
-        <v>5</v>
-      </c>
       <c r="I291">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J291">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K291">
         <v>1</v>
       </c>
       <c r="L291">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M291">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="N291">
-        <v>125</v>
+        <v>24</v>
       </c>
       <c r="O291">
-        <v>129</v>
+        <v>28</v>
       </c>
     </row>
     <row r="292" spans="1:15">
@@ -15241,46 +15217,46 @@
         <v>305</v>
       </c>
       <c r="B292">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C292">
         <v>0</v>
       </c>
       <c r="D292">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E292">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F292">
         <v>0</v>
       </c>
       <c r="G292">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H292">
         <v>1</v>
       </c>
       <c r="I292">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J292">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K292">
         <v>0</v>
       </c>
       <c r="L292">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="M292">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="N292">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="O292">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="293" spans="1:15">
@@ -15297,13 +15273,13 @@
         <v>0</v>
       </c>
       <c r="E293">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F293">
         <v>0</v>
       </c>
       <c r="G293">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H293">
         <v>2</v>
@@ -15312,22 +15288,22 @@
         <v>1</v>
       </c>
       <c r="J293">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K293">
         <v>0</v>
       </c>
       <c r="L293">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M293">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="N293">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="O293">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="294" spans="1:15">
@@ -15353,10 +15329,10 @@
         <v>0</v>
       </c>
       <c r="H294">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I294">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J294">
         <v>0</v>
@@ -15365,16 +15341,16 @@
         <v>0</v>
       </c>
       <c r="L294">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M294">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="N294">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="O294">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="295" spans="1:15">
@@ -15382,46 +15358,46 @@
         <v>308</v>
       </c>
       <c r="B295">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C295">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D295">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E295">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F295">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="G295">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="H295">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I295">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J295">
         <v>1</v>
       </c>
       <c r="K295">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L295">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="M295">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="N295">
-        <v>138</v>
+        <v>174</v>
       </c>
       <c r="O295">
-        <v>146</v>
+        <v>209</v>
       </c>
     </row>
     <row r="296" spans="1:15">
@@ -15429,46 +15405,46 @@
         <v>309</v>
       </c>
       <c r="B296">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C296">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D296">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E296">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="F296">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="G296">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="H296">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I296">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J296">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K296">
         <v>0</v>
       </c>
       <c r="L296">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="M296">
-        <v>122</v>
+        <v>25</v>
       </c>
       <c r="N296">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="O296">
-        <v>130</v>
+        <v>28</v>
       </c>
     </row>
     <row r="297" spans="1:15">
@@ -15476,43 +15452,43 @@
         <v>310</v>
       </c>
       <c r="B297">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C297">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D297">
         <v>0</v>
       </c>
       <c r="E297">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F297">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G297">
+        <v>20</v>
+      </c>
+      <c r="H297">
+        <v>5</v>
+      </c>
+      <c r="I297">
         <v>8</v>
       </c>
-      <c r="H297">
-        <v>6</v>
-      </c>
-      <c r="I297">
-        <v>0</v>
-      </c>
       <c r="J297">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K297">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L297">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="M297">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="N297">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O297">
         <v>52</v>
@@ -15529,40 +15505,40 @@
         <v>0</v>
       </c>
       <c r="D298">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E298">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F298">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G298">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="H298">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I298">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J298">
         <v>0</v>
       </c>
       <c r="K298">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L298">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="M298">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="N298">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="O298">
-        <v>21</v>
+        <v>94</v>
       </c>
     </row>
     <row r="299" spans="1:15">
@@ -15570,46 +15546,46 @@
         <v>312</v>
       </c>
       <c r="B299">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C299">
         <v>0</v>
       </c>
       <c r="D299">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E299">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F299">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G299">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H299">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I299">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J299">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K299">
         <v>0</v>
       </c>
       <c r="L299">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="M299">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="N299">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="O299">
-        <v>46</v>
+        <v>9</v>
       </c>
     </row>
     <row r="300" spans="1:15">
@@ -15626,37 +15602,37 @@
         <v>0</v>
       </c>
       <c r="E300">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F300">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G300">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H300">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I300">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J300">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K300">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L300">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="M300">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="N300">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="O300">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="301" spans="1:15">
@@ -15664,46 +15640,46 @@
         <v>314</v>
       </c>
       <c r="B301">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C301">
         <v>0</v>
       </c>
       <c r="D301">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E301">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F301">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G301">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H301">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I301">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J301">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K301">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L301">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M301">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="N301">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="O301">
-        <v>26</v>
+        <v>94</v>
       </c>
     </row>
     <row r="302" spans="1:15">
@@ -15711,46 +15687,46 @@
         <v>315</v>
       </c>
       <c r="B302">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C302">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D302">
         <v>0</v>
       </c>
       <c r="E302">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F302">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G302">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H302">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I302">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J302">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K302">
         <v>0</v>
       </c>
       <c r="L302">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="M302">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="N302">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="O302">
-        <v>28</v>
+        <v>120</v>
       </c>
     </row>
     <row r="303" spans="1:15">
@@ -15758,46 +15734,46 @@
         <v>316</v>
       </c>
       <c r="B303">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C303">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D303">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E303">
+        <v>1</v>
+      </c>
+      <c r="F303">
+        <v>2</v>
+      </c>
+      <c r="G303">
         <v>9</v>
       </c>
-      <c r="F303">
-        <v>16</v>
-      </c>
-      <c r="G303">
-        <v>74</v>
-      </c>
       <c r="H303">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I303">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="J303">
         <v>2</v>
       </c>
       <c r="K303">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L303">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M303">
-        <v>158</v>
+        <v>24</v>
       </c>
       <c r="N303">
-        <v>192</v>
+        <v>24</v>
       </c>
       <c r="O303">
-        <v>227</v>
+        <v>25</v>
       </c>
     </row>
     <row r="304" spans="1:15">
@@ -15805,46 +15781,46 @@
         <v>317</v>
       </c>
       <c r="B304">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C304">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D304">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E304">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="F304">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="G304">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="H304">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I304">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J304">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K304">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L304">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="M304">
-        <v>46</v>
+        <v>147</v>
       </c>
       <c r="N304">
-        <v>48</v>
+        <v>224</v>
       </c>
       <c r="O304">
-        <v>49</v>
+        <v>281</v>
       </c>
     </row>
     <row r="305" spans="1:15">
@@ -15852,46 +15828,46 @@
         <v>318</v>
       </c>
       <c r="B305">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C305">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D305">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E305">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="F305">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="G305">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="H305">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="I305">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J305">
         <v>3</v>
       </c>
       <c r="K305">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L305">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="M305">
-        <v>72</v>
+        <v>220</v>
       </c>
       <c r="N305">
-        <v>72</v>
+        <v>316</v>
       </c>
       <c r="O305">
-        <v>74</v>
+        <v>381</v>
       </c>
     </row>
     <row r="306" spans="1:15">
@@ -15899,46 +15875,46 @@
         <v>319</v>
       </c>
       <c r="B306">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C306">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D306">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E306">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F306">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="G306">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="H306">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I306">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J306">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K306">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L306">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="M306">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="N306">
-        <v>87</v>
+        <v>300</v>
       </c>
       <c r="O306">
-        <v>104</v>
+        <v>366</v>
       </c>
     </row>
     <row r="307" spans="1:15">
@@ -15946,46 +15922,46 @@
         <v>320</v>
       </c>
       <c r="B307">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C307">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D307">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E307">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="F307">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G307">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="H307">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I307">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J307">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K307">
         <v>0</v>
       </c>
       <c r="L307">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M307">
-        <v>13</v>
+        <v>116</v>
       </c>
       <c r="N307">
-        <v>14</v>
+        <v>160</v>
       </c>
       <c r="O307">
-        <v>14</v>
+        <v>193</v>
       </c>
     </row>
     <row r="308" spans="1:15">
@@ -15993,46 +15969,46 @@
         <v>321</v>
       </c>
       <c r="B308">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C308">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D308">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E308">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F308">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G308">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H308">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I308">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J308">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K308">
         <v>1</v>
       </c>
       <c r="L308">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M308">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="N308">
-        <v>15</v>
+        <v>73</v>
       </c>
       <c r="O308">
-        <v>15</v>
+        <v>90</v>
       </c>
     </row>
     <row r="309" spans="1:15">
@@ -16040,46 +16016,46 @@
         <v>322</v>
       </c>
       <c r="B309">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C309">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D309">
         <v>2</v>
       </c>
       <c r="E309">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F309">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G309">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H309">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I309">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J309">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K309">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L309">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M309">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N309">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="O309">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="310" spans="1:15">
@@ -16090,43 +16066,43 @@
         <v>3</v>
       </c>
       <c r="C310">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D310">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E310">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F310">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G310">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="H310">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I310">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J310">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K310">
         <v>0</v>
       </c>
       <c r="L310">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M310">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="N310">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="O310">
-        <v>126</v>
+        <v>92</v>
       </c>
     </row>
     <row r="311" spans="1:15">
@@ -16134,46 +16110,46 @@
         <v>324</v>
       </c>
       <c r="B311">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C311">
         <v>1</v>
       </c>
       <c r="D311">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E311">
         <v>1</v>
       </c>
       <c r="F311">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G311">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H311">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I311">
         <v>1</v>
       </c>
       <c r="J311">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K311">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L311">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M311">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="N311">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="O311">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="312" spans="1:15">
@@ -16181,46 +16157,46 @@
         <v>325</v>
       </c>
       <c r="B312">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C312">
+        <v>1</v>
+      </c>
+      <c r="D312">
+        <v>1</v>
+      </c>
+      <c r="E312">
+        <v>1</v>
+      </c>
+      <c r="F312">
         <v>5</v>
       </c>
-      <c r="D312">
-        <v>10</v>
-      </c>
-      <c r="E312">
-        <v>28</v>
-      </c>
-      <c r="F312">
-        <v>31</v>
-      </c>
       <c r="G312">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="H312">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I312">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J312">
         <v>3</v>
       </c>
       <c r="K312">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L312">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M312">
-        <v>149</v>
+        <v>21</v>
       </c>
       <c r="N312">
-        <v>226</v>
+        <v>24</v>
       </c>
       <c r="O312">
-        <v>283</v>
+        <v>25</v>
       </c>
     </row>
     <row r="313" spans="1:15">
@@ -16228,46 +16204,46 @@
         <v>326</v>
       </c>
       <c r="B313">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C313">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D313">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E313">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="F313">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="G313">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="H313">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="I313">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J313">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K313">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L313">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="M313">
-        <v>232</v>
+        <v>25</v>
       </c>
       <c r="N313">
-        <v>328</v>
+        <v>32</v>
       </c>
       <c r="O313">
-        <v>393</v>
+        <v>39</v>
       </c>
     </row>
     <row r="314" spans="1:15">
@@ -16275,46 +16251,46 @@
         <v>327</v>
       </c>
       <c r="B314">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C314">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D314">
+        <v>0</v>
+      </c>
+      <c r="E314">
+        <v>3</v>
+      </c>
+      <c r="F314">
+        <v>2</v>
+      </c>
+      <c r="G314">
+        <v>5</v>
+      </c>
+      <c r="H314">
+        <v>0</v>
+      </c>
+      <c r="I314">
+        <v>1</v>
+      </c>
+      <c r="J314">
+        <v>0</v>
+      </c>
+      <c r="K314">
+        <v>0</v>
+      </c>
+      <c r="L314">
+        <v>0</v>
+      </c>
+      <c r="M314">
         <v>12</v>
       </c>
-      <c r="E314">
-        <v>40</v>
-      </c>
-      <c r="F314">
-        <v>48</v>
-      </c>
-      <c r="G314">
-        <v>63</v>
-      </c>
-      <c r="H314">
-        <v>9</v>
-      </c>
-      <c r="I314">
-        <v>9</v>
-      </c>
-      <c r="J314">
-        <v>3</v>
-      </c>
-      <c r="K314">
-        <v>0</v>
-      </c>
-      <c r="L314">
-        <v>8</v>
-      </c>
-      <c r="M314">
-        <v>210</v>
-      </c>
       <c r="N314">
-        <v>307</v>
+        <v>17</v>
       </c>
       <c r="O314">
-        <v>373</v>
+        <v>19</v>
       </c>
     </row>
     <row r="315" spans="1:15">
@@ -16322,46 +16298,46 @@
         <v>328</v>
       </c>
       <c r="B315">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C315">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D315">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E315">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="F315">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G315">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="H315">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I315">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J315">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K315">
         <v>0</v>
       </c>
       <c r="L315">
+        <v>0</v>
+      </c>
+      <c r="M315">
+        <v>7</v>
+      </c>
+      <c r="N315">
+        <v>8</v>
+      </c>
+      <c r="O315">
         <v>9</v>
-      </c>
-      <c r="M315">
-        <v>127</v>
-      </c>
-      <c r="N315">
-        <v>171</v>
-      </c>
-      <c r="O315">
-        <v>204</v>
       </c>
     </row>
     <row r="316" spans="1:15">
@@ -16369,46 +16345,46 @@
         <v>329</v>
       </c>
       <c r="B316">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C316">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D316">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E316">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F316">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G316">
+        <v>3</v>
+      </c>
+      <c r="H316">
+        <v>2</v>
+      </c>
+      <c r="I316">
+        <v>2</v>
+      </c>
+      <c r="J316">
+        <v>0</v>
+      </c>
+      <c r="K316">
+        <v>0</v>
+      </c>
+      <c r="L316">
+        <v>1</v>
+      </c>
+      <c r="M316">
+        <v>12</v>
+      </c>
+      <c r="N316">
+        <v>16</v>
+      </c>
+      <c r="O316">
         <v>22</v>
-      </c>
-      <c r="H316">
-        <v>2</v>
-      </c>
-      <c r="I316">
-        <v>2</v>
-      </c>
-      <c r="J316">
-        <v>1</v>
-      </c>
-      <c r="K316">
-        <v>0</v>
-      </c>
-      <c r="L316">
-        <v>10</v>
-      </c>
-      <c r="M316">
-        <v>59</v>
-      </c>
-      <c r="N316">
-        <v>78</v>
-      </c>
-      <c r="O316">
-        <v>95</v>
       </c>
     </row>
     <row r="317" spans="1:15">
@@ -16419,43 +16395,43 @@
         <v>2</v>
       </c>
       <c r="C317">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D317">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E317">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F317">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G317">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="H317">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I317">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J317">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K317">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L317">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M317">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="N317">
-        <v>101</v>
+        <v>22</v>
       </c>
       <c r="O317">
-        <v>110</v>
+        <v>26</v>
       </c>
     </row>
     <row r="318" spans="1:15">
@@ -16463,46 +16439,46 @@
         <v>331</v>
       </c>
       <c r="B318">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C318">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D318">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E318">
         <v>4</v>
       </c>
       <c r="F318">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G318">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="H318">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I318">
         <v>1</v>
       </c>
       <c r="J318">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K318">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L318">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M318">
-        <v>91</v>
+        <v>18</v>
       </c>
       <c r="N318">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="O318">
-        <v>109</v>
+        <v>33</v>
       </c>
     </row>
     <row r="319" spans="1:15">
@@ -16510,46 +16486,46 @@
         <v>332</v>
       </c>
       <c r="B319">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C319">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D319">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E319">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F319">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G319">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H319">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I319">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J319">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K319">
         <v>0</v>
       </c>
       <c r="L319">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M319">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="N319">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="O319">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="320" spans="1:15">
@@ -16557,46 +16533,46 @@
         <v>333</v>
       </c>
       <c r="B320">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C320">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D320">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E320">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F320">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G320">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H320">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I320">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J320">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K320">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L320">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M320">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="N320">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="O320">
-        <v>34</v>
+        <v>16</v>
       </c>
     </row>
     <row r="321" spans="1:15">
@@ -16604,46 +16580,46 @@
         <v>334</v>
       </c>
       <c r="B321">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C321">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D321">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E321">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F321">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G321">
         <v>4</v>
       </c>
       <c r="H321">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I321">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J321">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K321">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L321">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M321">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="N321">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="O321">
-        <v>46</v>
+        <v>6</v>
       </c>
     </row>
     <row r="322" spans="1:15">
@@ -16660,37 +16636,37 @@
         <v>0</v>
       </c>
       <c r="E322">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F322">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G322">
+        <v>25</v>
+      </c>
+      <c r="H322">
         <v>5</v>
       </c>
-      <c r="H322">
-        <v>0</v>
-      </c>
       <c r="I322">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J322">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K322">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L322">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M322">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="N322">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="O322">
-        <v>23</v>
+        <v>60</v>
       </c>
     </row>
     <row r="323" spans="1:15">
@@ -16698,28 +16674,28 @@
         <v>336</v>
       </c>
       <c r="B323">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="C323">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D323">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E323">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F323">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G323">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H323">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I323">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J323">
         <v>0</v>
@@ -16728,16 +16704,16 @@
         <v>0</v>
       </c>
       <c r="L323">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M323">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="N323">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="O323">
-        <v>15</v>
+        <v>125</v>
       </c>
     </row>
     <row r="324" spans="1:15">
@@ -16745,46 +16721,46 @@
         <v>337</v>
       </c>
       <c r="B324">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C324">
         <v>0</v>
       </c>
       <c r="D324">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E324">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F324">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G324">
+        <v>20</v>
+      </c>
+      <c r="H324">
         <v>4</v>
       </c>
-      <c r="H324">
-        <v>2</v>
-      </c>
       <c r="I324">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J324">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K324">
         <v>0</v>
       </c>
       <c r="L324">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M324">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="N324">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="O324">
-        <v>32</v>
+        <v>51</v>
       </c>
     </row>
     <row r="325" spans="1:15">
@@ -16792,26 +16768,26 @@
         <v>338</v>
       </c>
       <c r="B325">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C325">
         <v>0</v>
       </c>
       <c r="D325">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E325">
         <v>0</v>
       </c>
       <c r="F325">
+        <v>3</v>
+      </c>
+      <c r="G325">
+        <v>7</v>
+      </c>
+      <c r="H325">
         <v>4</v>
       </c>
-      <c r="G325">
-        <v>5</v>
-      </c>
-      <c r="H325">
-        <v>1</v>
-      </c>
       <c r="I325">
         <v>1</v>
       </c>
@@ -16819,19 +16795,19 @@
         <v>0</v>
       </c>
       <c r="K325">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L325">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M325">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N325">
+        <v>23</v>
+      </c>
+      <c r="O325">
         <v>27</v>
-      </c>
-      <c r="O325">
-        <v>31</v>
       </c>
     </row>
     <row r="326" spans="1:15">
@@ -16839,7 +16815,7 @@
         <v>339</v>
       </c>
       <c r="B326">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C326">
         <v>0</v>
@@ -16848,37 +16824,37 @@
         <v>0</v>
       </c>
       <c r="E326">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F326">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G326">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="H326">
         <v>1</v>
       </c>
       <c r="I326">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J326">
         <v>1</v>
       </c>
       <c r="K326">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L326">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M326">
+        <v>30</v>
+      </c>
+      <c r="N326">
         <v>31</v>
       </c>
-      <c r="N326">
-        <v>45</v>
-      </c>
       <c r="O326">
-        <v>46</v>
+        <v>32</v>
       </c>
     </row>
     <row r="327" spans="1:15">
@@ -16886,7 +16862,7 @@
         <v>340</v>
       </c>
       <c r="B327">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C327">
         <v>0</v>
@@ -16895,10 +16871,10 @@
         <v>0</v>
       </c>
       <c r="E327">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F327">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G327">
         <v>1</v>
@@ -16916,16 +16892,16 @@
         <v>0</v>
       </c>
       <c r="L327">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M327">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="N327">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="O327">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328" spans="1:15">
@@ -16933,7 +16909,7 @@
         <v>341</v>
       </c>
       <c r="B328">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C328">
         <v>0</v>
@@ -16942,37 +16918,37 @@
         <v>0</v>
       </c>
       <c r="E328">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F328">
         <v>1</v>
       </c>
       <c r="G328">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H328">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I328">
         <v>0</v>
       </c>
       <c r="J328">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K328">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L328">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M328">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="N328">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="O328">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329" spans="1:15">
@@ -16980,25 +16956,25 @@
         <v>342</v>
       </c>
       <c r="B329">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C329">
         <v>0</v>
       </c>
       <c r="D329">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E329">
         <v>0</v>
       </c>
       <c r="F329">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G329">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H329">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I329">
         <v>0</v>
@@ -17010,16 +16986,16 @@
         <v>0</v>
       </c>
       <c r="L329">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M329">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="N329">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="O329">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="330" spans="1:15">
@@ -17027,7 +17003,7 @@
         <v>343</v>
       </c>
       <c r="B330">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C330">
         <v>0</v>
@@ -17036,37 +17012,37 @@
         <v>0</v>
       </c>
       <c r="E330">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F330">
+        <v>2</v>
+      </c>
+      <c r="G330">
+        <v>16</v>
+      </c>
+      <c r="H330">
+        <v>10</v>
+      </c>
+      <c r="I330">
+        <v>8</v>
+      </c>
+      <c r="J330">
+        <v>1</v>
+      </c>
+      <c r="K330">
+        <v>1</v>
+      </c>
+      <c r="L330">
         <v>4</v>
       </c>
-      <c r="G330">
-        <v>26</v>
-      </c>
-      <c r="H330">
-        <v>4</v>
-      </c>
-      <c r="I330">
-        <v>7</v>
-      </c>
-      <c r="J330">
-        <v>3</v>
-      </c>
-      <c r="K330">
-        <v>1</v>
-      </c>
-      <c r="L330">
-        <v>10</v>
-      </c>
       <c r="M330">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="N330">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="O330">
-        <v>71</v>
+        <v>47</v>
       </c>
     </row>
     <row r="331" spans="1:15">
@@ -17074,46 +17050,46 @@
         <v>344</v>
       </c>
       <c r="B331">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="C331">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D331">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E331">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F331">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G331">
+        <v>1</v>
+      </c>
+      <c r="H331">
+        <v>0</v>
+      </c>
+      <c r="I331">
+        <v>0</v>
+      </c>
+      <c r="J331">
+        <v>1</v>
+      </c>
+      <c r="K331">
+        <v>2</v>
+      </c>
+      <c r="L331">
+        <v>2</v>
+      </c>
+      <c r="M331">
         <v>10</v>
       </c>
-      <c r="H331">
-        <v>4</v>
-      </c>
-      <c r="I331">
-        <v>0</v>
-      </c>
-      <c r="J331">
-        <v>0</v>
-      </c>
-      <c r="K331">
-        <v>0</v>
-      </c>
-      <c r="L331">
-        <v>19</v>
-      </c>
-      <c r="M331">
-        <v>118</v>
-      </c>
       <c r="N331">
-        <v>125</v>
+        <v>10</v>
       </c>
       <c r="O331">
-        <v>147</v>
+        <v>10</v>
       </c>
     </row>
     <row r="332" spans="1:15">
@@ -17121,46 +17097,46 @@
         <v>345</v>
       </c>
       <c r="B332">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C332">
         <v>0</v>
       </c>
       <c r="D332">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E332">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F332">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G332">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H332">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I332">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J332">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K332">
         <v>0</v>
       </c>
       <c r="L332">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M332">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="N332">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="O332">
-        <v>53</v>
+        <v>3</v>
       </c>
     </row>
     <row r="333" spans="1:15">
@@ -17174,40 +17150,40 @@
         <v>0</v>
       </c>
       <c r="D333">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E333">
         <v>0</v>
       </c>
       <c r="F333">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G333">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H333">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I333">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J333">
         <v>0</v>
       </c>
       <c r="K333">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L333">
+        <v>0</v>
+      </c>
+      <c r="M333">
+        <v>3</v>
+      </c>
+      <c r="N333">
+        <v>5</v>
+      </c>
+      <c r="O333">
         <v>6</v>
-      </c>
-      <c r="M333">
-        <v>23</v>
-      </c>
-      <c r="N333">
-        <v>25</v>
-      </c>
-      <c r="O333">
-        <v>29</v>
       </c>
     </row>
     <row r="334" spans="1:15">
@@ -17215,7 +17191,7 @@
         <v>347</v>
       </c>
       <c r="B334">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C334">
         <v>0</v>
@@ -17227,16 +17203,16 @@
         <v>0</v>
       </c>
       <c r="F334">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G334">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H334">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I334">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J334">
         <v>1</v>
@@ -17245,16 +17221,16 @@
         <v>0</v>
       </c>
       <c r="L334">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M334">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="N334">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="O334">
-        <v>33</v>
+        <v>7</v>
       </c>
     </row>
     <row r="335" spans="1:15">
@@ -17277,7 +17253,7 @@
         <v>0</v>
       </c>
       <c r="G335">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H335">
         <v>0</v>
@@ -17286,22 +17262,22 @@
         <v>0</v>
       </c>
       <c r="J335">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K335">
         <v>0</v>
       </c>
       <c r="L335">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M335">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N335">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O335">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336" spans="1:15">
@@ -17318,37 +17294,37 @@
         <v>0</v>
       </c>
       <c r="E336">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F336">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G336">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H336">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I336">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J336">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K336">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L336">
         <v>0</v>
       </c>
       <c r="M336">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="N336">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="O336">
-        <v>1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="337" spans="1:15">
@@ -17356,31 +17332,31 @@
         <v>350</v>
       </c>
       <c r="B337">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C337">
         <v>0</v>
       </c>
       <c r="D337">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E337">
         <v>0</v>
       </c>
       <c r="F337">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G337">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H337">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I337">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J337">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K337">
         <v>0</v>
@@ -17389,13 +17365,13 @@
         <v>2</v>
       </c>
       <c r="M337">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="N337">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="O337">
-        <v>7</v>
+        <v>59</v>
       </c>
     </row>
     <row r="338" spans="1:15">
@@ -17412,37 +17388,37 @@
         <v>0</v>
       </c>
       <c r="E338">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F338">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G338">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H338">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I338">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J338">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K338">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L338">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M338">
+        <v>44</v>
+      </c>
+      <c r="N338">
+        <v>47</v>
+      </c>
+      <c r="O338">
         <v>49</v>
-      </c>
-      <c r="N338">
-        <v>51</v>
-      </c>
-      <c r="O338">
-        <v>53</v>
       </c>
     </row>
     <row r="339" spans="1:15">
@@ -17453,7 +17429,7 @@
         <v>1</v>
       </c>
       <c r="C339">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D339">
         <v>0</v>
@@ -17462,34 +17438,34 @@
         <v>0</v>
       </c>
       <c r="F339">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G339">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H339">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I339">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J339">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K339">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L339">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M339">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="N339">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="O339">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="340" spans="1:15">
@@ -17497,7 +17473,7 @@
         <v>353</v>
       </c>
       <c r="B340">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C340">
         <v>0</v>
@@ -17506,37 +17482,37 @@
         <v>0</v>
       </c>
       <c r="E340">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F340">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G340">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H340">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I340">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J340">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K340">
         <v>0</v>
       </c>
       <c r="L340">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M340">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="N340">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="O340">
-        <v>12</v>
+        <v>57</v>
       </c>
     </row>
     <row r="341" spans="1:15">
@@ -17544,46 +17520,46 @@
         <v>354</v>
       </c>
       <c r="B341">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C341">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D341">
         <v>0</v>
       </c>
       <c r="E341">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F341">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G341">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H341">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I341">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J341">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K341">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L341">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M341">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="N341">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="O341">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="342" spans="1:15">
@@ -17591,7 +17567,7 @@
         <v>355</v>
       </c>
       <c r="B342">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C342">
         <v>0</v>
@@ -17609,28 +17585,28 @@
         <v>2</v>
       </c>
       <c r="H342">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I342">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J342">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K342">
         <v>0</v>
       </c>
       <c r="L342">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M342">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N342">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O342">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="343" spans="1:15">
@@ -17638,46 +17614,46 @@
         <v>356</v>
       </c>
       <c r="B343">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C343">
         <v>0</v>
       </c>
       <c r="D343">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E343">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F343">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G343">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H343">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I343">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J343">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K343">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L343">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M343">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="N343">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="O343">
-        <v>6</v>
+        <v>52</v>
       </c>
     </row>
     <row r="344" spans="1:15">
@@ -17694,37 +17670,37 @@
         <v>0</v>
       </c>
       <c r="E344">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F344">
         <v>9</v>
       </c>
       <c r="G344">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H344">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I344">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J344">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K344">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L344">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M344">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="N344">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="O344">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="345" spans="1:15">
@@ -17732,7 +17708,7 @@
         <v>358</v>
       </c>
       <c r="B345">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C345">
         <v>0</v>
@@ -17741,37 +17717,37 @@
         <v>0</v>
       </c>
       <c r="E345">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F345">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G345">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H345">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I345">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J345">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K345">
         <v>0</v>
       </c>
       <c r="L345">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="M345">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="N345">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="O345">
-        <v>73</v>
+        <v>43</v>
       </c>
     </row>
     <row r="346" spans="1:15">
@@ -17788,37 +17764,37 @@
         <v>0</v>
       </c>
       <c r="E346">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F346">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G346">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H346">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I346">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J346">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K346">
         <v>0</v>
       </c>
       <c r="L346">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M346">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="N346">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="O346">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="347" spans="1:15">
@@ -17826,7 +17802,7 @@
         <v>360</v>
       </c>
       <c r="B347">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C347">
         <v>0</v>
@@ -17835,13 +17811,13 @@
         <v>0</v>
       </c>
       <c r="E347">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F347">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G347">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H347">
         <v>1</v>
@@ -17850,22 +17826,22 @@
         <v>4</v>
       </c>
       <c r="J347">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K347">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L347">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M347">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="N347">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="O347">
-        <v>26</v>
+        <v>9</v>
       </c>
     </row>
     <row r="348" spans="1:15">
@@ -17873,7 +17849,7 @@
         <v>361</v>
       </c>
       <c r="B348">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C348">
         <v>0</v>
@@ -17885,34 +17861,34 @@
         <v>1</v>
       </c>
       <c r="F348">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G348">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="H348">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I348">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J348">
         <v>2</v>
       </c>
       <c r="K348">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L348">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M348">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="N348">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="O348">
-        <v>60</v>
+        <v>43</v>
       </c>
     </row>
     <row r="349" spans="1:15">
@@ -17920,7 +17896,7 @@
         <v>362</v>
       </c>
       <c r="B349">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C349">
         <v>0</v>
@@ -17929,37 +17905,37 @@
         <v>0</v>
       </c>
       <c r="E349">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F349">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G349">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H349">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I349">
+        <v>1</v>
+      </c>
+      <c r="J349">
+        <v>1</v>
+      </c>
+      <c r="K349">
+        <v>0</v>
+      </c>
+      <c r="L349">
+        <v>0</v>
+      </c>
+      <c r="M349">
         <v>4</v>
       </c>
-      <c r="J349">
-        <v>1</v>
-      </c>
-      <c r="K349">
-        <v>0</v>
-      </c>
-      <c r="L349">
-        <v>6</v>
-      </c>
-      <c r="M349">
-        <v>30</v>
-      </c>
       <c r="N349">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="O349">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="350" spans="1:15">
@@ -17973,40 +17949,40 @@
         <v>0</v>
       </c>
       <c r="D350">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E350">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F350">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G350">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="H350">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I350">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J350">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K350">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L350">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M350">
-        <v>11</v>
+        <v>117</v>
       </c>
       <c r="N350">
-        <v>13</v>
+        <v>133</v>
       </c>
       <c r="O350">
-        <v>18</v>
+        <v>142</v>
       </c>
     </row>
     <row r="351" spans="1:15">
@@ -18014,46 +17990,46 @@
         <v>364</v>
       </c>
       <c r="B351">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C351">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D351">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E351">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F351">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G351">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="H351">
         <v>7</v>
       </c>
       <c r="I351">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J351">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K351">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L351">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M351">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="N351">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="O351">
-        <v>61</v>
+        <v>98</v>
       </c>
     </row>
     <row r="352" spans="1:15">
@@ -18061,7 +18037,7 @@
         <v>365</v>
       </c>
       <c r="B352">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C352">
         <v>0</v>
@@ -18073,34 +18049,34 @@
         <v>1</v>
       </c>
       <c r="F352">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G352">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="H352">
+        <v>3</v>
+      </c>
+      <c r="I352">
         <v>5</v>
       </c>
-      <c r="I352">
-        <v>3</v>
-      </c>
       <c r="J352">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K352">
         <v>0</v>
       </c>
       <c r="L352">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M352">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N352">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="O352">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="353" spans="1:15">
@@ -18108,46 +18084,46 @@
         <v>366</v>
       </c>
       <c r="B353">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C353">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D353">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E353">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="F353">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G353">
         <v>18</v>
       </c>
       <c r="H353">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I353">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J353">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K353">
         <v>0</v>
       </c>
       <c r="L353">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M353">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="N353">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="O353">
-        <v>53</v>
+        <v>82</v>
       </c>
     </row>
     <row r="354" spans="1:15">
@@ -18164,37 +18140,37 @@
         <v>0</v>
       </c>
       <c r="E354">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F354">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G354">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="H354">
+        <v>0</v>
+      </c>
+      <c r="I354">
+        <v>0</v>
+      </c>
+      <c r="J354">
+        <v>0</v>
+      </c>
+      <c r="K354">
+        <v>0</v>
+      </c>
+      <c r="L354">
+        <v>0</v>
+      </c>
+      <c r="M354">
         <v>5</v>
       </c>
-      <c r="I354">
-        <v>2</v>
-      </c>
-      <c r="J354">
-        <v>3</v>
-      </c>
-      <c r="K354">
-        <v>0</v>
-      </c>
-      <c r="L354">
+      <c r="N354">
         <v>5</v>
       </c>
-      <c r="M354">
-        <v>41</v>
-      </c>
-      <c r="N354">
-        <v>46</v>
-      </c>
       <c r="O354">
-        <v>53</v>
+        <v>6</v>
       </c>
     </row>
     <row r="355" spans="1:15">
@@ -18202,7 +18178,7 @@
         <v>368</v>
       </c>
       <c r="B355">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C355">
         <v>0</v>
@@ -18211,37 +18187,37 @@
         <v>0</v>
       </c>
       <c r="E355">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F355">
         <v>1</v>
       </c>
       <c r="G355">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H355">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I355">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J355">
         <v>0</v>
       </c>
       <c r="K355">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L355">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M355">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="N355">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="O355">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356" spans="1:15">
@@ -18258,37 +18234,37 @@
         <v>0</v>
       </c>
       <c r="E356">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F356">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G356">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="H356">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I356">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J356">
         <v>2</v>
       </c>
       <c r="K356">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L356">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M356">
+        <v>43</v>
+      </c>
+      <c r="N356">
         <v>44</v>
       </c>
-      <c r="N356">
-        <v>47</v>
-      </c>
       <c r="O356">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="357" spans="1:15">
@@ -18296,7 +18272,7 @@
         <v>370</v>
       </c>
       <c r="B357">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C357">
         <v>0</v>
@@ -18308,13 +18284,13 @@
         <v>0</v>
       </c>
       <c r="F357">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G357">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H357">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I357">
         <v>1</v>
@@ -18326,16 +18302,16 @@
         <v>0</v>
       </c>
       <c r="L357">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M357">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N357">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O357">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="358" spans="1:15">
@@ -18343,46 +18319,46 @@
         <v>371</v>
       </c>
       <c r="B358">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C358">
         <v>0</v>
       </c>
       <c r="D358">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E358">
+        <v>14</v>
+      </c>
+      <c r="F358">
         <v>9</v>
       </c>
-      <c r="F358">
-        <v>24</v>
-      </c>
       <c r="G358">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="H358">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I358">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J358">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K358">
         <v>1</v>
       </c>
       <c r="L358">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M358">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="N358">
-        <v>141</v>
+        <v>88</v>
       </c>
       <c r="O358">
-        <v>150</v>
+        <v>100</v>
       </c>
     </row>
     <row r="359" spans="1:15">
@@ -18393,43 +18369,43 @@
         <v>1</v>
       </c>
       <c r="C359">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D359">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E359">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F359">
         <v>18</v>
       </c>
       <c r="G359">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="H359">
         <v>6</v>
       </c>
       <c r="I359">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J359">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K359">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L359">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M359">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="N359">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="O359">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="360" spans="1:15">
@@ -18437,46 +18413,46 @@
         <v>373</v>
       </c>
       <c r="B360">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C360">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D360">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E360">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="F360">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G360">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H360">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I360">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J360">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K360">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L360">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M360">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="N360">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="O360">
-        <v>71</v>
+        <v>144</v>
       </c>
     </row>
     <row r="361" spans="1:15">
@@ -18484,46 +18460,46 @@
         <v>374</v>
       </c>
       <c r="B361">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C361">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D361">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E361">
+        <v>39</v>
+      </c>
+      <c r="F361">
         <v>21</v>
       </c>
-      <c r="F361">
-        <v>9</v>
-      </c>
       <c r="G361">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="H361">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I361">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J361">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K361">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L361">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="M361">
-        <v>70</v>
+        <v>146</v>
       </c>
       <c r="N361">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="O361">
-        <v>91</v>
+        <v>201</v>
       </c>
     </row>
     <row r="362" spans="1:15">
@@ -18531,7 +18507,7 @@
         <v>375</v>
       </c>
       <c r="B362">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C362">
         <v>0</v>
@@ -18540,16 +18516,16 @@
         <v>0</v>
       </c>
       <c r="E362">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F362">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G362">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H362">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I362">
         <v>0</v>
@@ -18558,19 +18534,19 @@
         <v>0</v>
       </c>
       <c r="K362">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L362">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M362">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="N362">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O362">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="363" spans="1:15">
@@ -18578,31 +18554,31 @@
         <v>376</v>
       </c>
       <c r="B363">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C363">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D363">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E363">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F363">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="G363">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="H363">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I363">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J363">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K363">
         <v>0</v>
@@ -18611,13 +18587,13 @@
         <v>5</v>
       </c>
       <c r="M363">
-        <v>9</v>
+        <v>143</v>
       </c>
       <c r="N363">
-        <v>9</v>
+        <v>158</v>
       </c>
       <c r="O363">
-        <v>9</v>
+        <v>174</v>
       </c>
     </row>
     <row r="364" spans="1:15">
@@ -18625,7 +18601,7 @@
         <v>377</v>
       </c>
       <c r="B364">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C364">
         <v>0</v>
@@ -18634,37 +18610,37 @@
         <v>0</v>
       </c>
       <c r="E364">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F364">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G364">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H364">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="I364">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="J364">
         <v>2</v>
       </c>
       <c r="K364">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L364">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M364">
-        <v>51</v>
+        <v>121</v>
       </c>
       <c r="N364">
-        <v>52</v>
+        <v>131</v>
       </c>
       <c r="O364">
-        <v>59</v>
+        <v>145</v>
       </c>
     </row>
     <row r="365" spans="1:15">
@@ -18672,7 +18648,7 @@
         <v>378</v>
       </c>
       <c r="B365">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C365">
         <v>0</v>
@@ -18681,37 +18657,37 @@
         <v>0</v>
       </c>
       <c r="E365">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F365">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G365">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H365">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I365">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J365">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K365">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L365">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M365">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="N365">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="O365">
-        <v>19</v>
+        <v>62</v>
       </c>
     </row>
     <row r="366" spans="1:15">
@@ -18719,46 +18695,46 @@
         <v>379</v>
       </c>
       <c r="B366">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C366">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D366">
         <v>1</v>
       </c>
       <c r="E366">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="F366">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="G366">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H366">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I366">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J366">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K366">
         <v>1</v>
       </c>
       <c r="L366">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="M366">
-        <v>82</v>
+        <v>175</v>
       </c>
       <c r="N366">
-        <v>90</v>
+        <v>209</v>
       </c>
       <c r="O366">
-        <v>102</v>
+        <v>239</v>
       </c>
     </row>
     <row r="367" spans="1:15">
@@ -18766,46 +18742,46 @@
         <v>380</v>
       </c>
       <c r="B367">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C367">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D367">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E367">
+        <v>36</v>
+      </c>
+      <c r="F367">
+        <v>30</v>
+      </c>
+      <c r="G367">
+        <v>53</v>
+      </c>
+      <c r="H367">
         <v>10</v>
       </c>
-      <c r="F367">
-        <v>19</v>
-      </c>
-      <c r="G367">
-        <v>26</v>
-      </c>
-      <c r="H367">
-        <v>6</v>
-      </c>
       <c r="I367">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J367">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K367">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L367">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M367">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="N367">
-        <v>93</v>
+        <v>200</v>
       </c>
       <c r="O367">
-        <v>103</v>
+        <v>223</v>
       </c>
     </row>
     <row r="368" spans="1:15">
@@ -18813,46 +18789,46 @@
         <v>381</v>
       </c>
       <c r="B368">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C368">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D368">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E368">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F368">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G368">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="H368">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I368">
+        <v>10</v>
+      </c>
+      <c r="J368">
+        <v>1</v>
+      </c>
+      <c r="K368">
+        <v>1</v>
+      </c>
+      <c r="L368">
         <v>4</v>
       </c>
-      <c r="J368">
-        <v>0</v>
-      </c>
-      <c r="K368">
-        <v>1</v>
-      </c>
-      <c r="L368">
-        <v>8</v>
-      </c>
       <c r="M368">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="N368">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="O368">
-        <v>152</v>
+        <v>177</v>
       </c>
     </row>
     <row r="369" spans="1:15">
@@ -18860,46 +18836,46 @@
         <v>382</v>
       </c>
       <c r="B369">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C369">
         <v>2</v>
       </c>
       <c r="D369">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E369">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="F369">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="G369">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H369">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I369">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J369">
         <v>2</v>
       </c>
       <c r="K369">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L369">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M369">
-        <v>149</v>
+        <v>72</v>
       </c>
       <c r="N369">
-        <v>170</v>
+        <v>74</v>
       </c>
       <c r="O369">
-        <v>204</v>
+        <v>74</v>
       </c>
     </row>
     <row r="370" spans="1:15">
@@ -18907,46 +18883,46 @@
         <v>383</v>
       </c>
       <c r="B370">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C370">
         <v>0</v>
       </c>
       <c r="D370">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E370">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F370">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G370">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="H370">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="I370">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J370">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K370">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L370">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M370">
-        <v>11</v>
+        <v>250</v>
       </c>
       <c r="N370">
-        <v>11</v>
+        <v>285</v>
       </c>
       <c r="O370">
-        <v>18</v>
+        <v>306</v>
       </c>
     </row>
     <row r="371" spans="1:15">
@@ -18954,46 +18930,46 @@
         <v>384</v>
       </c>
       <c r="B371">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C371">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D371">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E371">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F371">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="G371">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="H371">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I371">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J371">
         <v>2</v>
       </c>
       <c r="K371">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L371">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="M371">
-        <v>148</v>
+        <v>224</v>
       </c>
       <c r="N371">
-        <v>163</v>
+        <v>252</v>
       </c>
       <c r="O371">
-        <v>179</v>
+        <v>270</v>
       </c>
     </row>
     <row r="372" spans="1:15">
@@ -19001,46 +18977,46 @@
         <v>385</v>
       </c>
       <c r="B372">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C372">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D372">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E372">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F372">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G372">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="H372">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="I372">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="J372">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K372">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L372">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M372">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="N372">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O372">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="373" spans="1:15">
@@ -19048,422 +19024,46 @@
         <v>386</v>
       </c>
       <c r="B373">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C373">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D373">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E373">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="F373">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G373">
+        <v>68</v>
+      </c>
+      <c r="H373">
         <v>11</v>
       </c>
-      <c r="H373">
-        <v>19</v>
-      </c>
       <c r="I373">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J373">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K373">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L373">
         <v>8</v>
       </c>
       <c r="M373">
-        <v>62</v>
+        <v>262</v>
       </c>
       <c r="N373">
-        <v>66</v>
+        <v>307</v>
       </c>
       <c r="O373">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="374" spans="1:15">
-      <c r="A374" t="s">
-        <v>387</v>
-      </c>
-      <c r="B374">
-        <v>2</v>
-      </c>
-      <c r="C374">
-        <v>0</v>
-      </c>
-      <c r="D374">
-        <v>2</v>
-      </c>
-      <c r="E374">
-        <v>45</v>
-      </c>
-      <c r="F374">
-        <v>32</v>
-      </c>
-      <c r="G374">
-        <v>51</v>
-      </c>
-      <c r="H374">
-        <v>14</v>
-      </c>
-      <c r="I374">
-        <v>12</v>
-      </c>
-      <c r="J374">
-        <v>4</v>
-      </c>
-      <c r="K374">
-        <v>1</v>
-      </c>
-      <c r="L374">
-        <v>20</v>
-      </c>
-      <c r="M374">
-        <v>183</v>
-      </c>
-      <c r="N374">
-        <v>217</v>
-      </c>
-      <c r="O374">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="375" spans="1:15">
-      <c r="A375" t="s">
-        <v>388</v>
-      </c>
-      <c r="B375">
-        <v>2</v>
-      </c>
-      <c r="C375">
-        <v>1</v>
-      </c>
-      <c r="D375">
-        <v>2</v>
-      </c>
-      <c r="E375">
-        <v>35</v>
-      </c>
-      <c r="F375">
-        <v>33</v>
-      </c>
-      <c r="G375">
-        <v>51</v>
-      </c>
-      <c r="H375">
-        <v>9</v>
-      </c>
-      <c r="I375">
-        <v>12</v>
-      </c>
-      <c r="J375">
-        <v>0</v>
-      </c>
-      <c r="K375">
-        <v>0</v>
-      </c>
-      <c r="L375">
-        <v>8</v>
-      </c>
-      <c r="M375">
-        <v>153</v>
-      </c>
-      <c r="N375">
-        <v>207</v>
-      </c>
-      <c r="O375">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="376" spans="1:15">
-      <c r="A376" t="s">
-        <v>389</v>
-      </c>
-      <c r="B376">
-        <v>4</v>
-      </c>
-      <c r="C376">
-        <v>1</v>
-      </c>
-      <c r="D376">
-        <v>3</v>
-      </c>
-      <c r="E376">
-        <v>24</v>
-      </c>
-      <c r="F376">
-        <v>22</v>
-      </c>
-      <c r="G376">
-        <v>39</v>
-      </c>
-      <c r="H376">
-        <v>7</v>
-      </c>
-      <c r="I376">
-        <v>8</v>
-      </c>
-      <c r="J376">
-        <v>2</v>
-      </c>
-      <c r="K376">
-        <v>0</v>
-      </c>
-      <c r="L376">
-        <v>27</v>
-      </c>
-      <c r="M376">
-        <v>137</v>
-      </c>
-      <c r="N376">
-        <v>157</v>
-      </c>
-      <c r="O376">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="377" spans="1:15">
-      <c r="A377" t="s">
-        <v>390</v>
-      </c>
-      <c r="B377">
-        <v>2</v>
-      </c>
-      <c r="C377">
-        <v>0</v>
-      </c>
-      <c r="D377">
-        <v>1</v>
-      </c>
-      <c r="E377">
-        <v>2</v>
-      </c>
-      <c r="F377">
-        <v>5</v>
-      </c>
-      <c r="G377">
-        <v>39</v>
-      </c>
-      <c r="H377">
-        <v>11</v>
-      </c>
-      <c r="I377">
-        <v>5</v>
-      </c>
-      <c r="J377">
-        <v>2</v>
-      </c>
-      <c r="K377">
-        <v>0</v>
-      </c>
-      <c r="L377">
-        <v>17</v>
-      </c>
-      <c r="M377">
-        <v>84</v>
-      </c>
-      <c r="N377">
-        <v>86</v>
-      </c>
-      <c r="O377">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="378" spans="1:15">
-      <c r="A378" t="s">
-        <v>391</v>
-      </c>
-      <c r="B378">
-        <v>0</v>
-      </c>
-      <c r="C378">
-        <v>0</v>
-      </c>
-      <c r="D378">
-        <v>1</v>
-      </c>
-      <c r="E378">
-        <v>15</v>
-      </c>
-      <c r="F378">
-        <v>42</v>
-      </c>
-      <c r="G378">
-        <v>127</v>
-      </c>
-      <c r="H378">
-        <v>19</v>
-      </c>
-      <c r="I378">
-        <v>9</v>
-      </c>
-      <c r="J378">
-        <v>1</v>
-      </c>
-      <c r="K378">
-        <v>1</v>
-      </c>
-      <c r="L378">
-        <v>40</v>
-      </c>
-      <c r="M378">
-        <v>255</v>
-      </c>
-      <c r="N378">
-        <v>290</v>
-      </c>
-      <c r="O378">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="379" spans="1:15">
-      <c r="A379" t="s">
-        <v>392</v>
-      </c>
-      <c r="B379">
-        <v>2</v>
-      </c>
-      <c r="C379">
-        <v>2</v>
-      </c>
-      <c r="D379">
-        <v>4</v>
-      </c>
-      <c r="E379">
-        <v>31</v>
-      </c>
-      <c r="F379">
-        <v>36</v>
-      </c>
-      <c r="G379">
-        <v>68</v>
-      </c>
-      <c r="H379">
-        <v>13</v>
-      </c>
-      <c r="I379">
-        <v>13</v>
-      </c>
-      <c r="J379">
-        <v>3</v>
-      </c>
-      <c r="K379">
-        <v>3</v>
-      </c>
-      <c r="L379">
-        <v>59</v>
-      </c>
-      <c r="M379">
-        <v>234</v>
-      </c>
-      <c r="N379">
-        <v>263</v>
-      </c>
-      <c r="O379">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="380" spans="1:15">
-      <c r="A380" t="s">
-        <v>393</v>
-      </c>
-      <c r="B380">
-        <v>5</v>
-      </c>
-      <c r="C380">
-        <v>1</v>
-      </c>
-      <c r="D380">
-        <v>0</v>
-      </c>
-      <c r="E380">
-        <v>13</v>
-      </c>
-      <c r="F380">
-        <v>21</v>
-      </c>
-      <c r="G380">
-        <v>40</v>
-      </c>
-      <c r="H380">
-        <v>5</v>
-      </c>
-      <c r="I380">
-        <v>3</v>
-      </c>
-      <c r="J380">
-        <v>0</v>
-      </c>
-      <c r="K380">
-        <v>0</v>
-      </c>
-      <c r="L380">
-        <v>44</v>
-      </c>
-      <c r="M380">
-        <v>132</v>
-      </c>
-      <c r="N380">
-        <v>154</v>
-      </c>
-      <c r="O380">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="381" spans="1:15">
-      <c r="A381" t="s">
-        <v>394</v>
-      </c>
-      <c r="B381">
-        <v>17</v>
-      </c>
-      <c r="C381">
-        <v>6</v>
-      </c>
-      <c r="D381">
-        <v>1</v>
-      </c>
-      <c r="E381">
-        <v>51</v>
-      </c>
-      <c r="F381">
-        <v>52</v>
-      </c>
-      <c r="G381">
-        <v>58</v>
-      </c>
-      <c r="H381">
-        <v>9</v>
-      </c>
-      <c r="I381">
-        <v>7</v>
-      </c>
-      <c r="J381">
-        <v>0</v>
-      </c>
-      <c r="K381">
-        <v>1</v>
-      </c>
-      <c r="L381">
-        <v>73</v>
-      </c>
-      <c r="M381">
-        <v>275</v>
-      </c>
-      <c r="N381">
-        <v>320</v>
-      </c>
-      <c r="O381">
-        <v>337</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -6208,7 +6208,7 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E100">
         <v>2</v>
@@ -6232,7 +6232,7 @@
         <v>0</v>
       </c>
       <c r="L100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M100">
         <v>19</v>
@@ -7430,7 +7430,7 @@
         <v>2</v>
       </c>
       <c r="D126">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E126">
         <v>6</v>
@@ -7454,7 +7454,7 @@
         <v>0</v>
       </c>
       <c r="L126">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M126">
         <v>55</v>
@@ -12741,7 +12741,7 @@
         <v>3</v>
       </c>
       <c r="D239">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E239">
         <v>46</v>
@@ -12765,7 +12765,7 @@
         <v>0</v>
       </c>
       <c r="L239">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M239">
         <v>185</v>
@@ -14148,7 +14148,7 @@
         <v>1</v>
       </c>
       <c r="C269">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D269">
         <v>2</v>
@@ -14175,7 +14175,7 @@
         <v>0</v>
       </c>
       <c r="L269">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M269">
         <v>48</v>
@@ -14245,7 +14245,7 @@
         <v>6</v>
       </c>
       <c r="D271">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E271">
         <v>21</v>
@@ -14269,7 +14269,7 @@
         <v>0</v>
       </c>
       <c r="L271">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M271">
         <v>184</v>
@@ -14286,7 +14286,7 @@
         <v>285</v>
       </c>
       <c r="B272">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C272">
         <v>10</v>
@@ -14316,7 +14316,7 @@
         <v>1</v>
       </c>
       <c r="L272">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M272">
         <v>251</v>
@@ -14521,7 +14521,7 @@
         <v>290</v>
       </c>
       <c r="B277">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C277">
         <v>2</v>
@@ -14551,7 +14551,7 @@
         <v>1</v>
       </c>
       <c r="L277">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M277">
         <v>132</v>
@@ -14668,7 +14668,7 @@
         <v>2</v>
       </c>
       <c r="D280">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E280">
         <v>8</v>
@@ -14692,7 +14692,7 @@
         <v>0</v>
       </c>
       <c r="L280">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M280">
         <v>87</v>
@@ -14803,7 +14803,7 @@
         <v>296</v>
       </c>
       <c r="B283">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C283">
         <v>12</v>
@@ -14812,7 +14812,7 @@
         <v>22</v>
       </c>
       <c r="E283">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F283">
         <v>13</v>
@@ -14833,7 +14833,7 @@
         <v>1</v>
       </c>
       <c r="L283">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M283">
         <v>272</v>
@@ -14991,7 +14991,7 @@
         <v>300</v>
       </c>
       <c r="B287">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C287">
         <v>11</v>
@@ -15021,7 +15021,7 @@
         <v>0</v>
       </c>
       <c r="L287">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M287">
         <v>283</v>
@@ -15044,7 +15044,7 @@
         <v>4</v>
       </c>
       <c r="D288">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E288">
         <v>24</v>
@@ -15068,7 +15068,7 @@
         <v>1</v>
       </c>
       <c r="L288">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M288">
         <v>101</v>
@@ -15508,7 +15508,7 @@
         <v>311</v>
       </c>
       <c r="B298">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C298">
         <v>0</v>
@@ -15538,7 +15538,7 @@
         <v>4</v>
       </c>
       <c r="L298">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M298">
         <v>140</v>
@@ -15561,7 +15561,7 @@
         <v>0</v>
       </c>
       <c r="D299">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E299">
         <v>2</v>
@@ -15585,7 +15585,7 @@
         <v>0</v>
       </c>
       <c r="L299">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M299">
         <v>25</v>
@@ -15608,7 +15608,7 @@
         <v>0</v>
       </c>
       <c r="D300">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E300">
         <v>7</v>
@@ -15632,7 +15632,7 @@
         <v>0</v>
       </c>
       <c r="L300">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M300">
         <v>50</v>
@@ -15649,22 +15649,22 @@
         <v>314</v>
       </c>
       <c r="B301">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C301">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D301">
         <v>2</v>
       </c>
       <c r="E301">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F301">
         <v>6</v>
       </c>
       <c r="G301">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H301">
         <v>5</v>
@@ -15679,7 +15679,7 @@
         <v>2</v>
       </c>
       <c r="L301">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M301">
         <v>68</v>
@@ -15743,7 +15743,7 @@
         <v>316</v>
       </c>
       <c r="B303">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C303">
         <v>0</v>
@@ -15773,7 +15773,7 @@
         <v>1</v>
       </c>
       <c r="L303">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M303">
         <v>9</v>
@@ -15978,7 +15978,7 @@
         <v>321</v>
       </c>
       <c r="B308">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C308">
         <v>3</v>
@@ -16008,7 +16008,7 @@
         <v>1</v>
       </c>
       <c r="L308">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M308">
         <v>220</v>
@@ -16125,10 +16125,10 @@
         <v>1</v>
       </c>
       <c r="D311">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E311">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F311">
         <v>11</v>
@@ -16149,7 +16149,7 @@
         <v>1</v>
       </c>
       <c r="L311">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M311">
         <v>54</v>
@@ -16172,7 +16172,7 @@
         <v>1</v>
       </c>
       <c r="D312">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E312">
         <v>13</v>
@@ -16196,7 +16196,7 @@
         <v>0</v>
       </c>
       <c r="L312">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M312">
         <v>77</v>
@@ -16213,7 +16213,7 @@
         <v>326</v>
       </c>
       <c r="B313">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C313">
         <v>3</v>
@@ -16243,7 +16243,7 @@
         <v>0</v>
       </c>
       <c r="L313">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M313">
         <v>74</v>
@@ -16354,13 +16354,13 @@
         <v>329</v>
       </c>
       <c r="B316">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C316">
         <v>1</v>
       </c>
       <c r="D316">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E316">
         <v>4</v>
@@ -16369,7 +16369,7 @@
         <v>2</v>
       </c>
       <c r="G316">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H316">
         <v>1</v>
@@ -16384,7 +16384,7 @@
         <v>1</v>
       </c>
       <c r="L316">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M316">
         <v>25</v>
@@ -16495,7 +16495,7 @@
         <v>332</v>
       </c>
       <c r="B319">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C319">
         <v>0</v>
@@ -16525,7 +16525,7 @@
         <v>0</v>
       </c>
       <c r="L319">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M319">
         <v>12</v>
@@ -18951,7 +18951,7 @@
         <v>25</v>
       </c>
       <c r="F371">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G371">
         <v>40</v>
@@ -18969,7 +18969,7 @@
         <v>1</v>
       </c>
       <c r="L371">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M371">
         <v>128</v>
@@ -19095,7 +19095,7 @@
         <v>39</v>
       </c>
       <c r="G374">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H374">
         <v>19</v>
@@ -19110,7 +19110,7 @@
         <v>4</v>
       </c>
       <c r="L374">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M374">
         <v>224</v>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -18948,13 +18948,13 @@
         <v>6</v>
       </c>
       <c r="E371">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F371">
         <v>24</v>
       </c>
       <c r="G371">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H371">
         <v>13</v>
@@ -18969,7 +18969,7 @@
         <v>1</v>
       </c>
       <c r="L371">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M371">
         <v>128</v>
@@ -19001,7 +19001,7 @@
         <v>3</v>
       </c>
       <c r="G372">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H372">
         <v>9</v>
@@ -19016,7 +19016,7 @@
         <v>0</v>
       </c>
       <c r="L372">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M372">
         <v>72</v>
@@ -19089,13 +19089,13 @@
         <v>9</v>
       </c>
       <c r="E374">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F374">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G374">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H374">
         <v>19</v>
@@ -19110,7 +19110,7 @@
         <v>4</v>
       </c>
       <c r="L374">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="M374">
         <v>224</v>
@@ -19174,7 +19174,7 @@
         <v>389</v>
       </c>
       <c r="B376">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C376">
         <v>9</v>
@@ -19189,7 +19189,7 @@
         <v>43</v>
       </c>
       <c r="G376">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H376">
         <v>11</v>
@@ -19204,7 +19204,7 @@
         <v>1</v>
       </c>
       <c r="L376">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M376">
         <v>262</v>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -19095,7 +19095,7 @@
         <v>36</v>
       </c>
       <c r="F374">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G374">
         <v>94</v>
@@ -19113,7 +19113,7 @@
         <v>4</v>
       </c>
       <c r="L374">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M374">
         <v>224</v>
@@ -19224,22 +19224,22 @@
         <v>390</v>
       </c>
       <c r="B377">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C377">
         <v>4</v>
       </c>
       <c r="D377">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E377">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="F377">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="G377">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="H377">
         <v>12</v>
@@ -19254,7 +19254,7 @@
         <v>2</v>
       </c>
       <c r="L377">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="M377">
         <v>190</v>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O377"/>
+  <dimension ref="A1:O381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18917,6 +18917,202 @@
         <v>230</v>
       </c>
     </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>9</v>
+      </c>
+      <c r="C378" t="n">
+        <v>4</v>
+      </c>
+      <c r="D378" t="n">
+        <v>5</v>
+      </c>
+      <c r="E378" t="n">
+        <v>20</v>
+      </c>
+      <c r="F378" t="n">
+        <v>15</v>
+      </c>
+      <c r="G378" t="n">
+        <v>35</v>
+      </c>
+      <c r="H378" t="n">
+        <v>13</v>
+      </c>
+      <c r="I378" t="n">
+        <v>5</v>
+      </c>
+      <c r="J378" t="n">
+        <v>3</v>
+      </c>
+      <c r="K378" t="n">
+        <v>0</v>
+      </c>
+      <c r="L378" t="n">
+        <v>103</v>
+      </c>
+      <c r="M378" t="n">
+        <v>212</v>
+      </c>
+      <c r="N378" t="n">
+        <v>243</v>
+      </c>
+      <c r="O378" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>3</v>
+      </c>
+      <c r="C379" t="n">
+        <v>0</v>
+      </c>
+      <c r="D379" t="n">
+        <v>0</v>
+      </c>
+      <c r="E379" t="n">
+        <v>1</v>
+      </c>
+      <c r="F379" t="n">
+        <v>0</v>
+      </c>
+      <c r="G379" t="n">
+        <v>3</v>
+      </c>
+      <c r="H379" t="n">
+        <v>3</v>
+      </c>
+      <c r="I379" t="n">
+        <v>2</v>
+      </c>
+      <c r="J379" t="n">
+        <v>1</v>
+      </c>
+      <c r="K379" t="n">
+        <v>0</v>
+      </c>
+      <c r="L379" t="n">
+        <v>12</v>
+      </c>
+      <c r="M379" t="n">
+        <v>25</v>
+      </c>
+      <c r="N379" t="n">
+        <v>26</v>
+      </c>
+      <c r="O379" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>0</v>
+      </c>
+      <c r="C380" t="n">
+        <v>0</v>
+      </c>
+      <c r="D380" t="n">
+        <v>1</v>
+      </c>
+      <c r="E380" t="n">
+        <v>5</v>
+      </c>
+      <c r="F380" t="n">
+        <v>9</v>
+      </c>
+      <c r="G380" t="n">
+        <v>35</v>
+      </c>
+      <c r="H380" t="n">
+        <v>8</v>
+      </c>
+      <c r="I380" t="n">
+        <v>1</v>
+      </c>
+      <c r="J380" t="n">
+        <v>0</v>
+      </c>
+      <c r="K380" t="n">
+        <v>1</v>
+      </c>
+      <c r="L380" t="n">
+        <v>65</v>
+      </c>
+      <c r="M380" t="n">
+        <v>125</v>
+      </c>
+      <c r="N380" t="n">
+        <v>129</v>
+      </c>
+      <c r="O380" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>1</v>
+      </c>
+      <c r="C381" t="n">
+        <v>0</v>
+      </c>
+      <c r="D381" t="n">
+        <v>0</v>
+      </c>
+      <c r="E381" t="n">
+        <v>0</v>
+      </c>
+      <c r="F381" t="n">
+        <v>0</v>
+      </c>
+      <c r="G381" t="n">
+        <v>0</v>
+      </c>
+      <c r="H381" t="n">
+        <v>0</v>
+      </c>
+      <c r="I381" t="n">
+        <v>0</v>
+      </c>
+      <c r="J381" t="n">
+        <v>0</v>
+      </c>
+      <c r="K381" t="n">
+        <v>0</v>
+      </c>
+      <c r="L381" t="n">
+        <v>0</v>
+      </c>
+      <c r="M381" t="n">
+        <v>1</v>
+      </c>
+      <c r="N381" t="n">
+        <v>1</v>
+      </c>
+      <c r="O381" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -19292,7 +19292,7 @@
         <v>14</v>
       </c>
       <c r="E378">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F378">
         <v>21</v>
@@ -19313,7 +19313,7 @@
         <v>0</v>
       </c>
       <c r="L378">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M378">
         <v>212</v>
@@ -19392,7 +19392,7 @@
         <v>13</v>
       </c>
       <c r="G380">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H380">
         <v>7</v>
@@ -19407,7 +19407,7 @@
         <v>1</v>
       </c>
       <c r="L380">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M380">
         <v>125</v>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -18405,7 +18405,7 @@
         <v>6</v>
       </c>
       <c r="G359">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H359">
         <v>4</v>
@@ -18420,7 +18420,7 @@
         <v>0</v>
       </c>
       <c r="L359">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M359">
         <v>43</v>
@@ -19189,7 +19189,7 @@
         <v>389</v>
       </c>
       <c r="B376">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C376">
         <v>9</v>
@@ -19219,7 +19219,7 @@
         <v>1</v>
       </c>
       <c r="L376">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M376">
         <v>262</v>
@@ -19424,22 +19424,22 @@
         <v>394</v>
       </c>
       <c r="B381">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C381">
         <v>2</v>
       </c>
       <c r="D381">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E381">
         <v>6</v>
       </c>
       <c r="F381">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G381">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H381">
         <v>10</v>
@@ -19454,7 +19454,7 @@
         <v>1</v>
       </c>
       <c r="L381">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M381">
         <v>116</v>

--- a/daily_slab_mix.xlsx
+++ b/daily_slab_mix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="398">
   <si>
     <t>Date</t>
   </si>
@@ -1205,6 +1205,9 @@
   </si>
   <si>
     <t>2026-10-28</t>
+  </si>
+  <si>
+    <t>2026-10-29</t>
   </si>
 </sst>
 </file>
@@ -1562,7 +1565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O383"/>
+  <dimension ref="A1:O384"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -19492,7 +19495,7 @@
         <v>15</v>
       </c>
       <c r="G382">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H382">
         <v>9</v>
@@ -19507,7 +19510,7 @@
         <v>1</v>
       </c>
       <c r="L382">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M382">
         <v>80</v>
@@ -19530,40 +19533,87 @@
         <v>0</v>
       </c>
       <c r="D383">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E383">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F383">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="G383">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="H383">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I383">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J383">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K383">
         <v>0</v>
       </c>
       <c r="L383">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M383">
-        <v>6</v>
+        <v>130</v>
       </c>
       <c r="N383">
-        <v>6</v>
+        <v>139</v>
       </c>
       <c r="O383">
-        <v>6</v>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="384" spans="1:15">
+      <c r="A384" t="s">
+        <v>397</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+      <c r="C384">
+        <v>0</v>
+      </c>
+      <c r="D384">
+        <v>0</v>
+      </c>
+      <c r="E384">
+        <v>7</v>
+      </c>
+      <c r="F384">
+        <v>25</v>
+      </c>
+      <c r="G384">
+        <v>48</v>
+      </c>
+      <c r="H384">
+        <v>4</v>
+      </c>
+      <c r="I384">
+        <v>2</v>
+      </c>
+      <c r="J384">
+        <v>1</v>
+      </c>
+      <c r="K384">
+        <v>0</v>
+      </c>
+      <c r="L384">
+        <v>18</v>
+      </c>
+      <c r="M384">
+        <v>105</v>
+      </c>
+      <c r="N384">
+        <v>112</v>
+      </c>
+      <c r="O384">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
